--- a/qwen_zeroshot_2000_sample/qwen_zeroshot_disease_macro_metrics.xlsx
+++ b/qwen_zeroshot_2000_sample/qwen_zeroshot_disease_macro_metrics.xlsx
@@ -1473,19 +1473,19 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>0.1705057586379569</v>
+        <v>0.4988733099649474</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>0.001467351430667645</v>
       </c>
       <c r="D2">
-        <v>0.3451725862931466</v>
+        <v>0.319159579789895</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>0.0007347538574577516</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1493,19 +1493,19 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>0.6073934837092732</v>
+        <v>0.2800125313283208</v>
       </c>
       <c r="C3">
-        <v>0.005736137667304016</v>
+        <v>0.001587301587301587</v>
       </c>
       <c r="D3">
-        <v>0.4797398699349675</v>
+        <v>0.3706853426713357</v>
       </c>
       <c r="E3">
-        <v>0.002879078694817658</v>
+        <v>0.0007961783439490446</v>
       </c>
       <c r="F3">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1513,19 +1513,19 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>0.7943707236160067</v>
+        <v>0.8323599880203654</v>
       </c>
       <c r="C4">
-        <v>0.1145833333333333</v>
+        <v>0.1118012422360248</v>
       </c>
       <c r="D4">
-        <v>0.3196598299149575</v>
+        <v>0.2846423211605803</v>
       </c>
       <c r="E4">
-        <v>0.06089965397923876</v>
+        <v>0.05924950625411455</v>
       </c>
       <c r="F4">
-        <v>0.967032967032967</v>
+        <v>0.9890109890109891</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1533,19 +1533,19 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>0.607420894023104</v>
+        <v>0.7135547463586138</v>
       </c>
       <c r="C5">
-        <v>0.009463722397476341</v>
+        <v>0.01227935533384497</v>
       </c>
       <c r="D5">
-        <v>0.3716858429214607</v>
+        <v>0.3561780890445223</v>
       </c>
       <c r="E5">
-        <v>0.004761904761904762</v>
+        <v>0.006177606177606178</v>
       </c>
       <c r="F5">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1553,19 +1553,19 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>0.4195327017394218</v>
+        <v>0.4228493313431017</v>
       </c>
       <c r="C6">
-        <v>0.05158437730287398</v>
+        <v>0.05718370264474625</v>
       </c>
       <c r="D6">
-        <v>0.3561780890445223</v>
+        <v>0.3401700850425213</v>
       </c>
       <c r="E6">
-        <v>0.02715283165244375</v>
+        <v>0.03005259203606311</v>
       </c>
       <c r="F6">
-        <v>0.5147058823529411</v>
+        <v>0.5882352941176471</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1573,19 +1573,19 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>0.7574445756263937</v>
+        <v>0.820092155319428</v>
       </c>
       <c r="C7">
-        <v>0.08143547273982056</v>
+        <v>0.07908163265306123</v>
       </c>
       <c r="D7">
-        <v>0.3341670835417709</v>
+        <v>0.2776388194097049</v>
       </c>
       <c r="E7">
-        <v>0.04256854256854257</v>
+        <v>0.04119601328903655</v>
       </c>
       <c r="F7">
-        <v>0.9365079365079365</v>
+        <v>0.9841269841269841</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1593,19 +1593,19 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>0.2154624519150359</v>
+        <v>0.1870296036126443</v>
       </c>
       <c r="C8">
-        <v>0.001549186676994578</v>
+        <v>0.002754820936639119</v>
       </c>
       <c r="D8">
-        <v>0.3551775887943972</v>
+        <v>0.2756378189094547</v>
       </c>
       <c r="E8">
-        <v>0.0007782101167315176</v>
+        <v>0.001383125864453665</v>
       </c>
       <c r="F8">
-        <v>0.1666666666666667</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1613,19 +1613,19 @@
         <v>13</v>
       </c>
       <c r="B9">
-        <v>0.4978493373634039</v>
+        <v>0.5044175773076029</v>
       </c>
       <c r="C9">
-        <v>0.04103967168262654</v>
+        <v>0.04142394822006473</v>
       </c>
       <c r="D9">
-        <v>0.2986493246623312</v>
+        <v>0.2591295647823912</v>
       </c>
       <c r="E9">
-        <v>0.02115655853314527</v>
+        <v>0.02131912058627582</v>
       </c>
       <c r="F9">
-        <v>0.6818181818181818</v>
+        <v>0.7272727272727273</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1633,16 +1633,16 @@
         <v>14</v>
       </c>
       <c r="B10">
-        <v>0.5099624060150376</v>
+        <v>0.412781954887218</v>
       </c>
       <c r="C10">
-        <v>0.004172461752433936</v>
+        <v>0.004246284501061571</v>
       </c>
       <c r="D10">
-        <v>0.2836418209104552</v>
+        <v>0.2961480740370185</v>
       </c>
       <c r="E10">
-        <v>0.002092050209205021</v>
+        <v>0.0021291696238467</v>
       </c>
       <c r="F10">
         <v>0.75</v>
@@ -1653,19 +1653,19 @@
         <v>15</v>
       </c>
       <c r="B11">
-        <v>0.2751889168765743</v>
+        <v>0.4643396905361641</v>
       </c>
       <c r="C11">
-        <v>0.005830903790087463</v>
+        <v>0.01305483028720627</v>
       </c>
       <c r="D11">
-        <v>0.3176588294147074</v>
+        <v>0.2436218109054527</v>
       </c>
       <c r="E11">
-        <v>0.002945508100147275</v>
+        <v>0.006587615283267457</v>
       </c>
       <c r="F11">
-        <v>0.2857142857142857</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1673,16 +1673,16 @@
         <v>16</v>
       </c>
       <c r="B12">
-        <v>0.8547619047619047</v>
+        <v>0.8523809523809524</v>
       </c>
       <c r="C12">
-        <v>0.007117437722419928</v>
+        <v>0.006106870229007634</v>
       </c>
       <c r="D12">
-        <v>0.4417208604302151</v>
+        <v>0.3486743371685843</v>
       </c>
       <c r="E12">
-        <v>0.003571428571428571</v>
+        <v>0.003062787136294028</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -1693,16 +1693,16 @@
         <v>17</v>
       </c>
       <c r="B13">
-        <v>0.7735235235235235</v>
+        <v>0.9534534534534534</v>
       </c>
       <c r="C13">
-        <v>0.001358695652173913</v>
+        <v>0.001278772378516624</v>
       </c>
       <c r="D13">
-        <v>0.264632316158079</v>
+        <v>0.2186093046523262</v>
       </c>
       <c r="E13">
-        <v>0.0006798096532970768</v>
+        <v>0.0006397952655150352</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -1713,19 +1713,19 @@
         <v>18</v>
       </c>
       <c r="B14">
-        <v>0.7147811692506461</v>
+        <v>0.8083656330749354</v>
       </c>
       <c r="C14">
-        <v>0.07707641196013289</v>
+        <v>0.07901234567901234</v>
       </c>
       <c r="D14">
-        <v>0.3051525762881441</v>
+        <v>0.2536268134067033</v>
       </c>
       <c r="E14">
-        <v>0.04024982650936849</v>
+        <v>0.04113110539845758</v>
       </c>
       <c r="F14">
-        <v>0.90625</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1733,19 +1733,19 @@
         <v>19</v>
       </c>
       <c r="B15">
-        <v>0.7262024048096193</v>
+        <v>0.6422845691382766</v>
       </c>
       <c r="C15">
-        <v>0.004531722054380665</v>
+        <v>0.002635046113306983</v>
       </c>
       <c r="D15">
-        <v>0.3406703351675838</v>
+        <v>0.2426213106553277</v>
       </c>
       <c r="E15">
-        <v>0.002271006813020439</v>
+        <v>0.00132013201320132</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1753,19 +1753,19 @@
         <v>20</v>
       </c>
       <c r="B16">
-        <v>0.2053079619429143</v>
+        <v>0.3714321482223335</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>0.001346801346801347</v>
       </c>
       <c r="D16">
-        <v>0.4167083541770886</v>
+        <v>0.2581290645322661</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>0.0006743088334457181</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1773,19 +1773,19 @@
         <v>21</v>
       </c>
       <c r="B17">
-        <v>0.2175438596491228</v>
+        <v>0.2988095238095237</v>
       </c>
       <c r="C17">
-        <v>0.001567398119122257</v>
+        <v>0.002635046113306983</v>
       </c>
       <c r="D17">
-        <v>0.3626813406703352</v>
+        <v>0.2426213106553277</v>
       </c>
       <c r="E17">
-        <v>0.0007861635220125787</v>
+        <v>0.001321003963011889</v>
       </c>
       <c r="F17">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1793,16 +1793,16 @@
         <v>22</v>
       </c>
       <c r="B18">
-        <v>0.2266290726817042</v>
+        <v>0.3075814536340852</v>
       </c>
       <c r="C18">
-        <v>0.001472754050073638</v>
+        <v>0.00131578947368421</v>
       </c>
       <c r="D18">
-        <v>0.3216608304152076</v>
+        <v>0.2406203101550775</v>
       </c>
       <c r="E18">
-        <v>0.0007385524372230429</v>
+        <v>0.0006596306068601583</v>
       </c>
       <c r="F18">
         <v>0.25</v>
@@ -1813,19 +1813,19 @@
         <v>23</v>
       </c>
       <c r="B19">
-        <v>0.7338581539794886</v>
+        <v>0.7486999855553951</v>
       </c>
       <c r="C19">
-        <v>0.02616279069767442</v>
+        <v>0.02600780234070221</v>
       </c>
       <c r="D19">
-        <v>0.3296648324162081</v>
+        <v>0.2506253126563281</v>
       </c>
       <c r="E19">
-        <v>0.01328413284132841</v>
+        <v>0.01318391562294001</v>
       </c>
       <c r="F19">
-        <v>0.8571428571428571</v>
+        <v>0.9523809523809523</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1833,19 +1833,19 @@
         <v>24</v>
       </c>
       <c r="B20">
-        <v>0.8198946981192808</v>
+        <v>0.7750839196210971</v>
       </c>
       <c r="C20">
-        <v>0.03244837758112094</v>
+        <v>0.02604166666666667</v>
       </c>
       <c r="D20">
-        <v>0.343671835917959</v>
+        <v>0.2516258129064533</v>
       </c>
       <c r="E20">
-        <v>0.01649175412293853</v>
+        <v>0.01321003963011889</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>0.9090909090909091</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1853,16 +1853,16 @@
         <v>25</v>
       </c>
       <c r="B21">
-        <v>0.7953406813627254</v>
+        <v>0.8572144288577155</v>
       </c>
       <c r="C21">
-        <v>0.004559270516717325</v>
+        <v>0.004158004158004158</v>
       </c>
       <c r="D21">
-        <v>0.344672336168084</v>
+        <v>0.2811405702851426</v>
       </c>
       <c r="E21">
-        <v>0.002284843869002285</v>
+        <v>0.002083333333333333</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -1873,19 +1873,19 @@
         <v>26</v>
       </c>
       <c r="B22">
-        <v>0.5422736826846417</v>
+        <v>0.515265999855041</v>
       </c>
       <c r="C22">
-        <v>0.02888583218707015</v>
+        <v>0.03085177733065057</v>
       </c>
       <c r="D22">
-        <v>0.2936468234117058</v>
+        <v>0.2771385692846423</v>
       </c>
       <c r="E22">
-        <v>0.01472650771388499</v>
+        <v>0.01572112098427888</v>
       </c>
       <c r="F22">
-        <v>0.75</v>
+        <v>0.8214285714285714</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1893,16 +1893,16 @@
         <v>27</v>
       </c>
       <c r="B23">
-        <v>0.7582665330661322</v>
+        <v>0.8461923847695391</v>
       </c>
       <c r="C23">
-        <v>0.004528301886792453</v>
+        <v>0.003754693366708385</v>
       </c>
       <c r="D23">
-        <v>0.3401700850425213</v>
+        <v>0.2036018009004502</v>
       </c>
       <c r="E23">
-        <v>0.00226928895612708</v>
+        <v>0.001880877742946708</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -1913,19 +1913,19 @@
         <v>28</v>
       </c>
       <c r="B24">
-        <v>0.5487987987987988</v>
+        <v>0.1011011011011011</v>
       </c>
       <c r="C24">
-        <v>0.001662510390689942</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>0.3991995997998999</v>
+        <v>0.304152076038019</v>
       </c>
       <c r="E24">
-        <v>0.0008319467554076539</v>
+        <v>0</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -1933,16 +1933,16 @@
         <v>29</v>
       </c>
       <c r="B25">
-        <v>0.4478267900551909</v>
+        <v>0.3926305960416906</v>
       </c>
       <c r="C25">
-        <v>0.08751793400286945</v>
+        <v>0.07398423286840509</v>
       </c>
       <c r="D25">
-        <v>0.3636818409204602</v>
+        <v>0.2361180590295148</v>
       </c>
       <c r="E25">
-        <v>0.04717710750193349</v>
+        <v>0.03940568475452196</v>
       </c>
       <c r="F25">
         <v>0.6039603960396039</v>
@@ -1953,19 +1953,19 @@
         <v>30</v>
       </c>
       <c r="B26">
-        <v>0.4672250139586823</v>
+        <v>0.414321608040201</v>
       </c>
       <c r="C26">
-        <v>0.008319467554076539</v>
+        <v>0.006230529595015576</v>
       </c>
       <c r="D26">
-        <v>0.4037018509254627</v>
+        <v>0.3616808404202101</v>
       </c>
       <c r="E26">
-        <v>0.004191114836546521</v>
+        <v>0.003137254901960784</v>
       </c>
       <c r="F26">
-        <v>0.5555555555555556</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1973,19 +1973,19 @@
         <v>31</v>
       </c>
       <c r="B27">
-        <v>0.4946570493555066</v>
+        <v>0.4889801642957323</v>
       </c>
       <c r="C27">
-        <v>0.04736440030557677</v>
+        <v>0.04177215189873418</v>
       </c>
       <c r="D27">
-        <v>0.3761880940470235</v>
+        <v>0.2426213106553277</v>
       </c>
       <c r="E27">
-        <v>0.02454473475851148</v>
+        <v>0.02151238591916558</v>
       </c>
       <c r="F27">
-        <v>0.6739130434782609</v>
+        <v>0.7173913043478261</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -1993,19 +1993,19 @@
         <v>32</v>
       </c>
       <c r="B28">
-        <v>0.46662637919607</v>
+        <v>0.5817088385512106</v>
       </c>
       <c r="C28">
-        <v>0.02271006813020439</v>
+        <v>0.02668360864040661</v>
       </c>
       <c r="D28">
-        <v>0.3541770885442722</v>
+        <v>0.2336168084042021</v>
       </c>
       <c r="E28">
-        <v>0.01158301158301158</v>
+        <v>0.01356589147286822</v>
       </c>
       <c r="F28">
-        <v>0.5769230769230769</v>
+        <v>0.8076923076923077</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -2013,16 +2013,16 @@
         <v>33</v>
       </c>
       <c r="B29">
-        <v>0.9089089089089089</v>
+        <v>0.7752752752752753</v>
       </c>
       <c r="C29">
-        <v>0.001488095238095238</v>
+        <v>0.001549186676994578</v>
       </c>
       <c r="D29">
-        <v>0.328664332166083</v>
+        <v>0.3551775887943972</v>
       </c>
       <c r="E29">
-        <v>0.0007446016381236039</v>
+        <v>0.0007751937984496124</v>
       </c>
       <c r="F29">
         <v>1</v>
@@ -2033,19 +2033,19 @@
         <v>34</v>
       </c>
       <c r="B30">
-        <v>0.4778757888697648</v>
+        <v>0.3914228341939185</v>
       </c>
       <c r="C30">
-        <v>0.006896551724137931</v>
+        <v>0.005372733378106112</v>
       </c>
       <c r="D30">
-        <v>0.279639819909955</v>
+        <v>0.2591295647823912</v>
       </c>
       <c r="E30">
-        <v>0.003465003465003465</v>
+        <v>0.002699055330634278</v>
       </c>
       <c r="F30">
-        <v>0.7142857142857143</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -2053,16 +2053,16 @@
         <v>35</v>
       </c>
       <c r="B31">
-        <v>0.4634634634634635</v>
+        <v>0.6266266266266266</v>
       </c>
       <c r="C31">
-        <v>0.001506024096385542</v>
+        <v>0.001286173633440514</v>
       </c>
       <c r="D31">
-        <v>0.3366683341670835</v>
+        <v>0.2231115557778889</v>
       </c>
       <c r="E31">
-        <v>0.0007535795026375283</v>
+        <v>0.0006435006435006435</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -2073,16 +2073,16 @@
         <v>36</v>
       </c>
       <c r="B32">
-        <v>0.6310120240480962</v>
+        <v>0.4697728790915164</v>
       </c>
       <c r="C32">
-        <v>0.004078857919782461</v>
+        <v>0.004016064257028112</v>
       </c>
       <c r="D32">
-        <v>0.2671335667833917</v>
+        <v>0.2556278139069535</v>
       </c>
       <c r="E32">
-        <v>0.002043596730245231</v>
+        <v>0.002012072434607646</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -2093,13 +2093,13 @@
         <v>37</v>
       </c>
       <c r="B33">
-        <v>0.0503003003003003</v>
+        <v>0.1178678678678678</v>
       </c>
       <c r="C33">
         <v>0</v>
       </c>
       <c r="D33">
-        <v>0.2786393196598299</v>
+        <v>0.279639819909955</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2113,16 +2113,16 @@
         <v>38</v>
       </c>
       <c r="B34">
-        <v>0.4702202202202203</v>
+        <v>0.8891391391391391</v>
       </c>
       <c r="C34">
-        <v>0.001509433962264151</v>
+        <v>0.00128783000643915</v>
       </c>
       <c r="D34">
-        <v>0.3381690845422711</v>
+        <v>0.224112056028014</v>
       </c>
       <c r="E34">
-        <v>0.0007552870090634441</v>
+        <v>0.0006443298969072165</v>
       </c>
       <c r="F34">
         <v>1</v>
@@ -2133,19 +2133,19 @@
         <v>39</v>
       </c>
       <c r="B35">
-        <v>0.3995023088763469</v>
+        <v>0.4590661877886095</v>
       </c>
       <c r="C35">
-        <v>0.04055032585083273</v>
+        <v>0.05003207184092367</v>
       </c>
       <c r="D35">
-        <v>0.3371685842921461</v>
+        <v>0.2591295647823912</v>
       </c>
       <c r="E35">
-        <v>0.02103681442524418</v>
+        <v>0.02584493041749503</v>
       </c>
       <c r="F35">
-        <v>0.5600000000000001</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -2153,19 +2153,19 @@
         <v>40</v>
       </c>
       <c r="B36">
-        <v>0.2604846810647916</v>
+        <v>0.3768520843797087</v>
       </c>
       <c r="C36">
-        <v>0.004338394793926247</v>
+        <v>0.007366482504604052</v>
       </c>
       <c r="D36">
-        <v>0.3111555777888945</v>
+        <v>0.1910955477738869</v>
       </c>
       <c r="E36">
-        <v>0.002181818181818182</v>
+        <v>0.003701418877236274</v>
       </c>
       <c r="F36">
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -2173,19 +2173,19 @@
         <v>41</v>
       </c>
       <c r="B37">
-        <v>0.2064564564564565</v>
+        <v>0.3440940940940941</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>0.001267427122940431</v>
       </c>
       <c r="D37">
-        <v>0.2741370685342671</v>
+        <v>0.2116058029014507</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>0.0006341154090044388</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -2193,16 +2193,16 @@
         <v>42</v>
       </c>
       <c r="B38">
-        <v>0.6759398496240602</v>
+        <v>0.7648496240601503</v>
       </c>
       <c r="C38">
-        <v>0.006010518407212622</v>
+        <v>0.005387205387205387</v>
       </c>
       <c r="D38">
-        <v>0.3381690845422711</v>
+        <v>0.2611305652826413</v>
       </c>
       <c r="E38">
-        <v>0.003014318010550113</v>
+        <v>0.002700877785280216</v>
       </c>
       <c r="F38">
         <v>1</v>
@@ -2213,16 +2213,16 @@
         <v>43</v>
       </c>
       <c r="B39">
-        <v>0.3947368421052632</v>
+        <v>0.2399122807017544</v>
       </c>
       <c r="C39">
-        <v>0.003000750187546887</v>
+        <v>0.002479851208927464</v>
       </c>
       <c r="D39">
-        <v>0.3351675837918959</v>
+        <v>0.1950975487743872</v>
       </c>
       <c r="E39">
-        <v>0.001504890895410083</v>
+        <v>0.001243008079552517</v>
       </c>
       <c r="F39">
         <v>0.5</v>
@@ -2233,19 +2233,19 @@
         <v>44</v>
       </c>
       <c r="B40">
-        <v>0.6159638554216866</v>
+        <v>0.7607214572576018</v>
       </c>
       <c r="C40">
-        <v>0.006915629322268326</v>
+        <v>0.008432888264230498</v>
       </c>
       <c r="D40">
-        <v>0.2816408204102051</v>
+        <v>0.2941470735367684</v>
       </c>
       <c r="E40">
-        <v>0.003474635163307853</v>
+        <v>0.00423728813559322</v>
       </c>
       <c r="F40">
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -2253,19 +2253,19 @@
         <v>45</v>
       </c>
       <c r="B41">
-        <v>0.4304304304304304</v>
+        <v>0.1263763763763764</v>
       </c>
       <c r="C41">
-        <v>0.001467351430667645</v>
+        <v>0</v>
       </c>
       <c r="D41">
-        <v>0.319159579789895</v>
+        <v>0.2726363181590795</v>
       </c>
       <c r="E41">
-        <v>0.0007342143906020558</v>
+        <v>0</v>
       </c>
       <c r="F41">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -2273,16 +2273,16 @@
         <v>46</v>
       </c>
       <c r="B42">
-        <v>0.781813627254509</v>
+        <v>0.7374749498997996</v>
       </c>
       <c r="C42">
-        <v>0.004329004329004329</v>
+        <v>0.004234297812279464</v>
       </c>
       <c r="D42">
-        <v>0.3096548274137069</v>
+        <v>0.2941470735367684</v>
       </c>
       <c r="E42">
-        <v>0.002169197396963124</v>
+        <v>0.002121640735502122</v>
       </c>
       <c r="F42">
         <v>1</v>
@@ -2293,19 +2293,19 @@
         <v>47</v>
       </c>
       <c r="B43">
-        <v>0.6549648946840522</v>
+        <v>0.6689067201604815</v>
       </c>
       <c r="C43">
-        <v>0.005886681383370125</v>
+        <v>0.007320644216691069</v>
       </c>
       <c r="D43">
-        <v>0.3241620810405202</v>
+        <v>0.3216608304152076</v>
       </c>
       <c r="E43">
-        <v>0.002954209748892172</v>
+        <v>0.003673769287288758</v>
       </c>
       <c r="F43">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -2313,16 +2313,16 @@
         <v>48</v>
       </c>
       <c r="B44">
-        <v>0.7407407407407407</v>
+        <v>0.9224224224224224</v>
       </c>
       <c r="C44">
-        <v>0.001474926253687316</v>
+        <v>0.001373626373626374</v>
       </c>
       <c r="D44">
-        <v>0.3226613306653326</v>
+        <v>0.2726363181590795</v>
       </c>
       <c r="E44">
-        <v>0.0007380073800738007</v>
+        <v>0.0006872852233676976</v>
       </c>
       <c r="F44">
         <v>1</v>
@@ -2333,16 +2333,16 @@
         <v>49</v>
       </c>
       <c r="B45">
-        <v>0.4296796796796797</v>
+        <v>0.6051051051051051</v>
       </c>
       <c r="C45">
-        <v>0.001431639226914817</v>
+        <v>0.00128122998078155</v>
       </c>
       <c r="D45">
-        <v>0.3021510755377689</v>
+        <v>0.2201100550275138</v>
       </c>
       <c r="E45">
-        <v>0.0007163323782234957</v>
+        <v>0.000641025641025641</v>
       </c>
       <c r="F45">
         <v>1</v>
@@ -2353,16 +2353,16 @@
         <v>50</v>
       </c>
       <c r="B46">
-        <v>0.6493910095429433</v>
+        <v>0.7009354595680563</v>
       </c>
       <c r="C46">
-        <v>0.01017811704834606</v>
+        <v>0.009592326139088728</v>
       </c>
       <c r="D46">
-        <v>0.2216108054027013</v>
+        <v>0.1735867933966984</v>
       </c>
       <c r="E46">
-        <v>0.005115089514066497</v>
+        <v>0.004819277108433735</v>
       </c>
       <c r="F46">
         <v>1</v>
@@ -2373,19 +2373,19 @@
         <v>51</v>
       </c>
       <c r="B47">
-        <v>0.6386094895973657</v>
+        <v>0.7022975602454723</v>
       </c>
       <c r="C47">
-        <v>0.04075895994378075</v>
+        <v>0.04094689699296225</v>
       </c>
       <c r="D47">
-        <v>0.3171585792896448</v>
+        <v>0.2501250625312657</v>
       </c>
       <c r="E47">
-        <v>0.02087832973362131</v>
+        <v>0.02092871157619359</v>
       </c>
       <c r="F47">
-        <v>0.8529411764705882</v>
+        <v>0.9411764705882353</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -2393,19 +2393,19 @@
         <v>52</v>
       </c>
       <c r="B48">
-        <v>0.1984335839598997</v>
+        <v>0.04718045112781957</v>
       </c>
       <c r="C48">
-        <v>0.001434720229555237</v>
+        <v>0</v>
       </c>
       <c r="D48">
-        <v>0.3036518259129565</v>
+        <v>0.2631315657828914</v>
       </c>
       <c r="E48">
-        <v>0.0007194244604316547</v>
+        <v>0</v>
       </c>
       <c r="F48">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -2413,19 +2413,19 @@
         <v>53</v>
       </c>
       <c r="B49">
-        <v>0.4282967725668179</v>
+        <v>0.3968891830559758</v>
       </c>
       <c r="C49">
-        <v>0.01526717557251908</v>
+        <v>0.0150281778334377</v>
       </c>
       <c r="D49">
-        <v>0.3546773386693347</v>
+        <v>0.2131065532766383</v>
       </c>
       <c r="E49">
-        <v>0.007727975270479135</v>
+        <v>0.007590132827324478</v>
       </c>
       <c r="F49">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -2433,19 +2433,19 @@
         <v>54</v>
       </c>
       <c r="B50">
-        <v>0.4343029087261785</v>
+        <v>0.5583751253761284</v>
       </c>
       <c r="C50">
-        <v>0.004344677769732078</v>
+        <v>0.006150061500615006</v>
       </c>
       <c r="D50">
-        <v>0.3121560780390195</v>
+        <v>0.1915957978989495</v>
       </c>
       <c r="E50">
-        <v>0.002180232558139535</v>
+        <v>0.003084515731030228</v>
       </c>
       <c r="F50">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -2453,19 +2453,19 @@
         <v>55</v>
       </c>
       <c r="B51">
-        <v>0.6269404106159239</v>
+        <v>0.5559589384076113</v>
       </c>
       <c r="C51">
-        <v>0.002949852507374631</v>
+        <v>0.00130890052356021</v>
       </c>
       <c r="D51">
-        <v>0.3236618309154577</v>
+        <v>0.2366183091545773</v>
       </c>
       <c r="E51">
-        <v>0.001477104874446086</v>
+        <v>0.000655307994757536</v>
       </c>
       <c r="F51">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -2473,19 +2473,19 @@
         <v>56</v>
       </c>
       <c r="B52">
-        <v>0.4643175735950045</v>
+        <v>0.5006262446048352</v>
       </c>
       <c r="C52">
-        <v>0.1052631578947368</v>
+        <v>0.1051912568306011</v>
       </c>
       <c r="D52">
-        <v>0.3196598299149575</v>
+        <v>0.344672336168084</v>
       </c>
       <c r="E52">
-        <v>0.05706134094151213</v>
+        <v>0.05720653789004457</v>
       </c>
       <c r="F52">
-        <v>0.6779661016949152</v>
+        <v>0.652542372881356</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -2493,16 +2493,16 @@
         <v>57</v>
       </c>
       <c r="B53">
-        <v>0.7818136272545091</v>
+        <v>0.6420340681362725</v>
       </c>
       <c r="C53">
-        <v>0.004576659038901602</v>
+        <v>0.003778337531486146</v>
       </c>
       <c r="D53">
-        <v>0.3471735867933967</v>
+        <v>0.2086043021510755</v>
       </c>
       <c r="E53">
-        <v>0.002293577981651376</v>
+        <v>0.001892744479495268</v>
       </c>
       <c r="F53">
         <v>1</v>
@@ -2513,19 +2513,19 @@
         <v>58</v>
       </c>
       <c r="B54">
-        <v>0.3406393568147013</v>
+        <v>0.4116258295048494</v>
       </c>
       <c r="C54">
-        <v>0.02771699489423778</v>
+        <v>0.03268945022288262</v>
       </c>
       <c r="D54">
-        <v>0.3331665832916458</v>
+        <v>0.3486743371685843</v>
       </c>
       <c r="E54">
-        <v>0.01427498121712998</v>
+        <v>0.01684532924961715</v>
       </c>
       <c r="F54">
-        <v>0.475</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -2533,19 +2533,19 @@
         <v>59</v>
       </c>
       <c r="B55">
-        <v>0.7745024251547082</v>
+        <v>0.7471985281819702</v>
       </c>
       <c r="C55">
-        <v>0.007407407407407408</v>
+        <v>0.007920792079207921</v>
       </c>
       <c r="D55">
-        <v>0.3296648324162081</v>
+        <v>0.2481240620310155</v>
       </c>
       <c r="E55">
-        <v>0.003720238095238095</v>
+        <v>0.003976143141153081</v>
       </c>
       <c r="F55">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -2553,16 +2553,16 @@
         <v>60</v>
       </c>
       <c r="B56">
-        <v>0.7375626880641926</v>
+        <v>0.7615847542627884</v>
       </c>
       <c r="C56">
-        <v>0.007097232079488999</v>
+        <v>0.006925207756232687</v>
       </c>
       <c r="D56">
-        <v>0.3001500750375188</v>
+        <v>0.2826413206603302</v>
       </c>
       <c r="E56">
-        <v>0.003561253561253561</v>
+        <v>0.003474635163307853</v>
       </c>
       <c r="F56">
         <v>1</v>
@@ -2573,19 +2573,19 @@
         <v>61</v>
       </c>
       <c r="B57">
-        <v>0.6460300288486756</v>
+        <v>0.7109149619722004</v>
       </c>
       <c r="C57">
-        <v>0.0360128617363344</v>
+        <v>0.03423848878394333</v>
       </c>
       <c r="D57">
-        <v>0.2501250625312657</v>
+        <v>0.1815907953976988</v>
       </c>
       <c r="E57">
-        <v>0.01837270341207349</v>
+        <v>0.0174383644016837</v>
       </c>
       <c r="F57">
-        <v>0.9032258064516129</v>
+        <v>0.9354838709677419</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -2593,19 +2593,19 @@
         <v>62</v>
       </c>
       <c r="B58">
-        <v>0.6615747830525779</v>
+        <v>0.5854581419091374</v>
       </c>
       <c r="C58">
-        <v>0.05035506778566817</v>
+        <v>0.04642166344294004</v>
       </c>
       <c r="D58">
-        <v>0.2641320660330165</v>
+        <v>0.2601300650325162</v>
       </c>
       <c r="E58">
-        <v>0.02584493041749503</v>
+        <v>0.02382528127068167</v>
       </c>
       <c r="F58">
-        <v>0.975</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -2613,16 +2613,16 @@
         <v>63</v>
       </c>
       <c r="B59">
-        <v>0.8200563860477313</v>
+        <v>0.8001163781799109</v>
       </c>
       <c r="C59">
-        <v>0.04350978970268311</v>
+        <v>0.03764115432873275</v>
       </c>
       <c r="D59">
-        <v>0.3401700850425213</v>
+        <v>0.2326163081540771</v>
       </c>
       <c r="E59">
-        <v>0.02225519287833828</v>
+        <v>0.01919385796545105</v>
       </c>
       <c r="F59">
         <v>0.967741935483871</v>
@@ -2633,19 +2633,19 @@
         <v>64</v>
       </c>
       <c r="B60">
-        <v>0.7583963365910629</v>
+        <v>0.7719282070194848</v>
       </c>
       <c r="C60">
-        <v>0.1061337008959338</v>
+        <v>0.09564164648910412</v>
       </c>
       <c r="D60">
-        <v>0.351175587793897</v>
+        <v>0.2526263131565783</v>
       </c>
       <c r="E60">
-        <v>0.05636896046852123</v>
+        <v>0.05041480536056158</v>
       </c>
       <c r="F60">
-        <v>0.9058823529411765</v>
+        <v>0.9294117647058824</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -2653,19 +2653,19 @@
         <v>65</v>
       </c>
       <c r="B61">
-        <v>0.6516545323363505</v>
+        <v>0.6630345664436573</v>
       </c>
       <c r="C61">
-        <v>0.0776978417266187</v>
+        <v>0.07462686567164178</v>
       </c>
       <c r="D61">
-        <v>0.3586793396698349</v>
+        <v>0.2556278139069535</v>
       </c>
       <c r="E61">
-        <v>0.04069329314242653</v>
+        <v>0.03883495145631068</v>
       </c>
       <c r="F61">
-        <v>0.8571428571428571</v>
+        <v>0.9523809523809523</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -2673,19 +2673,19 @@
         <v>66</v>
       </c>
       <c r="B62">
-        <v>0.7676637037733779</v>
+        <v>0.7852059132452304</v>
       </c>
       <c r="C62">
-        <v>0.08384043272481406</v>
+        <v>0.07687687687687687</v>
       </c>
       <c r="D62">
-        <v>0.3221610805402702</v>
+        <v>0.2311155577788895</v>
       </c>
       <c r="E62">
-        <v>0.04387827317763623</v>
+        <v>0.04002501563477173</v>
       </c>
       <c r="F62">
-        <v>0.9393939393939394</v>
+        <v>0.9696969696969697</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -2693,19 +2693,19 @@
         <v>67</v>
       </c>
       <c r="B63">
-        <v>0.4764336372847011</v>
+        <v>0.4885106382978723</v>
       </c>
       <c r="C63">
-        <v>0.02724014336917563</v>
+        <v>0.02278481012658228</v>
       </c>
       <c r="D63">
-        <v>0.321160580290145</v>
+        <v>0.2276138069034517</v>
       </c>
       <c r="E63">
-        <v>0.01386861313868613</v>
+        <v>0.01157556270096463</v>
       </c>
       <c r="F63">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -2713,19 +2713,19 @@
         <v>68</v>
       </c>
       <c r="B64">
-        <v>0.4211589580010633</v>
+        <v>0.4103801169590643</v>
       </c>
       <c r="C64">
-        <v>0.01613987895090787</v>
+        <v>0.01671641791044776</v>
       </c>
       <c r="D64">
-        <v>0.2681340670335168</v>
+        <v>0.176088044022011</v>
       </c>
       <c r="E64">
-        <v>0.008174386920980926</v>
+        <v>0.008454106280193236</v>
       </c>
       <c r="F64">
-        <v>0.631578947368421</v>
+        <v>0.7368421052631579</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -2733,19 +2733,19 @@
         <v>69</v>
       </c>
       <c r="B65">
-        <v>0.683647428347075</v>
+        <v>0.6625722138089629</v>
       </c>
       <c r="C65">
-        <v>0.02153625269203159</v>
+        <v>0.02033492822966507</v>
       </c>
       <c r="D65">
-        <v>0.3181590795397699</v>
+        <v>0.1805902951475738</v>
       </c>
       <c r="E65">
-        <v>0.01090909090909091</v>
+        <v>0.01027811366384522</v>
       </c>
       <c r="F65">
-        <v>0.8333333333333334</v>
+        <v>0.9444444444444444</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -2753,19 +2753,19 @@
         <v>70</v>
       </c>
       <c r="B66">
-        <v>0.799153496804439</v>
+        <v>0.7562835350779205</v>
       </c>
       <c r="C66">
-        <v>0.1473414477898783</v>
+        <v>0.1326228537596211</v>
       </c>
       <c r="D66">
-        <v>0.3341670835417709</v>
+        <v>0.2671335667833917</v>
       </c>
       <c r="E66">
-        <v>0.07958477508650519</v>
+        <v>0.0712015257469803</v>
       </c>
       <c r="F66">
-        <v>0.9913793103448276</v>
+        <v>0.9655172413793104</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -2773,16 +2773,16 @@
         <v>71</v>
       </c>
       <c r="B67">
-        <v>0.849197592778335</v>
+        <v>0.7655967903711134</v>
       </c>
       <c r="C67">
-        <v>0.007102272727272727</v>
+        <v>0.006180469715698393</v>
       </c>
       <c r="D67">
-        <v>0.3006503251625813</v>
+        <v>0.1955977988994497</v>
       </c>
       <c r="E67">
-        <v>0.003563791874554526</v>
+        <v>0.003099814011159331</v>
       </c>
       <c r="F67">
         <v>1</v>
@@ -2793,16 +2793,16 @@
         <v>72</v>
       </c>
       <c r="B68">
-        <v>0.765529112408322</v>
+        <v>0.7544978296662177</v>
       </c>
       <c r="C68">
-        <v>0.04548494983277592</v>
+        <v>0.04069419509275882</v>
       </c>
       <c r="D68">
-        <v>0.2861430715357679</v>
+        <v>0.1980990495247624</v>
       </c>
       <c r="E68">
-        <v>0.02327173169062286</v>
+        <v>0.02076970067196091</v>
       </c>
       <c r="F68">
         <v>1</v>
@@ -2813,16 +2813,16 @@
         <v>73</v>
       </c>
       <c r="B69">
-        <v>0.7943504857862541</v>
+        <v>0.8034005037783375</v>
       </c>
       <c r="C69">
-        <v>0.01909959072305593</v>
+        <v>0.01768793430195831</v>
       </c>
       <c r="D69">
-        <v>0.2806403201600801</v>
+        <v>0.2221110555277639</v>
       </c>
       <c r="E69">
-        <v>0.009641873278236915</v>
+        <v>0.008922880815806247</v>
       </c>
       <c r="F69">
         <v>1</v>
@@ -2833,16 +2833,16 @@
         <v>74</v>
       </c>
       <c r="B70">
-        <v>0.7653038767563908</v>
+        <v>0.7413915693245302</v>
       </c>
       <c r="C70">
-        <v>0.03846153846153846</v>
+        <v>0.03661616161616162</v>
       </c>
       <c r="D70">
-        <v>0.2746373186593297</v>
+        <v>0.2366183091545773</v>
       </c>
       <c r="E70">
-        <v>0.01962110960757781</v>
+        <v>0.01866151866151866</v>
       </c>
       <c r="F70">
         <v>0.9666666666666667</v>
@@ -2853,19 +2853,19 @@
         <v>75</v>
       </c>
       <c r="B71">
-        <v>0.7758435067757101</v>
+        <v>0.7582671565722413</v>
       </c>
       <c r="C71">
-        <v>0.06581598388179986</v>
+        <v>0.06246172688303735</v>
       </c>
       <c r="D71">
-        <v>0.304152076038019</v>
+        <v>0.2341170585292646</v>
       </c>
       <c r="E71">
-        <v>0.03409881697981907</v>
+        <v>0.03225806451612903</v>
       </c>
       <c r="F71">
-        <v>0.9423076923076923</v>
+        <v>0.9807692307692307</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -2873,16 +2873,16 @@
         <v>76</v>
       </c>
       <c r="B72">
-        <v>0.6949849548645938</v>
+        <v>0.7211133400200602</v>
       </c>
       <c r="C72">
-        <v>0.006839945280437756</v>
+        <v>0.006901311249137336</v>
       </c>
       <c r="D72">
-        <v>0.2736368184092046</v>
+        <v>0.2801400700350175</v>
       </c>
       <c r="E72">
-        <v>0.003431708991077557</v>
+        <v>0.003462603878116343</v>
       </c>
       <c r="F72">
         <v>1</v>
@@ -2893,19 +2893,19 @@
         <v>77</v>
       </c>
       <c r="B73">
-        <v>0.7911656646626586</v>
+        <v>0.6929692718770875</v>
       </c>
       <c r="C73">
-        <v>0.004366812227074236</v>
+        <v>0.002808988764044944</v>
       </c>
       <c r="D73">
-        <v>0.3156578289144572</v>
+        <v>0.2896448224112056</v>
       </c>
       <c r="E73">
-        <v>0.002188183807439825</v>
+        <v>0.001407459535538353</v>
       </c>
       <c r="F73">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -2913,19 +2913,19 @@
         <v>78</v>
       </c>
       <c r="B74">
-        <v>0.4491214266981379</v>
+        <v>0.4136014948859166</v>
       </c>
       <c r="C74">
-        <v>0.02597402597402598</v>
+        <v>0.02663115845539281</v>
       </c>
       <c r="D74">
-        <v>0.3621810905452726</v>
+        <v>0.2686343171585793</v>
       </c>
       <c r="E74">
-        <v>0.01330203442879499</v>
+        <v>0.01359619306594154</v>
       </c>
       <c r="F74">
-        <v>0.5483870967741935</v>
+        <v>0.6451612903225806</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -2933,19 +2933,19 @@
         <v>79</v>
       </c>
       <c r="B75">
-        <v>0.4478283131859569</v>
+        <v>0.4921080166521961</v>
       </c>
       <c r="C75">
-        <v>0.04324324324324325</v>
+        <v>0.04474002418379686</v>
       </c>
       <c r="D75">
-        <v>0.3801900950475238</v>
+        <v>0.2096048024012006</v>
       </c>
       <c r="E75">
-        <v>0.02241793434747798</v>
+        <v>0.02300995024875622</v>
       </c>
       <c r="F75">
-        <v>0.6086956521739131</v>
+        <v>0.8043478260869565</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -2953,19 +2953,19 @@
         <v>80</v>
       </c>
       <c r="B76">
-        <v>0.469852487520332</v>
+        <v>0.3998962364686747</v>
       </c>
       <c r="C76">
-        <v>0.0167046317388003</v>
+        <v>0.01563517915309446</v>
       </c>
       <c r="D76">
-        <v>0.352176088044022</v>
+        <v>0.2441220610305153</v>
       </c>
       <c r="E76">
-        <v>0.008468052347959968</v>
+        <v>0.007910349373764008</v>
       </c>
       <c r="F76">
-        <v>0.6111111111111112</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -2973,16 +2973,16 @@
         <v>81</v>
       </c>
       <c r="B77">
-        <v>0.6477939942962591</v>
+        <v>0.5711080355645026</v>
       </c>
       <c r="C77">
-        <v>0.01554001554001554</v>
+        <v>0.0128122998078155</v>
       </c>
       <c r="D77">
-        <v>0.3661830915457729</v>
+        <v>0.2291145572786393</v>
       </c>
       <c r="E77">
-        <v>0.007843137254901961</v>
+        <v>0.006455777921239509</v>
       </c>
       <c r="F77">
         <v>0.8333333333333334</v>
@@ -2993,19 +2993,19 @@
         <v>82</v>
       </c>
       <c r="B78">
-        <v>0.4554663991975927</v>
+        <v>0.449197592778335</v>
       </c>
       <c r="C78">
-        <v>0.005835156819839533</v>
+        <v>0.00411240575736806</v>
       </c>
       <c r="D78">
-        <v>0.3181590795397699</v>
+        <v>0.2731365682841421</v>
       </c>
       <c r="E78">
-        <v>0.002928257686676428</v>
+        <v>0.002063273727647868</v>
       </c>
       <c r="F78">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -3013,19 +3013,19 @@
         <v>83</v>
       </c>
       <c r="B79">
-        <v>0.4082242417158553</v>
+        <v>0.4643102390275262</v>
       </c>
       <c r="C79">
-        <v>0.05596269153897402</v>
+        <v>0.06053119209388511</v>
       </c>
       <c r="D79">
-        <v>0.2911455727863932</v>
+        <v>0.2391195597798899</v>
       </c>
       <c r="E79">
-        <v>0.02937062937062937</v>
+        <v>0.03165374677002584</v>
       </c>
       <c r="F79">
-        <v>0.5915492957746479</v>
+        <v>0.6901408450704225</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -3033,16 +3033,16 @@
         <v>84</v>
       </c>
       <c r="B80">
-        <v>0.6735658136812176</v>
+        <v>0.7088141829737413</v>
       </c>
       <c r="C80">
-        <v>0.008135593220338983</v>
+        <v>0.007672634271099744</v>
       </c>
       <c r="D80">
-        <v>0.2681340670335168</v>
+        <v>0.2236118059029515</v>
       </c>
       <c r="E80">
-        <v>0.004084411164057181</v>
+        <v>0.003851091142490372</v>
       </c>
       <c r="F80">
         <v>1</v>
@@ -3053,16 +3053,16 @@
         <v>85</v>
       </c>
       <c r="B81">
-        <v>0.645142378559464</v>
+        <v>0.7848408710217756</v>
       </c>
       <c r="C81">
-        <v>0.01222826086956522</v>
+        <v>0.01100917431192661</v>
       </c>
       <c r="D81">
-        <v>0.2726363181590795</v>
+        <v>0.1910955477738869</v>
       </c>
       <c r="E81">
-        <v>0.006151742993848257</v>
+        <v>0.005535055350553505</v>
       </c>
       <c r="F81">
         <v>1</v>
@@ -3073,16 +3073,16 @@
         <v>86</v>
       </c>
       <c r="B82">
-        <v>0.677423981640849</v>
+        <v>0.7154331612162937</v>
       </c>
       <c r="C82">
-        <v>0.01015228426395939</v>
+        <v>0.009003215434083601</v>
       </c>
       <c r="D82">
-        <v>0.3171585792896448</v>
+        <v>0.2291145572786393</v>
       </c>
       <c r="E82">
-        <v>0.00510204081632653</v>
+        <v>0.004521963824289405</v>
       </c>
       <c r="F82">
         <v>1</v>
@@ -3093,16 +3093,16 @@
         <v>87</v>
       </c>
       <c r="B83">
-        <v>0.6537937464142284</v>
+        <v>0.828886976477338</v>
       </c>
       <c r="C83">
-        <v>0.009543285616905249</v>
+        <v>0.00865265760197775</v>
       </c>
       <c r="D83">
-        <v>0.2731365682841421</v>
+        <v>0.1975987993996998</v>
       </c>
       <c r="E83">
-        <v>0.004794520547945206</v>
+        <v>0.004345127250155183</v>
       </c>
       <c r="F83">
         <v>1</v>
@@ -3113,16 +3113,16 @@
         <v>88</v>
       </c>
       <c r="B84">
-        <v>0.7171045982819605</v>
+        <v>0.7446816574027285</v>
       </c>
       <c r="C84">
-        <v>0.02478799739073712</v>
+        <v>0.02335586969883221</v>
       </c>
       <c r="D84">
-        <v>0.2521260630315157</v>
+        <v>0.2051025512756378</v>
       </c>
       <c r="E84">
-        <v>0.01255783212161269</v>
+        <v>0.01182327317983821</v>
       </c>
       <c r="F84">
         <v>0.95</v>
@@ -3133,19 +3133,19 @@
         <v>89</v>
       </c>
       <c r="B85">
-        <v>0.6933804951995958</v>
+        <v>0.7379231935320869</v>
       </c>
       <c r="C85">
-        <v>0.02450646698434309</v>
+        <v>0.02454780361757106</v>
       </c>
       <c r="D85">
-        <v>0.2831415707853927</v>
+        <v>0.2446223111555778</v>
       </c>
       <c r="E85">
-        <v>0.0124223602484472</v>
+        <v>0.01243455497382199</v>
       </c>
       <c r="F85">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -3153,19 +3153,19 @@
         <v>90</v>
       </c>
       <c r="B86">
-        <v>0.5977620730270907</v>
+        <v>0.6593611531774075</v>
       </c>
       <c r="C86">
-        <v>0.02092050209205021</v>
+        <v>0.02370990237099024</v>
       </c>
       <c r="D86">
-        <v>0.2976488244122061</v>
+        <v>0.2996498249124562</v>
       </c>
       <c r="E86">
-        <v>0.01059322033898305</v>
+        <v>0.01200564971751412</v>
       </c>
       <c r="F86">
-        <v>0.8333333333333334</v>
+        <v>0.9444444444444444</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -3173,19 +3173,19 @@
         <v>91</v>
       </c>
       <c r="B87">
-        <v>0.4054317478682999</v>
+        <v>0.495249264280504</v>
       </c>
       <c r="C87">
-        <v>0.06623470122390208</v>
+        <v>0.07138221933809215</v>
       </c>
       <c r="D87">
-        <v>0.351175587793897</v>
+        <v>0.2841420710355178</v>
       </c>
       <c r="E87">
-        <v>0.03522205206738132</v>
+        <v>0.03772290809327846</v>
       </c>
       <c r="F87">
-        <v>0.5542168674698795</v>
+        <v>0.6626506024096386</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -3193,19 +3193,19 @@
         <v>92</v>
       </c>
       <c r="B88">
-        <v>0.4614271938283511</v>
+        <v>0.5159366593919708</v>
       </c>
       <c r="C88">
-        <v>0.04916732751784298</v>
+        <v>0.05661619486504279</v>
       </c>
       <c r="D88">
-        <v>0.400200100050025</v>
+        <v>0.2831415707853927</v>
       </c>
       <c r="E88">
-        <v>0.02583333333333333</v>
+        <v>0.02949245541838134</v>
       </c>
       <c r="F88">
-        <v>0.5081967213114754</v>
+        <v>0.7049180327868853</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -3213,19 +3213,19 @@
         <v>93</v>
       </c>
       <c r="B89">
-        <v>0.3706839915322286</v>
+        <v>0.3771686497797893</v>
       </c>
       <c r="C89">
-        <v>0.02681388012618297</v>
+        <v>0.02872062663185379</v>
       </c>
       <c r="D89">
-        <v>0.3826913456728364</v>
+        <v>0.2556278139069535</v>
       </c>
       <c r="E89">
-        <v>0.01386623164763458</v>
+        <v>0.01476510067114094</v>
       </c>
       <c r="F89">
-        <v>0.4047619047619048</v>
+        <v>0.5238095238095238</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -3233,19 +3233,19 @@
         <v>94</v>
       </c>
       <c r="B90">
-        <v>0.3148891646592209</v>
+        <v>0.4942331557047959</v>
       </c>
       <c r="C90">
-        <v>0.02214022140221402</v>
+        <v>0.03896103896103896</v>
       </c>
       <c r="D90">
-        <v>0.3371685842921461</v>
+        <v>0.2596298149074537</v>
       </c>
       <c r="E90">
-        <v>0.01142421934501143</v>
+        <v>0.02002670226969292</v>
       </c>
       <c r="F90">
-        <v>0.3571428571428572</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -3253,16 +3253,16 @@
         <v>95</v>
       </c>
       <c r="B91">
-        <v>0.3691191191191192</v>
+        <v>0.8898898898898899</v>
       </c>
       <c r="C91">
-        <v>0.00132890365448505</v>
+        <v>0.001212121212121212</v>
       </c>
       <c r="D91">
-        <v>0.2481240620310155</v>
+        <v>0.1755877938969485</v>
       </c>
       <c r="E91">
-        <v>0.0006648936170212766</v>
+        <v>0.0006064281382656155</v>
       </c>
       <c r="F91">
         <v>1</v>
@@ -3273,19 +3273,19 @@
         <v>96</v>
       </c>
       <c r="B92">
-        <v>0.2950480040424456</v>
+        <v>0.4675720060636686</v>
       </c>
       <c r="C92">
-        <v>0.009077155824508321</v>
+        <v>0.01704918032786885</v>
       </c>
       <c r="D92">
-        <v>0.344672336168084</v>
+        <v>0.2501250625312657</v>
       </c>
       <c r="E92">
-        <v>0.004608294930875576</v>
+        <v>0.008637873754152824</v>
       </c>
       <c r="F92">
-        <v>0.3</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -3293,19 +3293,19 @@
         <v>97</v>
       </c>
       <c r="B93">
-        <v>0.3087955677943877</v>
+        <v>0.4885178992918962</v>
       </c>
       <c r="C93">
-        <v>0.01663201663201663</v>
+        <v>0.0277602523659306</v>
       </c>
       <c r="D93">
-        <v>0.2901450725362681</v>
+        <v>0.2291145572786393</v>
       </c>
       <c r="E93">
-        <v>0.0084985835694051</v>
+        <v>0.01415701415701416</v>
       </c>
       <c r="F93">
-        <v>0.3870967741935484</v>
+        <v>0.7096774193548387</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -3313,19 +3313,19 @@
         <v>98</v>
       </c>
       <c r="B94">
-        <v>0.2869137646161668</v>
+        <v>0.4395414972038638</v>
       </c>
       <c r="C94">
-        <v>0.01596516690856313</v>
+        <v>0.02772526780088217</v>
       </c>
       <c r="D94">
-        <v>0.3216608304152076</v>
+        <v>0.2281140570285143</v>
       </c>
       <c r="E94">
-        <v>0.008172362555720654</v>
+        <v>0.01414790996784566</v>
       </c>
       <c r="F94">
-        <v>0.34375</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -3333,19 +3333,19 @@
         <v>99</v>
       </c>
       <c r="B95">
-        <v>0.284545686574783</v>
+        <v>0.5391015824400205</v>
       </c>
       <c r="C95">
-        <v>0.01956358164033108</v>
+        <v>0.03810694529809465</v>
       </c>
       <c r="D95">
-        <v>0.3481740870435218</v>
+        <v>0.2171085542771386</v>
       </c>
       <c r="E95">
-        <v>0.01008533747090768</v>
+        <v>0.01953371140516698</v>
       </c>
       <c r="F95">
-        <v>0.325</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -3353,19 +3353,19 @@
         <v>100</v>
       </c>
       <c r="B96">
-        <v>0.3533148241628807</v>
+        <v>0.4290061136350889</v>
       </c>
       <c r="C96">
-        <v>0.01180811808118081</v>
+        <v>0.01611903285802852</v>
       </c>
       <c r="D96">
-        <v>0.3301650825412706</v>
+        <v>0.2061030515257629</v>
       </c>
       <c r="E96">
-        <v>0.005983545250560957</v>
+        <v>0.008150470219435737</v>
       </c>
       <c r="F96">
-        <v>0.4444444444444444</v>
+        <v>0.7222222222222222</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -3373,19 +3373,19 @@
         <v>101</v>
       </c>
       <c r="B97">
-        <v>0.3104388635210553</v>
+        <v>0.4718598245995506</v>
       </c>
       <c r="C97">
-        <v>0.01451612903225807</v>
+        <v>0.02382445141065831</v>
       </c>
       <c r="D97">
-        <v>0.3886943471735868</v>
+        <v>0.2211105552776388</v>
       </c>
       <c r="E97">
-        <v>0.007425742574257425</v>
+        <v>0.01212507977026165</v>
       </c>
       <c r="F97">
-        <v>0.3214285714285715</v>
+        <v>0.6785714285714286</v>
       </c>
     </row>
     <row r="98" spans="1:6">
@@ -3393,19 +3393,19 @@
         <v>102</v>
       </c>
       <c r="B98">
-        <v>0.295620163774322</v>
+        <v>0.4173052362707534</v>
       </c>
       <c r="C98">
-        <v>0.01587301587301587</v>
+        <v>0.01951219512195122</v>
       </c>
       <c r="D98">
-        <v>0.2556278139069535</v>
+        <v>0.1955977988994497</v>
       </c>
       <c r="E98">
-        <v>0.008080808080808081</v>
+        <v>0.009919404835709857</v>
       </c>
       <c r="F98">
-        <v>0.4444444444444444</v>
+        <v>0.5925925925925926</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -3413,19 +3413,19 @@
         <v>103</v>
       </c>
       <c r="B99">
-        <v>0.4310652937672474</v>
+        <v>0.3868604043326566</v>
       </c>
       <c r="C99">
-        <v>0.06906077348066299</v>
+        <v>0.07072463768115941</v>
       </c>
       <c r="D99">
-        <v>0.3256628314157078</v>
+        <v>0.1980990495247624</v>
       </c>
       <c r="E99">
-        <v>0.03671071953010279</v>
+        <v>0.03721781574130567</v>
       </c>
       <c r="F99">
-        <v>0.5813953488372093</v>
+        <v>0.7093023255813954</v>
       </c>
     </row>
     <row r="100" spans="1:6">
@@ -3433,16 +3433,16 @@
         <v>104</v>
       </c>
       <c r="B100">
-        <v>0.5363044566850276</v>
+        <v>0.74949924887331</v>
       </c>
       <c r="C100">
-        <v>0.003319502074688797</v>
+        <v>0.002636783124588002</v>
       </c>
       <c r="D100">
-        <v>0.3991995997998999</v>
+        <v>0.2431215607803902</v>
       </c>
       <c r="E100">
-        <v>0.001662510390689942</v>
+        <v>0.00132013201320132</v>
       </c>
       <c r="F100">
         <v>1</v>
@@ -3453,19 +3453,19 @@
         <v>105</v>
       </c>
       <c r="B101">
-        <v>0.4650232318017553</v>
+        <v>0.4419413126384333</v>
       </c>
       <c r="C101">
-        <v>0.06082036775106082</v>
+        <v>0.0544378698224852</v>
       </c>
       <c r="D101">
-        <v>0.3356678339169585</v>
+        <v>0.200600300150075</v>
       </c>
       <c r="E101">
-        <v>0.03180473372781065</v>
+        <v>0.02825552825552826</v>
       </c>
       <c r="F101">
-        <v>0.6935483870967742</v>
+        <v>0.7419354838709677</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -3473,19 +3473,19 @@
         <v>106</v>
       </c>
       <c r="B102">
-        <v>0.4931020733652313</v>
+        <v>0.48924774056353</v>
       </c>
       <c r="C102">
-        <v>0.0179372197309417</v>
+        <v>0.01748486886348352</v>
       </c>
       <c r="D102">
-        <v>0.3426713356678339</v>
+        <v>0.2691345672836418</v>
       </c>
       <c r="E102">
-        <v>0.009097801364670205</v>
+        <v>0.008855585831062671</v>
       </c>
       <c r="F102">
-        <v>0.631578947368421</v>
+        <v>0.6842105263157895</v>
       </c>
     </row>
     <row r="103" spans="1:6">
@@ -3493,16 +3493,16 @@
         <v>107</v>
       </c>
       <c r="B103">
-        <v>0.6270655983975963</v>
+        <v>0.7382323485227842</v>
       </c>
       <c r="C103">
-        <v>0.00319744204636291</v>
+        <v>0.002688172043010753</v>
       </c>
       <c r="D103">
-        <v>0.3761880940470235</v>
+        <v>0.2576288144072036</v>
       </c>
       <c r="E103">
-        <v>0.001601281024819856</v>
+        <v>0.001345895020188425</v>
       </c>
       <c r="F103">
         <v>1</v>
@@ -3513,19 +3513,19 @@
         <v>108</v>
       </c>
       <c r="B104">
-        <v>0.1493993993993994</v>
+        <v>0.4324324324324325</v>
       </c>
       <c r="C104">
-        <v>0</v>
+        <v>0.001393728222996516</v>
       </c>
       <c r="D104">
-        <v>0.3671835917958979</v>
+        <v>0.2831415707853927</v>
       </c>
       <c r="E104">
-        <v>0</v>
+        <v>0.0006973500697350069</v>
       </c>
       <c r="F104">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -3533,16 +3533,16 @@
         <v>109</v>
       </c>
       <c r="B105">
-        <v>0.5783283283283284</v>
+        <v>0.514014014014014</v>
       </c>
       <c r="C105">
-        <v>0.00175284837861525</v>
+        <v>0.001545595054095827</v>
       </c>
       <c r="D105">
-        <v>0.4302151075537769</v>
+        <v>0.3536768384192096</v>
       </c>
       <c r="E105">
-        <v>0.0008771929824561404</v>
+        <v>0.0007733952049497294</v>
       </c>
       <c r="F105">
         <v>1</v>
@@ -3553,13 +3553,13 @@
         <v>110</v>
       </c>
       <c r="B106">
-        <v>0.1188688688688689</v>
+        <v>0.2047047047047047</v>
       </c>
       <c r="C106">
         <v>0</v>
       </c>
       <c r="D106">
-        <v>0.3206603301650826</v>
+        <v>0.2786393196598299</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -3573,16 +3573,16 @@
         <v>111</v>
       </c>
       <c r="B107">
-        <v>0.4696058784235137</v>
+        <v>0.5581162324649298</v>
       </c>
       <c r="C107">
-        <v>0.003065134099616858</v>
+        <v>0.003259983700081499</v>
       </c>
       <c r="D107">
-        <v>0.3491745872936468</v>
+        <v>0.3881940970485243</v>
       </c>
       <c r="E107">
-        <v>0.001536098310291859</v>
+        <v>0.001633986928104575</v>
       </c>
       <c r="F107">
         <v>0.6666666666666666</v>
@@ -3593,13 +3593,13 @@
         <v>112</v>
       </c>
       <c r="B108">
-        <v>0.0142642642642643</v>
+        <v>0.06431431431431434</v>
       </c>
       <c r="C108">
         <v>0</v>
       </c>
       <c r="D108">
-        <v>0.3311655827913957</v>
+        <v>0.3281640820410205</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -3613,13 +3613,13 @@
         <v>113</v>
       </c>
       <c r="B109">
-        <v>0.08183183183183185</v>
+        <v>0.2364864864864865</v>
       </c>
       <c r="C109">
         <v>0</v>
       </c>
       <c r="D109">
-        <v>0.3341670835417709</v>
+        <v>0.3021510755377689</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -3633,19 +3633,19 @@
         <v>114</v>
       </c>
       <c r="B110">
-        <v>0.5363493571719443</v>
+        <v>0.5602687661191801</v>
       </c>
       <c r="C110">
-        <v>0.05013192612137203</v>
+        <v>0.055286800276434</v>
       </c>
       <c r="D110">
-        <v>0.279639819909955</v>
+        <v>0.3161580790395198</v>
       </c>
       <c r="E110">
-        <v>0.02597402597402598</v>
+        <v>0.02869440459110473</v>
       </c>
       <c r="F110">
-        <v>0.7169811320754716</v>
+        <v>0.7547169811320755</v>
       </c>
     </row>
     <row r="111" spans="1:6">
@@ -3653,13 +3653,13 @@
         <v>115</v>
       </c>
       <c r="B111">
-        <v>0.0558058058058058</v>
+        <v>0.2462462462462462</v>
       </c>
       <c r="C111">
         <v>0</v>
       </c>
       <c r="D111">
-        <v>0.3466733366683342</v>
+        <v>0.3306653326663332</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>116</v>
       </c>
       <c r="B112">
-        <v>0.2264764764764765</v>
+        <v>0.4076576576576577</v>
       </c>
       <c r="C112">
-        <v>0</v>
+        <v>0.00136332651670075</v>
       </c>
       <c r="D112">
-        <v>0.3001500750375188</v>
+        <v>0.2671335667833917</v>
       </c>
       <c r="E112">
-        <v>0</v>
+        <v>0.0006821282401091405</v>
       </c>
       <c r="F112">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -3693,19 +3693,19 @@
         <v>117</v>
       </c>
       <c r="B113">
-        <v>0.5057176561221051</v>
+        <v>0.6021594684385382</v>
       </c>
       <c r="C113">
-        <v>0.02001539645881447</v>
+        <v>0.0265210608424337</v>
       </c>
       <c r="D113">
-        <v>0.3631815907953977</v>
+        <v>0.375687843921961</v>
       </c>
       <c r="E113">
-        <v>0.01017214397496088</v>
+        <v>0.01348136399682792</v>
       </c>
       <c r="F113">
-        <v>0.6190476190476191</v>
+        <v>0.8095238095238095</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -3713,7 +3713,7 @@
         <v>118</v>
       </c>
       <c r="B114">
-        <v>0.1108608608608609</v>
+        <v>0.2192192192192192</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -3733,19 +3733,19 @@
         <v>119</v>
       </c>
       <c r="B115">
-        <v>0.616402449253481</v>
+        <v>0.6771514846502265</v>
       </c>
       <c r="C115">
-        <v>0.01437814521926671</v>
+        <v>0.0145985401459854</v>
       </c>
       <c r="D115">
-        <v>0.3141570785392696</v>
+        <v>0.1895947973986994</v>
       </c>
       <c r="E115">
-        <v>0.007251631617113851</v>
+        <v>0.007352941176470588</v>
       </c>
       <c r="F115">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -3753,16 +3753,16 @@
         <v>120</v>
       </c>
       <c r="B116">
-        <v>0.7394894894894894</v>
+        <v>0.6368868868868869</v>
       </c>
       <c r="C116">
-        <v>0.001497005988023952</v>
+        <v>0.001282873636946761</v>
       </c>
       <c r="D116">
-        <v>0.3326663331665833</v>
+        <v>0.2211105552776388</v>
       </c>
       <c r="E116">
-        <v>0.000749063670411985</v>
+        <v>0.0006418485237483953</v>
       </c>
       <c r="F116">
         <v>1</v>
@@ -3773,16 +3773,16 @@
         <v>121</v>
       </c>
       <c r="B117">
-        <v>0.9331831831831833</v>
+        <v>0.8946446446446447</v>
       </c>
       <c r="C117">
-        <v>0.001434720229555237</v>
+        <v>0.001232285890326556</v>
       </c>
       <c r="D117">
-        <v>0.3036518259129565</v>
+        <v>0.1890945472736368</v>
       </c>
       <c r="E117">
-        <v>0.0007178750897343862</v>
+        <v>0.0006165228113440197</v>
       </c>
       <c r="F117">
         <v>1</v>
@@ -3793,19 +3793,19 @@
         <v>122</v>
       </c>
       <c r="B118">
-        <v>0.6311272428822098</v>
+        <v>0.6090663383709741</v>
       </c>
       <c r="C118">
-        <v>0.03872752420470263</v>
+        <v>0.03936039360393604</v>
       </c>
       <c r="D118">
-        <v>0.3046523261630815</v>
+        <v>0.2186093046523262</v>
       </c>
       <c r="E118">
-        <v>0.0198581560283688</v>
+        <v>0.02012578616352201</v>
       </c>
       <c r="F118">
-        <v>0.7777777777777778</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="119" spans="1:6">
@@ -3813,19 +3813,19 @@
         <v>123</v>
       </c>
       <c r="B119">
-        <v>0.803649237472767</v>
+        <v>0.6757944557133199</v>
       </c>
       <c r="C119">
-        <v>0.03566333808844508</v>
+        <v>0.02844214608920491</v>
       </c>
       <c r="D119">
-        <v>0.3236618309154577</v>
+        <v>0.2481240620310155</v>
       </c>
       <c r="E119">
-        <v>0.01818181818181818</v>
+        <v>0.01447368421052632</v>
       </c>
       <c r="F119">
-        <v>0.9259259259259259</v>
+        <v>0.8148148148148148</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -3833,19 +3833,19 @@
         <v>124</v>
       </c>
       <c r="B120">
-        <v>0.5708532695374801</v>
+        <v>0.5522993088782562</v>
       </c>
       <c r="C120">
-        <v>0.022271714922049</v>
+        <v>0.02256699576868829</v>
       </c>
       <c r="D120">
-        <v>0.3411705852926463</v>
+        <v>0.3066533266633317</v>
       </c>
       <c r="E120">
-        <v>0.01129518072289157</v>
+        <v>0.01143674052894925</v>
       </c>
       <c r="F120">
-        <v>0.7894736842105263</v>
+        <v>0.8421052631578947</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -3853,19 +3853,19 @@
         <v>125</v>
       </c>
       <c r="B121">
-        <v>0.665780387804803</v>
+        <v>0.5340947624772651</v>
       </c>
       <c r="C121">
-        <v>0.03695806680881308</v>
+        <v>0.03198976327575176</v>
       </c>
       <c r="D121">
-        <v>0.3221610805402702</v>
+        <v>0.2431215607803902</v>
       </c>
       <c r="E121">
-        <v>0.01892285298398836</v>
+        <v>0.01633986928104575</v>
       </c>
       <c r="F121">
-        <v>0.7878787878787878</v>
+        <v>0.7575757575757576</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -3873,16 +3873,16 @@
         <v>126</v>
       </c>
       <c r="B122">
-        <v>0.6873430436966349</v>
+        <v>0.6272915620291312</v>
       </c>
       <c r="C122">
-        <v>0.009971509971509971</v>
+        <v>0.009722222222222222</v>
       </c>
       <c r="D122">
-        <v>0.3046523261630815</v>
+        <v>0.2866433216608304</v>
       </c>
       <c r="E122">
-        <v>0.00501432664756447</v>
+        <v>0.004888268156424581</v>
       </c>
       <c r="F122">
         <v>0.875</v>
@@ -3893,19 +3893,19 @@
         <v>127</v>
       </c>
       <c r="B123">
-        <v>0.6424151195852149</v>
+        <v>0.5968389362769694</v>
       </c>
       <c r="C123">
-        <v>0.007733952049497293</v>
+        <v>0.007920792079207921</v>
       </c>
       <c r="D123">
-        <v>0.3581790895447724</v>
+        <v>0.2481240620310155</v>
       </c>
       <c r="E123">
-        <v>0.003885003885003885</v>
+        <v>0.003976143141153081</v>
       </c>
       <c r="F123">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -3913,19 +3913,19 @@
         <v>128</v>
       </c>
       <c r="B124">
-        <v>0.750752256770311</v>
+        <v>0.5626379137412237</v>
       </c>
       <c r="C124">
-        <v>0.007843137254901961</v>
+        <v>0.005536332179930796</v>
       </c>
       <c r="D124">
-        <v>0.3671835917958979</v>
+        <v>0.2811405702851426</v>
       </c>
       <c r="E124">
-        <v>0.003937007874015748</v>
+        <v>0.002777777777777778</v>
       </c>
       <c r="F124">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -3933,19 +3933,19 @@
         <v>129</v>
       </c>
       <c r="B125">
-        <v>0.7055583375062594</v>
+        <v>0.3972208312468703</v>
       </c>
       <c r="C125">
-        <v>0.002965159377316531</v>
+        <v>0.001275510204081633</v>
       </c>
       <c r="D125">
-        <v>0.3271635817908954</v>
+        <v>0.216608304152076</v>
       </c>
       <c r="E125">
-        <v>0.001484780994803266</v>
+        <v>0.0006385696040868455</v>
       </c>
       <c r="F125">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -3953,19 +3953,19 @@
         <v>130</v>
       </c>
       <c r="B126">
-        <v>0.6482187837351566</v>
+        <v>0.6271320618927672</v>
       </c>
       <c r="C126">
-        <v>0.0180327868852459</v>
+        <v>0.01577909270216963</v>
       </c>
       <c r="D126">
-        <v>0.4007003501750875</v>
+        <v>0.2511255627813907</v>
       </c>
       <c r="E126">
-        <v>0.00912106135986733</v>
+        <v>0.007962840079628402</v>
       </c>
       <c r="F126">
-        <v>0.7857142857142857</v>
+        <v>0.8571428571428571</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -3973,19 +3973,19 @@
         <v>131</v>
       </c>
       <c r="B127">
-        <v>0.6261928679055752</v>
+        <v>0.5144713711702662</v>
       </c>
       <c r="C127">
-        <v>0.009188361408882083</v>
+        <v>0.009893992932862191</v>
       </c>
       <c r="D127">
-        <v>0.3526763381690846</v>
+        <v>0.2991495747873937</v>
       </c>
       <c r="E127">
-        <v>0.004622496147919877</v>
+        <v>0.004975124378109453</v>
       </c>
       <c r="F127">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -3993,19 +3993,19 @@
         <v>132</v>
       </c>
       <c r="B128">
-        <v>0.6187121785173979</v>
+        <v>0.6202880736258195</v>
       </c>
       <c r="C128">
-        <v>0.02069475240206948</v>
+        <v>0.01789401238816242</v>
       </c>
       <c r="D128">
-        <v>0.3371685842921461</v>
+        <v>0.2861430715357679</v>
       </c>
       <c r="E128">
-        <v>0.01047120418848168</v>
+        <v>0.009046624913013222</v>
       </c>
       <c r="F128">
-        <v>0.875</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -4013,19 +4013,19 @@
         <v>133</v>
       </c>
       <c r="B129">
-        <v>0.6548417132216016</v>
+        <v>0.6075334349077366</v>
       </c>
       <c r="C129">
-        <v>0.03504218040233614</v>
+        <v>0.03259452411994785</v>
       </c>
       <c r="D129">
-        <v>0.256128064032016</v>
+        <v>0.2576288144072036</v>
       </c>
       <c r="E129">
-        <v>0.01786896095301125</v>
+        <v>0.01662234042553191</v>
       </c>
       <c r="F129">
-        <v>0.9</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -4033,16 +4033,16 @@
         <v>134</v>
       </c>
       <c r="B130">
-        <v>0.6274986041317699</v>
+        <v>0.6196538246789504</v>
       </c>
       <c r="C130">
-        <v>0.009491525423728813</v>
+        <v>0.009472259810554804</v>
       </c>
       <c r="D130">
-        <v>0.2691345672836418</v>
+        <v>0.2676338169084542</v>
       </c>
       <c r="E130">
-        <v>0.004774897680763984</v>
+        <v>0.004765146358066712</v>
       </c>
       <c r="F130">
         <v>0.7777777777777778</v>
@@ -4053,19 +4053,19 @@
         <v>135</v>
       </c>
       <c r="B131">
-        <v>0.6886603110888109</v>
+        <v>0.6522829904666333</v>
       </c>
       <c r="C131">
-        <v>0.007304601899196494</v>
+        <v>0.008053691275167786</v>
       </c>
       <c r="D131">
-        <v>0.32016008004002</v>
+        <v>0.2606303151575788</v>
       </c>
       <c r="E131">
-        <v>0.003668378576669112</v>
+        <v>0.004043126684636119</v>
       </c>
       <c r="F131">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -4073,19 +4073,19 @@
         <v>136</v>
       </c>
       <c r="B132">
-        <v>0.3753008895866038</v>
+        <v>0.5208071690214547</v>
       </c>
       <c r="C132">
-        <v>0.02874743326488706</v>
+        <v>0.04064554692169755</v>
       </c>
       <c r="D132">
-        <v>0.2901450725362681</v>
+        <v>0.1970985492746373</v>
       </c>
       <c r="E132">
-        <v>0.01476793248945148</v>
+        <v>0.0208078335373317</v>
       </c>
       <c r="F132">
-        <v>0.5384615384615384</v>
+        <v>0.8717948717948718</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -4093,19 +4093,19 @@
         <v>137</v>
       </c>
       <c r="B133">
-        <v>0.4359595881246485</v>
+        <v>0.4247173689619733</v>
       </c>
       <c r="C133">
-        <v>0.04691689008042895</v>
+        <v>0.04960677555958862</v>
       </c>
       <c r="D133">
-        <v>0.2886443221610805</v>
+        <v>0.2141070535267634</v>
       </c>
       <c r="E133">
-        <v>0.02432244614315497</v>
+        <v>0.025625</v>
       </c>
       <c r="F133">
-        <v>0.660377358490566</v>
+        <v>0.7735849056603774</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -4113,19 +4113,19 @@
         <v>138</v>
       </c>
       <c r="B134">
-        <v>0.4648527237575344</v>
+        <v>0.4683213920163766</v>
       </c>
       <c r="C134">
-        <v>0.03924528301886793</v>
+        <v>0.04193138500635324</v>
       </c>
       <c r="D134">
-        <v>0.3631815907953977</v>
+        <v>0.2456228114057029</v>
       </c>
       <c r="E134">
-        <v>0.0203125</v>
+        <v>0.02158273381294964</v>
       </c>
       <c r="F134">
-        <v>0.5777777777777777</v>
+        <v>0.7333333333333333</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -4133,13 +4133,13 @@
         <v>139</v>
       </c>
       <c r="B135">
-        <v>0.0402902902902903</v>
+        <v>0.1041041041041041</v>
       </c>
       <c r="C135">
         <v>0</v>
       </c>
       <c r="D135">
-        <v>0.2901450725362681</v>
+        <v>0.1445722861430715</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -4153,19 +4153,19 @@
         <v>140</v>
       </c>
       <c r="B136">
-        <v>0.3977253176690343</v>
+        <v>0.4309656647086293</v>
       </c>
       <c r="C136">
-        <v>0.1629179331306991</v>
+        <v>0.186221743810549</v>
       </c>
       <c r="D136">
-        <v>0.3111555777888945</v>
+        <v>0.2436218109054527</v>
       </c>
       <c r="E136">
-        <v>0.09469964664310954</v>
+        <v>0.1062653562653563</v>
       </c>
       <c r="F136">
-        <v>0.5826086956521739</v>
+        <v>0.7521739130434782</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -4173,19 +4173,19 @@
         <v>141</v>
       </c>
       <c r="B137">
-        <v>0.4674092978341841</v>
+        <v>0.5776773807881547</v>
       </c>
       <c r="C137">
-        <v>0.02501839587932303</v>
+        <v>0.02580645161290323</v>
       </c>
       <c r="D137">
-        <v>0.3371685842921461</v>
+        <v>0.2446223111555778</v>
       </c>
       <c r="E137">
-        <v>0.01271503365744203</v>
+        <v>0.01308900523560209</v>
       </c>
       <c r="F137">
-        <v>0.7727272727272727</v>
+        <v>0.9090909090909091</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -4193,19 +4193,19 @@
         <v>142</v>
       </c>
       <c r="B138">
-        <v>0.4052764486975013</v>
+        <v>0.4325491759702286</v>
       </c>
       <c r="C138">
-        <v>0.01404494382022472</v>
+        <v>0.01521876981610653</v>
       </c>
       <c r="D138">
-        <v>0.2976488244122061</v>
+        <v>0.2231115557778889</v>
       </c>
       <c r="E138">
-        <v>0.007117437722419928</v>
+        <v>0.007702182284980745</v>
       </c>
       <c r="F138">
-        <v>0.5263157894736842</v>
+        <v>0.631578947368421</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -4213,19 +4213,19 @@
         <v>143</v>
       </c>
       <c r="B139">
-        <v>0.4052947112245504</v>
+        <v>0.4635395025820621</v>
       </c>
       <c r="C139">
-        <v>0.01611721611721612</v>
+        <v>0.01515151515151515</v>
       </c>
       <c r="D139">
-        <v>0.3281640820410205</v>
+        <v>0.2196098049024512</v>
       </c>
       <c r="E139">
-        <v>0.008160237388724036</v>
+        <v>0.007657945118059987</v>
       </c>
       <c r="F139">
-        <v>0.6470588235294118</v>
+        <v>0.7058823529411765</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -4233,19 +4233,19 @@
         <v>144</v>
       </c>
       <c r="B140">
-        <v>0.4378247139121871</v>
+        <v>0.4189531053686034</v>
       </c>
       <c r="C140">
-        <v>0.1577958672510958</v>
+        <v>0.1546511627906977</v>
       </c>
       <c r="D140">
-        <v>0.3271635817908954</v>
+        <v>0.2726363181590795</v>
       </c>
       <c r="E140">
-        <v>0.08993576017130621</v>
+        <v>0.08727034120734908</v>
       </c>
       <c r="F140">
-        <v>0.6428571428571429</v>
+        <v>0.6785714285714286</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -4253,19 +4253,19 @@
         <v>145</v>
       </c>
       <c r="B141">
-        <v>0.4661114343904568</v>
+        <v>0.5163951120162933</v>
       </c>
       <c r="C141">
-        <v>0.03072625698324022</v>
+        <v>0.03443877551020408</v>
       </c>
       <c r="D141">
-        <v>0.3056528264132066</v>
+        <v>0.2426213106553277</v>
       </c>
       <c r="E141">
-        <v>0.01574803149606299</v>
+        <v>0.01761252446183953</v>
       </c>
       <c r="F141">
-        <v>0.6285714285714286</v>
+        <v>0.7714285714285715</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -4273,16 +4273,16 @@
         <v>146</v>
       </c>
       <c r="B142">
-        <v>0.4238476953907815</v>
+        <v>0.2508350033400133</v>
       </c>
       <c r="C142">
-        <v>0.002906976744186046</v>
+        <v>0.002503128911138924</v>
       </c>
       <c r="D142">
-        <v>0.3136568284142071</v>
+        <v>0.2026013006503252</v>
       </c>
       <c r="E142">
-        <v>0.001456664238892935</v>
+        <v>0.001253918495297806</v>
       </c>
       <c r="F142">
         <v>0.6666666666666666</v>
@@ -4293,13 +4293,13 @@
         <v>147</v>
       </c>
       <c r="B143">
-        <v>0.0650650650650651</v>
+        <v>0.07757757757757755</v>
       </c>
       <c r="C143">
         <v>0</v>
       </c>
       <c r="D143">
-        <v>0.3626813406703352</v>
+        <v>0.2261130565282641</v>
       </c>
       <c r="E143">
         <v>0</v>
@@ -4313,13 +4313,13 @@
         <v>148</v>
       </c>
       <c r="B144">
-        <v>0.1486486486486486</v>
+        <v>0.1108608608608608</v>
       </c>
       <c r="C144">
         <v>0</v>
       </c>
       <c r="D144">
-        <v>0.3331665832916458</v>
+        <v>0.2386193096548274</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -4333,19 +4333,19 @@
         <v>149</v>
       </c>
       <c r="B145">
-        <v>0.4728903486609399</v>
+        <v>0.5932920667003537</v>
       </c>
       <c r="C145">
-        <v>0.01697530864197531</v>
+        <v>0.02418207681365576</v>
       </c>
       <c r="D145">
-        <v>0.3626813406703352</v>
+        <v>0.3136568284142071</v>
       </c>
       <c r="E145">
-        <v>0.008620689655172414</v>
+        <v>0.01226551226551227</v>
       </c>
       <c r="F145">
-        <v>0.55</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -4353,19 +4353,19 @@
         <v>150</v>
       </c>
       <c r="B146">
-        <v>0.4153884886513285</v>
+        <v>0.5209543729181192</v>
       </c>
       <c r="C146">
-        <v>0.0104089219330855</v>
+        <v>0.01275690999291283</v>
       </c>
       <c r="D146">
-        <v>0.3341670835417709</v>
+        <v>0.3031515757878939</v>
       </c>
       <c r="E146">
-        <v>0.005255255255255256</v>
+        <v>0.006437768240343348</v>
       </c>
       <c r="F146">
-        <v>0.5384615384615384</v>
+        <v>0.6923076923076923</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -4373,19 +4373,19 @@
         <v>151</v>
       </c>
       <c r="B147">
-        <v>0.3782861153649821</v>
+        <v>0.5043198060234814</v>
       </c>
       <c r="C147">
-        <v>0.03176795580110497</v>
+        <v>0.03727506426735219</v>
       </c>
       <c r="D147">
-        <v>0.2986493246623312</v>
+        <v>0.2506253126563281</v>
       </c>
       <c r="E147">
-        <v>0.01633522727272727</v>
+        <v>0.01912928759894459</v>
       </c>
       <c r="F147">
-        <v>0.575</v>
+        <v>0.725</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -4393,19 +4393,19 @@
         <v>152</v>
       </c>
       <c r="B148">
-        <v>0.3988247667825133</v>
+        <v>0.5947503201024328</v>
       </c>
       <c r="C148">
-        <v>0.008869179600886918</v>
+        <v>0.01189591078066914</v>
       </c>
       <c r="D148">
-        <v>0.3291645822911456</v>
+        <v>0.3351675837918959</v>
       </c>
       <c r="E148">
-        <v>0.004470938897168405</v>
+        <v>0.005997001499250375</v>
       </c>
       <c r="F148">
-        <v>0.5454545454545454</v>
+        <v>0.7272727272727273</v>
       </c>
     </row>
     <row r="149" spans="1:6">
@@ -4413,19 +4413,19 @@
         <v>153</v>
       </c>
       <c r="B149">
-        <v>0.3993353525155646</v>
+        <v>0.3780638285938639</v>
       </c>
       <c r="C149">
-        <v>0.0148347943358058</v>
+        <v>0.0154539600772698</v>
       </c>
       <c r="D149">
-        <v>0.2691345672836418</v>
+        <v>0.2351175587793897</v>
       </c>
       <c r="E149">
-        <v>0.007508532423208191</v>
+        <v>0.007817589576547232</v>
       </c>
       <c r="F149">
-        <v>0.6111111111111112</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="150" spans="1:6">
@@ -4433,19 +4433,19 @@
         <v>154</v>
       </c>
       <c r="B150">
-        <v>0.3120160884866768</v>
+        <v>0.4364504776269482</v>
       </c>
       <c r="C150">
-        <v>0.00599250936329588</v>
+        <v>0.008124576844955992</v>
       </c>
       <c r="D150">
-        <v>0.336168084042021</v>
+        <v>0.2671335667833917</v>
       </c>
       <c r="E150">
-        <v>0.003018867924528302</v>
+        <v>0.00408997955010225</v>
       </c>
       <c r="F150">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -4453,19 +4453,19 @@
         <v>155</v>
       </c>
       <c r="B151">
-        <v>0.3701736318138291</v>
+        <v>0.5461858818002783</v>
       </c>
       <c r="C151">
-        <v>0.04261363636363636</v>
+        <v>0.05342465753424658</v>
       </c>
       <c r="D151">
-        <v>0.3256628314157078</v>
+        <v>0.3086543271635818</v>
       </c>
       <c r="E151">
-        <v>0.02220577350111029</v>
+        <v>0.0277975766215253</v>
       </c>
       <c r="F151">
-        <v>0.5263157894736842</v>
+        <v>0.6842105263157895</v>
       </c>
     </row>
     <row r="152" spans="1:6">
@@ -4473,19 +4473,19 @@
         <v>156</v>
       </c>
       <c r="B152">
-        <v>0.3785695674830641</v>
+        <v>0.4608324648254299</v>
       </c>
       <c r="C152">
-        <v>0.06085753803596127</v>
+        <v>0.06426229508196721</v>
       </c>
       <c r="D152">
-        <v>0.3206603301650826</v>
+        <v>0.2861430715357679</v>
       </c>
       <c r="E152">
-        <v>0.0322108345534407</v>
+        <v>0.03391003460207612</v>
       </c>
       <c r="F152">
-        <v>0.55</v>
+        <v>0.6125</v>
       </c>
     </row>
     <row r="153" spans="1:6">
@@ -4493,19 +4493,19 @@
         <v>157</v>
       </c>
       <c r="B153">
-        <v>0.3914242728184554</v>
+        <v>0.6736208625877633</v>
       </c>
       <c r="C153">
-        <v>0.00446096654275093</v>
+        <v>0.006756756756756757</v>
       </c>
       <c r="D153">
-        <v>0.3301650825412706</v>
+        <v>0.264632316158079</v>
       </c>
       <c r="E153">
-        <v>0.002238805970149254</v>
+        <v>0.003389830508474576</v>
       </c>
       <c r="F153">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -4513,16 +4513,16 @@
         <v>158</v>
       </c>
       <c r="B154">
-        <v>0.5055082623935904</v>
+        <v>0.8714321482223335</v>
       </c>
       <c r="C154">
-        <v>0.00311284046692607</v>
+        <v>0.002949852507374631</v>
       </c>
       <c r="D154">
-        <v>0.3591795897948974</v>
+        <v>0.3236618309154577</v>
       </c>
       <c r="E154">
-        <v>0.001558846453624318</v>
+        <v>0.001477104874446086</v>
       </c>
       <c r="F154">
         <v>1</v>
@@ -4533,19 +4533,19 @@
         <v>159</v>
       </c>
       <c r="B155">
-        <v>0.415005397625045</v>
+        <v>0.4539942425332854</v>
       </c>
       <c r="C155">
-        <v>0.01198501872659176</v>
+        <v>0.009859154929577466</v>
       </c>
       <c r="D155">
-        <v>0.3401700850425213</v>
+        <v>0.296648324162081</v>
       </c>
       <c r="E155">
-        <v>0.006056018168054504</v>
+        <v>0.004978662873399715</v>
       </c>
       <c r="F155">
-        <v>0.5714285714285714</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="156" spans="1:6">
@@ -4553,19 +4553,19 @@
         <v>160</v>
       </c>
       <c r="B156">
-        <v>0.3598004834545022</v>
+        <v>0.4637203105828923</v>
       </c>
       <c r="C156">
-        <v>0.06539074960127592</v>
+        <v>0.09715475364330327</v>
       </c>
       <c r="D156">
-        <v>0.4137068534267134</v>
+        <v>0.3491745872936468</v>
       </c>
       <c r="E156">
-        <v>0.03602811950790861</v>
+        <v>0.05283018867924529</v>
       </c>
       <c r="F156">
-        <v>0.353448275862069</v>
+        <v>0.603448275862069</v>
       </c>
     </row>
     <row r="157" spans="1:6">
@@ -4573,19 +4573,19 @@
         <v>161</v>
       </c>
       <c r="B157">
-        <v>0.4058274650565028</v>
+        <v>0.4854471804387393</v>
       </c>
       <c r="C157">
-        <v>0.1520056298381421</v>
+        <v>0.1861360718870347</v>
       </c>
       <c r="D157">
-        <v>0.3971985992996498</v>
+        <v>0.3656828414207103</v>
       </c>
       <c r="E157">
-        <v>0.09007506255212677</v>
+        <v>0.1085329341317365</v>
       </c>
       <c r="F157">
-        <v>0.4864864864864865</v>
+        <v>0.6531531531531531</v>
       </c>
     </row>
     <row r="158" spans="1:6">
@@ -4593,16 +4593,16 @@
         <v>162</v>
       </c>
       <c r="B158">
-        <v>0.4041753815167713</v>
+        <v>0.4723255093345728</v>
       </c>
       <c r="C158">
-        <v>0.01126307320997587</v>
+        <v>0.01015228426395939</v>
       </c>
       <c r="D158">
-        <v>0.3851925962981491</v>
+        <v>0.3171585792896448</v>
       </c>
       <c r="E158">
-        <v>0.005691056910569106</v>
+        <v>0.005124450951683748</v>
       </c>
       <c r="F158">
         <v>0.5384615384615384</v>
@@ -4613,16 +4613,16 @@
         <v>163</v>
       </c>
       <c r="B159">
-        <v>0.7135703555332999</v>
+        <v>0.7696544817225839</v>
       </c>
       <c r="C159">
-        <v>0.00354924578527063</v>
+        <v>0.003007518796992481</v>
       </c>
       <c r="D159">
-        <v>0.4382191095547774</v>
+        <v>0.3366683341670835</v>
       </c>
       <c r="E159">
-        <v>0.001777777777777778</v>
+        <v>0.001506024096385542</v>
       </c>
       <c r="F159">
         <v>1</v>
@@ -4633,16 +4633,16 @@
         <v>164</v>
       </c>
       <c r="B160">
-        <v>0.8176993689041883</v>
+        <v>0.8071572002294892</v>
       </c>
       <c r="C160">
-        <v>0.0102489019033675</v>
+        <v>0.009880028228652082</v>
       </c>
       <c r="D160">
-        <v>0.3236618309154577</v>
+        <v>0.2981490745372686</v>
       </c>
       <c r="E160">
-        <v>0.005150846210448859</v>
+        <v>0.004964539007092199</v>
       </c>
       <c r="F160">
         <v>1</v>
@@ -4653,19 +4653,19 @@
         <v>165</v>
       </c>
       <c r="B161">
-        <v>0.4540304073436603</v>
+        <v>0.5846959265633964</v>
       </c>
       <c r="C161">
-        <v>0.00642570281124498</v>
+        <v>0.007032348804500703</v>
       </c>
       <c r="D161">
-        <v>0.3811905952976488</v>
+        <v>0.2936468234117058</v>
       </c>
       <c r="E161">
-        <v>0.003231017770597738</v>
+        <v>0.00353356890459364</v>
       </c>
       <c r="F161">
-        <v>0.5714285714285714</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="162" spans="1:6">
@@ -4673,13 +4673,13 @@
         <v>166</v>
       </c>
       <c r="B162">
-        <v>0.2892892892892893</v>
+        <v>0.1473973973973974</v>
       </c>
       <c r="C162">
         <v>0</v>
       </c>
       <c r="D162">
-        <v>0.3691845922961481</v>
+        <v>0.3236618309154577</v>
       </c>
       <c r="E162">
         <v>0</v>
@@ -4693,19 +4693,19 @@
         <v>167</v>
       </c>
       <c r="B163">
-        <v>0.4274274274274274</v>
+        <v>0.1796796796796797</v>
       </c>
       <c r="C163">
-        <v>0.001443001443001443</v>
+        <v>0</v>
       </c>
       <c r="D163">
-        <v>0.3076538269134567</v>
+        <v>0.3796898449224612</v>
       </c>
       <c r="E163">
-        <v>0.0007220216606498195</v>
+        <v>0</v>
       </c>
       <c r="F163">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -4713,19 +4713,19 @@
         <v>168</v>
       </c>
       <c r="B164">
-        <v>0.5947671507260891</v>
+        <v>0.6104156234351527</v>
       </c>
       <c r="C164">
-        <v>0.002947678703021371</v>
+        <v>0.001877934272300469</v>
       </c>
       <c r="D164">
-        <v>0.3231615807903952</v>
+        <v>0.4682341170585292</v>
       </c>
       <c r="E164">
-        <v>0.001476014760147601</v>
+        <v>0.0009407337723424271</v>
       </c>
       <c r="F164">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="165" spans="1:6">
@@ -4733,13 +4733,13 @@
         <v>169</v>
       </c>
       <c r="B165">
-        <v>0.2637637637637638</v>
+        <v>0.09184184184184185</v>
       </c>
       <c r="C165">
         <v>0</v>
       </c>
       <c r="D165">
-        <v>0.32016008004002</v>
+        <v>0.3706853426713357</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -4753,19 +4753,19 @@
         <v>170</v>
       </c>
       <c r="B166">
-        <v>0.6143057682491068</v>
+        <v>0.5787327718223584</v>
       </c>
       <c r="C166">
-        <v>0.04608294930875576</v>
+        <v>0.0503655564581641</v>
       </c>
       <c r="D166">
-        <v>0.2751375687843922</v>
+        <v>0.415207603801901</v>
       </c>
       <c r="E166">
-        <v>0.02366463826910074</v>
+        <v>0.02602854743912678</v>
       </c>
       <c r="F166">
-        <v>0.875</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="167" spans="1:6">
@@ -4773,13 +4773,13 @@
         <v>171</v>
       </c>
       <c r="B167">
-        <v>0.2602602602602603</v>
+        <v>0.2017017017017017</v>
       </c>
       <c r="C167">
         <v>0</v>
       </c>
       <c r="D167">
-        <v>0.3256628314157078</v>
+        <v>0.4092046023011506</v>
       </c>
       <c r="E167">
         <v>0</v>
@@ -4793,19 +4793,19 @@
         <v>172</v>
       </c>
       <c r="B168">
-        <v>0.5608412618928392</v>
+        <v>0.5100150225338007</v>
       </c>
       <c r="C168">
-        <v>0.002886002886002886</v>
+        <v>0.001531393568147014</v>
       </c>
       <c r="D168">
-        <v>0.3086543271635818</v>
+        <v>0.3476738369184592</v>
       </c>
       <c r="E168">
-        <v>0.001445086705202312</v>
+        <v>0.0007668711656441718</v>
       </c>
       <c r="F168">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="169" spans="1:6">
@@ -4813,13 +4813,13 @@
         <v>173</v>
       </c>
       <c r="B169">
-        <v>0.2752752752752752</v>
+        <v>0.2049549549549549</v>
       </c>
       <c r="C169">
         <v>0</v>
       </c>
       <c r="D169">
-        <v>0.343671835917959</v>
+        <v>0.4207103551775888</v>
       </c>
       <c r="E169">
         <v>0</v>
@@ -4833,19 +4833,19 @@
         <v>174</v>
       </c>
       <c r="B170">
-        <v>0.668677727501257</v>
+        <v>0.5991955756661639</v>
       </c>
       <c r="C170">
-        <v>0.01329787234042553</v>
+        <v>0.01202749140893471</v>
       </c>
       <c r="D170">
-        <v>0.2576288144072036</v>
+        <v>0.4247123561780891</v>
       </c>
       <c r="E170">
-        <v>0.006693440428380187</v>
+        <v>0.006065857885615251</v>
       </c>
       <c r="F170">
-        <v>1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="171" spans="1:6">
@@ -4853,19 +4853,19 @@
         <v>175</v>
       </c>
       <c r="B171">
-        <v>0.5522712090848363</v>
+        <v>0.5136105544422177</v>
       </c>
       <c r="C171">
-        <v>0.004207573632538569</v>
+        <v>0.003745318352059925</v>
       </c>
       <c r="D171">
-        <v>0.2896448224112056</v>
+        <v>0.4677338669334667</v>
       </c>
       <c r="E171">
-        <v>0.002108222066057625</v>
+        <v>0.001877934272300469</v>
       </c>
       <c r="F171">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="172" spans="1:6">
@@ -4873,19 +4873,19 @@
         <v>176</v>
       </c>
       <c r="B172">
-        <v>0.4609829488465397</v>
+        <v>0.5138916750250753</v>
       </c>
       <c r="C172">
-        <v>0.003055767761650115</v>
+        <v>0.004583651642475172</v>
       </c>
       <c r="D172">
-        <v>0.3471735867933967</v>
+        <v>0.3481740870435218</v>
       </c>
       <c r="E172">
-        <v>0.001533742331288344</v>
+        <v>0.002300613496932515</v>
       </c>
       <c r="F172">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="173" spans="1:6">
@@ -4893,13 +4893,13 @@
         <v>177</v>
       </c>
       <c r="B173">
-        <v>0.2617617617617617</v>
+        <v>0.2064564564564564</v>
       </c>
       <c r="C173">
         <v>0</v>
       </c>
       <c r="D173">
-        <v>0.3316658329164582</v>
+        <v>0.4317158579289645</v>
       </c>
       <c r="E173">
         <v>0</v>
@@ -4913,13 +4913,13 @@
         <v>178</v>
       </c>
       <c r="B174">
-        <v>0.2304804804804805</v>
+        <v>0.1801801801801802</v>
       </c>
       <c r="C174">
         <v>0</v>
       </c>
       <c r="D174">
-        <v>0.2846423211605803</v>
+        <v>0.3736868434217109</v>
       </c>
       <c r="E174">
         <v>0</v>
@@ -4933,16 +4933,16 @@
         <v>179</v>
       </c>
       <c r="B175">
-        <v>0.6852779168753129</v>
+        <v>0.6987981972959438</v>
       </c>
       <c r="C175">
-        <v>0.002911208151382824</v>
+        <v>0.002768166089965398</v>
       </c>
       <c r="D175">
-        <v>0.3146573286643322</v>
+        <v>0.2791395697848925</v>
       </c>
       <c r="E175">
-        <v>0.001457725947521866</v>
+        <v>0.001386001386001386</v>
       </c>
       <c r="F175">
         <v>1</v>
@@ -4953,19 +4953,19 @@
         <v>180</v>
       </c>
       <c r="B176">
-        <v>0.3059757942511346</v>
+        <v>0.4508478315683307</v>
       </c>
       <c r="C176">
-        <v>0.006779661016949152</v>
+        <v>0.01226158038147139</v>
       </c>
       <c r="D176">
-        <v>0.4137068534267134</v>
+        <v>0.2746373186593297</v>
       </c>
       <c r="E176">
-        <v>0.003436426116838488</v>
+        <v>0.006198347107438017</v>
       </c>
       <c r="F176">
-        <v>0.25</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="177" spans="1:6">
@@ -4973,19 +4973,19 @@
         <v>181</v>
       </c>
       <c r="B177">
-        <v>0.4378578676523882</v>
+        <v>0.4305736754366891</v>
       </c>
       <c r="C177">
-        <v>0.02206461780929866</v>
+        <v>0.02229102167182663</v>
       </c>
       <c r="D177">
-        <v>0.3791895947973987</v>
+        <v>0.2101050525262631</v>
       </c>
       <c r="E177">
-        <v>0.0112812248186946</v>
+        <v>0.0113421550094518</v>
       </c>
       <c r="F177">
-        <v>0.5</v>
+        <v>0.6428571428571429</v>
       </c>
     </row>
     <row r="178" spans="1:6">
@@ -4993,16 +4993,16 @@
         <v>182</v>
       </c>
       <c r="B178">
-        <v>0.3926524130451623</v>
+        <v>0.361685645673561</v>
       </c>
       <c r="C178">
-        <v>0.008375209380234505</v>
+        <v>0.007874015748031496</v>
       </c>
       <c r="D178">
-        <v>0.407703851925963</v>
+        <v>0.3696848424212106</v>
       </c>
       <c r="E178">
-        <v>0.004233700254022015</v>
+        <v>0.003977724741447892</v>
       </c>
       <c r="F178">
         <v>0.3846153846153846</v>
@@ -5013,16 +5013,16 @@
         <v>183</v>
       </c>
       <c r="B179">
-        <v>0.6941662493740611</v>
+        <v>0.9109914872308462</v>
       </c>
       <c r="C179">
-        <v>0.003091190108191654</v>
+        <v>0.002836879432624114</v>
       </c>
       <c r="D179">
-        <v>0.3546773386693347</v>
+        <v>0.296648324162081</v>
       </c>
       <c r="E179">
-        <v>0.001547987616099071</v>
+        <v>0.001420454545454545</v>
       </c>
       <c r="F179">
         <v>1</v>
@@ -5033,19 +5033,19 @@
         <v>184</v>
       </c>
       <c r="B180">
-        <v>0.7508305647840531</v>
+        <v>0.7180774230824787</v>
       </c>
       <c r="C180">
-        <v>0.0274390243902439</v>
+        <v>0.02185792349726776</v>
       </c>
       <c r="D180">
-        <v>0.3616808404202101</v>
+        <v>0.2836418209104552</v>
       </c>
       <c r="E180">
-        <v>0.0139426800929512</v>
+        <v>0.01108801108801109</v>
       </c>
       <c r="F180">
-        <v>0.8571428571428571</v>
+        <v>0.7619047619047619</v>
       </c>
     </row>
     <row r="181" spans="1:6">
@@ -5053,19 +5053,19 @@
         <v>185</v>
       </c>
       <c r="B181">
-        <v>0.7343854375417501</v>
+        <v>0.9112391449565799</v>
       </c>
       <c r="C181">
-        <v>0.003241491085899514</v>
+        <v>0.004084411164057181</v>
       </c>
       <c r="D181">
-        <v>0.3846923461730866</v>
+        <v>0.2681340670335168</v>
       </c>
       <c r="E181">
-        <v>0.001624695369618197</v>
+        <v>0.002046384720327421</v>
       </c>
       <c r="F181">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182" spans="1:6">
@@ -5073,19 +5073,19 @@
         <v>186</v>
       </c>
       <c r="B182">
-        <v>0.6040310465698547</v>
+        <v>0.7853029544316475</v>
       </c>
       <c r="C182">
-        <v>0.001544401544401544</v>
+        <v>0.0026542800265428</v>
       </c>
       <c r="D182">
-        <v>0.3531765882941471</v>
+        <v>0.2481240620310155</v>
       </c>
       <c r="E182">
-        <v>0.0007733952049497294</v>
+        <v>0.00132890365448505</v>
       </c>
       <c r="F182">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183" spans="1:6">
@@ -5093,19 +5093,19 @@
         <v>187</v>
       </c>
       <c r="B183">
-        <v>0.5839178356713427</v>
+        <v>0.6421175684702739</v>
       </c>
       <c r="C183">
-        <v>0.003072196620583717</v>
+        <v>0.004172461752433936</v>
       </c>
       <c r="D183">
-        <v>0.3506753376688344</v>
+        <v>0.2836418209104552</v>
       </c>
       <c r="E183">
-        <v>0.001539645881447267</v>
+        <v>0.002090592334494774</v>
       </c>
       <c r="F183">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184" spans="1:6">
@@ -5113,19 +5113,19 @@
         <v>188</v>
       </c>
       <c r="B184">
-        <v>0.5995816871949803</v>
+        <v>0.6356030676272368</v>
       </c>
       <c r="C184">
-        <v>0.01374045801526718</v>
+        <v>0.01538461538461539</v>
       </c>
       <c r="D184">
-        <v>0.3536768384192096</v>
+        <v>0.295647823911956</v>
       </c>
       <c r="E184">
-        <v>0.006939090208172706</v>
+        <v>0.00776287932251235</v>
       </c>
       <c r="F184">
-        <v>0.6923076923076923</v>
+        <v>0.8461538461538461</v>
       </c>
     </row>
     <row r="185" spans="1:6">
@@ -5133,19 +5133,19 @@
         <v>189</v>
       </c>
       <c r="B185">
-        <v>0.6123628691983123</v>
+        <v>0.6502320675105485</v>
       </c>
       <c r="C185">
-        <v>0.02550637659414854</v>
+        <v>0.02995234853641933</v>
       </c>
       <c r="D185">
-        <v>0.3501750875437719</v>
+        <v>0.2871435717858929</v>
       </c>
       <c r="E185">
-        <v>0.01298701298701299</v>
+        <v>0.01522491349480969</v>
       </c>
       <c r="F185">
-        <v>0.7083333333333334</v>
+        <v>0.9166666666666666</v>
       </c>
     </row>
     <row r="186" spans="1:6">
@@ -5153,16 +5153,16 @@
         <v>190</v>
       </c>
       <c r="B186">
-        <v>0.6935403104656985</v>
+        <v>0.9351527290936404</v>
       </c>
       <c r="C186">
-        <v>0.003051106025934401</v>
+        <v>0.00264026402640264</v>
       </c>
       <c r="D186">
-        <v>0.3461730865432716</v>
+        <v>0.2441220610305153</v>
       </c>
       <c r="E186">
-        <v>0.001527883880825057</v>
+        <v>0.001321877065432915</v>
       </c>
       <c r="F186">
         <v>1</v>
@@ -5173,19 +5173,19 @@
         <v>191</v>
       </c>
       <c r="B187">
-        <v>0.6032799198798198</v>
+        <v>0.792814221331998</v>
       </c>
       <c r="C187">
-        <v>0.001511715797430083</v>
+        <v>0.002735978112175103</v>
       </c>
       <c r="D187">
-        <v>0.3391695847923962</v>
+        <v>0.2706353176588294</v>
       </c>
       <c r="E187">
-        <v>0.000757002271006813</v>
+        <v>0.00136986301369863</v>
       </c>
       <c r="F187">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188" spans="1:6">
@@ -5193,16 +5193,16 @@
         <v>192</v>
       </c>
       <c r="B188">
-        <v>0.5861291937906861</v>
+        <v>0.756634952428643</v>
       </c>
       <c r="C188">
-        <v>0.002960769800148038</v>
+        <v>0.002762430939226519</v>
       </c>
       <c r="D188">
-        <v>0.3261630815407704</v>
+        <v>0.2776388194097049</v>
       </c>
       <c r="E188">
-        <v>0.001482579688658265</v>
+        <v>0.001383125864453665</v>
       </c>
       <c r="F188">
         <v>1</v>
@@ -5213,16 +5213,16 @@
         <v>193</v>
       </c>
       <c r="B189">
-        <v>0.6614672977624785</v>
+        <v>0.7738453815261045</v>
       </c>
       <c r="C189">
-        <v>0.009230769230769232</v>
+        <v>0.008135593220338983</v>
       </c>
       <c r="D189">
-        <v>0.3556778389194598</v>
+        <v>0.2681340670335168</v>
       </c>
       <c r="E189">
-        <v>0.004640371229698376</v>
+        <v>0.004087193460490463</v>
       </c>
       <c r="F189">
         <v>0.8571428571428571</v>
@@ -5233,16 +5233,16 @@
         <v>194</v>
       </c>
       <c r="B190">
-        <v>0.7295943915873812</v>
+        <v>0.9271407110665999</v>
       </c>
       <c r="C190">
-        <v>0.003325020781379884</v>
+        <v>0.002664890073284477</v>
       </c>
       <c r="D190">
-        <v>0.400200100050025</v>
+        <v>0.2511255627813907</v>
       </c>
       <c r="E190">
-        <v>0.001665278934221482</v>
+        <v>0.00133422281521014</v>
       </c>
       <c r="F190">
         <v>1</v>
@@ -5253,19 +5253,19 @@
         <v>195</v>
       </c>
       <c r="B191">
-        <v>0.6742067553735926</v>
+        <v>0.669117479813488</v>
       </c>
       <c r="C191">
-        <v>0.05319148936170213</v>
+        <v>0.0580789277736411</v>
       </c>
       <c r="D191">
-        <v>0.376688344172086</v>
+        <v>0.3671835917958979</v>
       </c>
       <c r="E191">
-        <v>0.02753737214791503</v>
+        <v>0.0300462249614792</v>
       </c>
       <c r="F191">
-        <v>0.7777777777777778</v>
+        <v>0.8666666666666667</v>
       </c>
     </row>
     <row r="192" spans="1:6">
@@ -5273,19 +5273,19 @@
         <v>196</v>
       </c>
       <c r="B192">
-        <v>0.6055332999499249</v>
+        <v>0.6857786680020029</v>
       </c>
       <c r="C192">
-        <v>0.001542020046260601</v>
+        <v>0.002956393200295639</v>
       </c>
       <c r="D192">
-        <v>0.352176088044022</v>
+        <v>0.3251625812906453</v>
       </c>
       <c r="E192">
-        <v>0.0007722007722007722</v>
+        <v>0.001480384900074019</v>
       </c>
       <c r="F192">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193" spans="1:6">
@@ -5293,16 +5293,16 @@
         <v>197</v>
       </c>
       <c r="B193">
-        <v>0.7795591182364729</v>
+        <v>0.7734635938543755</v>
       </c>
       <c r="C193">
-        <v>0.004405286343612335</v>
+        <v>0.004231311706629055</v>
       </c>
       <c r="D193">
-        <v>0.3216608304152076</v>
+        <v>0.2936468234117058</v>
       </c>
       <c r="E193">
-        <v>0.002207505518763797</v>
+        <v>0.002120141342756184</v>
       </c>
       <c r="F193">
         <v>1</v>
@@ -5313,16 +5313,16 @@
         <v>198</v>
       </c>
       <c r="B194">
-        <v>0.5730477970102282</v>
+        <v>0.5504851822711776</v>
       </c>
       <c r="C194">
-        <v>0.03183791606367583</v>
+        <v>0.02883355176933159</v>
       </c>
       <c r="D194">
-        <v>0.3306653326663332</v>
+        <v>0.2586293146573287</v>
       </c>
       <c r="E194">
-        <v>0.01628423390081421</v>
+        <v>0.01471571906354515</v>
       </c>
       <c r="F194">
         <v>0.7096774193548387</v>
@@ -5333,16 +5333,16 @@
         <v>199</v>
       </c>
       <c r="B195">
-        <v>0.4491991991991992</v>
+        <v>0.6148648648648648</v>
       </c>
       <c r="C195">
-        <v>0.001474926253687316</v>
+        <v>0.001316655694535879</v>
       </c>
       <c r="D195">
-        <v>0.3226613306653326</v>
+        <v>0.2411205602801401</v>
       </c>
       <c r="E195">
-        <v>0.0007380073800738007</v>
+        <v>0.0006587615283267457</v>
       </c>
       <c r="F195">
         <v>1</v>
@@ -5353,16 +5353,16 @@
         <v>200</v>
       </c>
       <c r="B196">
-        <v>0.4997497497497497</v>
+        <v>0.6656656656656657</v>
       </c>
       <c r="C196">
-        <v>0.001589825119236884</v>
+        <v>0.001332445036642239</v>
       </c>
       <c r="D196">
-        <v>0.3716858429214607</v>
+        <v>0.2501250625312657</v>
       </c>
       <c r="E196">
-        <v>0.0007955449482895784</v>
+        <v>0.0006666666666666666</v>
       </c>
       <c r="F196">
         <v>1</v>
@@ -5373,16 +5373,16 @@
         <v>201</v>
       </c>
       <c r="B197">
-        <v>0.80837636259323</v>
+        <v>0.6817627653471027</v>
       </c>
       <c r="C197">
-        <v>0.009049773755656109</v>
+        <v>0.00844475721323012</v>
       </c>
       <c r="D197">
-        <v>0.3426713356678339</v>
+        <v>0.2951475737868934</v>
       </c>
       <c r="E197">
-        <v>0.004548900682335102</v>
+        <v>0.004243281471004243</v>
       </c>
       <c r="F197">
         <v>0.8571428571428571</v>
@@ -5393,19 +5393,19 @@
         <v>202</v>
       </c>
       <c r="B198">
-        <v>0.5851870576339737</v>
+        <v>0.5987770234484087</v>
       </c>
       <c r="C198">
-        <v>0.02344322344322344</v>
+        <v>0.02292993630573248</v>
       </c>
       <c r="D198">
-        <v>0.3331665832916458</v>
+        <v>0.2326163081540771</v>
       </c>
       <c r="E198">
-        <v>0.0119047619047619</v>
+        <v>0.01162040025823112</v>
       </c>
       <c r="F198">
-        <v>0.7619047619047619</v>
+        <v>0.8571428571428571</v>
       </c>
     </row>
     <row r="199" spans="1:6">
@@ -5413,16 +5413,16 @@
         <v>203</v>
       </c>
       <c r="B199">
-        <v>0.480980980980981</v>
+        <v>0.6721721721721722</v>
       </c>
       <c r="C199">
-        <v>0.00153727901614143</v>
+        <v>0.001375515818431912</v>
       </c>
       <c r="D199">
-        <v>0.3501750875437719</v>
+        <v>0.2736368184092046</v>
       </c>
       <c r="E199">
-        <v>0.0007692307692307692</v>
+        <v>0.0006882312456985547</v>
       </c>
       <c r="F199">
         <v>1</v>
@@ -5433,19 +5433,19 @@
         <v>204</v>
       </c>
       <c r="B200">
-        <v>0.3874122367101304</v>
+        <v>0.6515045135406219</v>
       </c>
       <c r="C200">
-        <v>0.003134796238244514</v>
+        <v>0.005509641873278237</v>
       </c>
       <c r="D200">
-        <v>0.3636818409204602</v>
+        <v>0.2776388194097049</v>
       </c>
       <c r="E200">
-        <v>0.001573564122738002</v>
+        <v>0.0027643400138217</v>
       </c>
       <c r="F200">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="201" spans="1:6">
@@ -5453,19 +5453,19 @@
         <v>205</v>
       </c>
       <c r="B201">
-        <v>0.4265581731906544</v>
+        <v>0.3964940233499854</v>
       </c>
       <c r="C201">
-        <v>0.3114035087719298</v>
+        <v>0.3452380952380952</v>
       </c>
       <c r="D201">
-        <v>0.3716858429214607</v>
+        <v>0.2846423211605803</v>
       </c>
       <c r="E201">
-        <v>0.2097488921713442</v>
+        <v>0.219953325554259</v>
       </c>
       <c r="F201">
-        <v>0.6042553191489362</v>
+        <v>0.8021276595744681</v>
       </c>
     </row>
     <row r="202" spans="1:6">
@@ -5473,19 +5473,19 @@
         <v>206</v>
       </c>
       <c r="B202">
-        <v>0.4397474494062552</v>
+        <v>0.4594413781568825</v>
       </c>
       <c r="C202">
-        <v>0.003314001657000828</v>
+        <v>0.006377551020408163</v>
       </c>
       <c r="D202">
-        <v>0.3981990995497749</v>
+        <v>0.2206103051525763</v>
       </c>
       <c r="E202">
-        <v>0.001665278934221482</v>
+        <v>0.003201024327784891</v>
       </c>
       <c r="F202">
-        <v>0.3333333333333333</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="203" spans="1:6">
@@ -5493,19 +5493,19 @@
         <v>207</v>
       </c>
       <c r="B203">
-        <v>0.3843943969132696</v>
+        <v>0.3722320080523402</v>
       </c>
       <c r="C203">
-        <v>0.009015777610818933</v>
+        <v>0.008871989860583017</v>
       </c>
       <c r="D203">
-        <v>0.3401700850425213</v>
+        <v>0.2176088044022011</v>
       </c>
       <c r="E203">
-        <v>0.004548900682335102</v>
+        <v>0.004469987228607918</v>
       </c>
       <c r="F203">
-        <v>0.5</v>
+        <v>0.5833333333333334</v>
       </c>
     </row>
     <row r="204" spans="1:6">
@@ -5513,19 +5513,19 @@
         <v>208</v>
       </c>
       <c r="B204">
-        <v>0.4201228145170336</v>
+        <v>0.4005159968106425</v>
       </c>
       <c r="C204">
-        <v>0.2994594594594595</v>
+        <v>0.2883156297420334</v>
       </c>
       <c r="D204">
-        <v>0.3516758379189595</v>
+        <v>0.2961480740370185</v>
       </c>
       <c r="E204">
-        <v>0.1933007676203768</v>
+        <v>0.1826923076923077</v>
       </c>
       <c r="F204">
-        <v>0.6642685851318945</v>
+        <v>0.6834532374100719</v>
       </c>
     </row>
     <row r="205" spans="1:6">
@@ -5533,19 +5533,19 @@
         <v>209</v>
       </c>
       <c r="B205">
-        <v>0.5321965897693079</v>
+        <v>0.3211634904714142</v>
       </c>
       <c r="C205">
-        <v>0.005882352941176471</v>
+        <v>0.002574002574002574</v>
       </c>
       <c r="D205">
-        <v>0.3236618309154577</v>
+        <v>0.2246123061530765</v>
       </c>
       <c r="E205">
-        <v>0.002952029520295203</v>
+        <v>0.001291155584247902</v>
       </c>
       <c r="F205">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="206" spans="1:6">
@@ -5553,16 +5553,16 @@
         <v>210</v>
       </c>
       <c r="B206">
-        <v>0.3614916286149163</v>
+        <v>0.3406356454301659</v>
       </c>
       <c r="C206">
-        <v>0.01773835920177384</v>
+        <v>0.01731601731601732</v>
       </c>
       <c r="D206">
-        <v>0.3351675837918959</v>
+        <v>0.3186593296648324</v>
       </c>
       <c r="E206">
-        <v>0.009056603773584906</v>
+        <v>0.008836524300441826</v>
       </c>
       <c r="F206">
         <v>0.4285714285714285</v>
@@ -5573,19 +5573,19 @@
         <v>211</v>
       </c>
       <c r="B207">
-        <v>0.08575484301937206</v>
+        <v>0.3124582498329993</v>
       </c>
       <c r="C207">
-        <v>0</v>
+        <v>0.001268230818008878</v>
       </c>
       <c r="D207">
-        <v>0.3256628314157078</v>
+        <v>0.2121060530265133</v>
       </c>
       <c r="E207">
-        <v>0</v>
+        <v>0.0006353240152477764</v>
       </c>
       <c r="F207">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="208" spans="1:6">
@@ -5593,16 +5593,16 @@
         <v>212</v>
       </c>
       <c r="B208">
-        <v>0.6095524382097528</v>
+        <v>0.7694555778223113</v>
       </c>
       <c r="C208">
-        <v>0.005016722408026756</v>
+        <v>0.004137931034482759</v>
       </c>
       <c r="D208">
-        <v>0.4047023511755878</v>
+        <v>0.2776388194097049</v>
       </c>
       <c r="E208">
-        <v>0.002514668901927913</v>
+        <v>0.002073255010366275</v>
       </c>
       <c r="F208">
         <v>1</v>
@@ -5613,19 +5613,19 @@
         <v>213</v>
       </c>
       <c r="B209">
-        <v>0.2565854071440664</v>
+        <v>0.4378703233451837</v>
       </c>
       <c r="C209">
-        <v>0.01018181818181818</v>
+        <v>0.02392947103274559</v>
       </c>
       <c r="D209">
-        <v>0.319159579789895</v>
+        <v>0.2246123061530765</v>
       </c>
       <c r="E209">
-        <v>0.005204460966542751</v>
+        <v>0.01219512195121951</v>
       </c>
       <c r="F209">
-        <v>0.2333333333333333</v>
+        <v>0.6333333333333333</v>
       </c>
     </row>
     <row r="210" spans="1:6">
@@ -5633,19 +5633,19 @@
         <v>214</v>
       </c>
       <c r="B210">
-        <v>0.7118177265898848</v>
+        <v>0.2238357536304456</v>
       </c>
       <c r="C210">
-        <v>0.002830856334041048</v>
+        <v>0.001242236024844721</v>
       </c>
       <c r="D210">
-        <v>0.2951475737868934</v>
+        <v>0.1955977988994497</v>
       </c>
       <c r="E210">
-        <v>0.001417434443656981</v>
+        <v>0.0006218905472636816</v>
       </c>
       <c r="F210">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="211" spans="1:6">
@@ -5653,19 +5653,19 @@
         <v>215</v>
       </c>
       <c r="B211">
-        <v>0.7323308270676692</v>
+        <v>0.7209273182957393</v>
       </c>
       <c r="C211">
-        <v>0.004705882352941176</v>
+        <v>0.005547850208044383</v>
       </c>
       <c r="D211">
-        <v>0.3651825912956478</v>
+        <v>0.2826413206603302</v>
       </c>
       <c r="E211">
-        <v>0.002360346184107002</v>
+        <v>0.002781641168289291</v>
       </c>
       <c r="F211">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="212" spans="1:6">
@@ -5673,16 +5673,16 @@
         <v>216</v>
       </c>
       <c r="B212">
-        <v>0.8020077220077221</v>
+        <v>0.7884134784134784</v>
       </c>
       <c r="C212">
-        <v>0.100709219858156</v>
+        <v>0.08543922984356198</v>
       </c>
       <c r="D212">
-        <v>0.3656828414207103</v>
+        <v>0.2396198099049525</v>
       </c>
       <c r="E212">
-        <v>0.0531437125748503</v>
+        <v>0.04471032745591939</v>
       </c>
       <c r="F212">
         <v>0.9594594594594594</v>
@@ -5693,16 +5693,16 @@
         <v>217</v>
       </c>
       <c r="B213">
-        <v>0.8770875083500334</v>
+        <v>0.9291082164328658</v>
       </c>
       <c r="C213">
-        <v>0.005286343612334802</v>
+        <v>0.00398406374501992</v>
       </c>
       <c r="D213">
-        <v>0.4352176088044022</v>
+        <v>0.2496248124062031</v>
       </c>
       <c r="E213">
-        <v>0.00265017667844523</v>
+        <v>0.001996007984031936</v>
       </c>
       <c r="F213">
         <v>1</v>
@@ -5713,19 +5713,19 @@
         <v>218</v>
       </c>
       <c r="B214">
-        <v>0.7207961579509071</v>
+        <v>0.7065186766275346</v>
       </c>
       <c r="C214">
-        <v>0.1578566256335988</v>
+        <v>0.1351511558980439</v>
       </c>
       <c r="D214">
-        <v>0.4182091045522761</v>
+        <v>0.2701350675337669</v>
       </c>
       <c r="E214">
-        <v>0.08678343949044585</v>
+        <v>0.07298335467349552</v>
       </c>
       <c r="F214">
-        <v>0.872</v>
+        <v>0.912</v>
       </c>
     </row>
     <row r="215" spans="1:6">
@@ -5733,19 +5733,19 @@
         <v>219</v>
       </c>
       <c r="B215">
-        <v>0.761122483793927</v>
+        <v>0.6895541908336176</v>
       </c>
       <c r="C215">
-        <v>0.06451612903225806</v>
+        <v>0.05069708491761724</v>
       </c>
       <c r="D215">
-        <v>0.4342171085542771</v>
+        <v>0.2506253126563281</v>
       </c>
       <c r="E215">
-        <v>0.03350515463917526</v>
+        <v>0.02609262883235486</v>
       </c>
       <c r="F215">
-        <v>0.8666666666666667</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="216" spans="1:6">
@@ -5753,19 +5753,19 @@
         <v>220</v>
       </c>
       <c r="B216">
-        <v>0.7258414662260815</v>
+        <v>0.7500537923614847</v>
       </c>
       <c r="C216">
-        <v>0.1707317073170732</v>
+        <v>0.1538461538461539</v>
       </c>
       <c r="D216">
-        <v>0.4217108554277139</v>
+        <v>0.2571285642821411</v>
       </c>
       <c r="E216">
-        <v>0.09489633173843701</v>
+        <v>0.08359133126934984</v>
       </c>
       <c r="F216">
-        <v>0.85</v>
+        <v>0.9642857142857143</v>
       </c>
     </row>
     <row r="217" spans="1:6">
@@ -5773,19 +5773,19 @@
         <v>221</v>
       </c>
       <c r="B217">
-        <v>0.7841174906964381</v>
+        <v>0.8081605528973951</v>
       </c>
       <c r="C217">
-        <v>0.02564102564102564</v>
+        <v>0.024</v>
       </c>
       <c r="D217">
-        <v>0.3536768384192096</v>
+        <v>0.2676338169084542</v>
       </c>
       <c r="E217">
-        <v>0.01300688599846978</v>
+        <v>0.01215395003376097</v>
       </c>
       <c r="F217">
-        <v>0.8947368421052632</v>
+        <v>0.9473684210526315</v>
       </c>
     </row>
     <row r="218" spans="1:6">
@@ -5793,16 +5793,16 @@
         <v>222</v>
       </c>
       <c r="B218">
-        <v>0.9160821643286572</v>
+        <v>0.8919505678022712</v>
       </c>
       <c r="C218">
-        <v>0.004792332268370607</v>
+        <v>0.003970880211780278</v>
       </c>
       <c r="D218">
-        <v>0.376688344172086</v>
+        <v>0.2471235617808905</v>
       </c>
       <c r="E218">
-        <v>0.002401921537229784</v>
+        <v>0.001989389920424403</v>
       </c>
       <c r="F218">
         <v>1</v>
@@ -5813,19 +5813,19 @@
         <v>223</v>
       </c>
       <c r="B219">
-        <v>0.7629319646104996</v>
+        <v>0.7814359258916735</v>
       </c>
       <c r="C219">
-        <v>0.04593929450369155</v>
+        <v>0.03944020356234097</v>
       </c>
       <c r="D219">
-        <v>0.4182091045522761</v>
+        <v>0.2446223111555778</v>
       </c>
       <c r="E219">
-        <v>0.02360876897133221</v>
+        <v>0.02014294996751137</v>
       </c>
       <c r="F219">
-        <v>0.8484848484848485</v>
+        <v>0.9393939393939394</v>
       </c>
     </row>
     <row r="220" spans="1:6">
@@ -5833,19 +5833,19 @@
         <v>224</v>
       </c>
       <c r="B220">
-        <v>0.404490092819699</v>
+        <v>0.5506630837301014</v>
       </c>
       <c r="C220">
-        <v>0.06390704429920116</v>
+        <v>0.08748481166464156</v>
       </c>
       <c r="D220">
-        <v>0.3551775887943972</v>
+        <v>0.248624312156078</v>
       </c>
       <c r="E220">
-        <v>0.03410852713178295</v>
+        <v>0.04618345093008339</v>
       </c>
       <c r="F220">
-        <v>0.5057471264367817</v>
+        <v>0.8275862068965517</v>
       </c>
     </row>
     <row r="221" spans="1:6">
@@ -5853,16 +5853,16 @@
         <v>225</v>
       </c>
       <c r="B221">
-        <v>0.532032032032032</v>
+        <v>0.9474474474474475</v>
       </c>
       <c r="C221">
-        <v>0.001610305958132045</v>
+        <v>0.001380262249827467</v>
       </c>
       <c r="D221">
-        <v>0.3796898449224612</v>
+        <v>0.2761380690345173</v>
       </c>
       <c r="E221">
-        <v>0.0008058017727639</v>
+        <v>0.0006906077348066298</v>
       </c>
       <c r="F221">
         <v>1</v>
@@ -5873,16 +5873,16 @@
         <v>226</v>
       </c>
       <c r="B222">
-        <v>0.710960960960961</v>
+        <v>0.9234234234234234</v>
       </c>
       <c r="C222">
-        <v>0.001350438892640108</v>
+        <v>0.001243008079552517</v>
       </c>
       <c r="D222">
-        <v>0.2601300650325162</v>
+        <v>0.1960980490245122</v>
       </c>
       <c r="E222">
-        <v>0.0006756756756756757</v>
+        <v>0.0006218905472636816</v>
       </c>
       <c r="F222">
         <v>1</v>
@@ -5893,16 +5893,16 @@
         <v>227</v>
       </c>
       <c r="B223">
-        <v>0.7317511346444781</v>
+        <v>0.7897440746343923</v>
       </c>
       <c r="C223">
-        <v>0.02059025394646534</v>
+        <v>0.01897533206831119</v>
       </c>
       <c r="D223">
-        <v>0.2861430715357679</v>
+        <v>0.224112056028014</v>
       </c>
       <c r="E223">
-        <v>0.01040943789035392</v>
+        <v>0.009584664536741214</v>
       </c>
       <c r="F223">
         <v>0.9375</v>
@@ -5913,16 +5913,16 @@
         <v>228</v>
       </c>
       <c r="B224">
-        <v>0.7807928531546622</v>
+        <v>0.7498045784477946</v>
       </c>
       <c r="C224">
-        <v>0.01158580738595221</v>
+        <v>0.01075991930060525</v>
       </c>
       <c r="D224">
-        <v>0.3171585792896448</v>
+        <v>0.2641320660330165</v>
       </c>
       <c r="E224">
-        <v>0.005830903790087463</v>
+        <v>0.005412719891745603</v>
       </c>
       <c r="F224">
         <v>0.8888888888888888</v>
@@ -5933,19 +5933,19 @@
         <v>229</v>
       </c>
       <c r="B225">
-        <v>0.7322445561139028</v>
+        <v>0.7501675041876046</v>
       </c>
       <c r="C225">
-        <v>0.009485094850948509</v>
+        <v>0.01026298909557409</v>
       </c>
       <c r="D225">
-        <v>0.2686343171585793</v>
+        <v>0.2281140570285143</v>
       </c>
       <c r="E225">
-        <v>0.004771642808452625</v>
+        <v>0.005161290322580645</v>
       </c>
       <c r="F225">
-        <v>0.7777777777777778</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="226" spans="1:6">
@@ -5953,16 +5953,16 @@
         <v>230</v>
       </c>
       <c r="B226">
-        <v>0.6225745325922183</v>
+        <v>0.5698206164729662</v>
       </c>
       <c r="C226">
-        <v>0.02010723860589812</v>
+        <v>0.01920614596670935</v>
       </c>
       <c r="D226">
-        <v>0.2686343171585793</v>
+        <v>0.2336168084042021</v>
       </c>
       <c r="E226">
-        <v>0.01019021739130435</v>
+        <v>0.009727626459143969</v>
       </c>
       <c r="F226">
         <v>0.75</v>
@@ -5973,19 +5973,19 @@
         <v>231</v>
       </c>
       <c r="B227">
-        <v>0.6283406925400883</v>
+        <v>0.6798745061584941</v>
       </c>
       <c r="C227">
-        <v>0.0136986301369863</v>
+        <v>0.01415701415701416</v>
       </c>
       <c r="D227">
-        <v>0.279639819909955</v>
+        <v>0.2336168084042021</v>
       </c>
       <c r="E227">
-        <v>0.006910850034554251</v>
+        <v>0.007138221933809215</v>
       </c>
       <c r="F227">
-        <v>0.7692307692307693</v>
+        <v>0.8461538461538461</v>
       </c>
     </row>
     <row r="228" spans="1:6">
@@ -5993,19 +5993,19 @@
         <v>232</v>
       </c>
       <c r="B228">
-        <v>0.6885118149824032</v>
+        <v>0.587430869783811</v>
       </c>
       <c r="C228">
-        <v>0.0115190784737221</v>
+        <v>0.01005025125628141</v>
       </c>
       <c r="D228">
-        <v>0.3131565782891446</v>
+        <v>0.3101550775387694</v>
       </c>
       <c r="E228">
-        <v>0.005801305293691081</v>
+        <v>0.005061460592913955</v>
       </c>
       <c r="F228">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="229" spans="1:6">
@@ -6013,19 +6013,19 @@
         <v>233</v>
       </c>
       <c r="B229">
-        <v>0.6782709693621296</v>
+        <v>0.7117654445002511</v>
       </c>
       <c r="C229">
-        <v>0.01073825503355705</v>
+        <v>0.009702009702009701</v>
       </c>
       <c r="D229">
-        <v>0.2626313156578289</v>
+        <v>0.2851425712856428</v>
       </c>
       <c r="E229">
-        <v>0.005398110661268556</v>
+        <v>0.004878048780487805</v>
       </c>
       <c r="F229">
-        <v>1</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="230" spans="1:6">
@@ -6033,16 +6033,16 @@
         <v>234</v>
       </c>
       <c r="B230">
-        <v>0.8436404606910365</v>
+        <v>0.9183775663495243</v>
       </c>
       <c r="C230">
-        <v>0.003236245954692557</v>
+        <v>0.002772002772002772</v>
       </c>
       <c r="D230">
-        <v>0.3836918459229615</v>
+        <v>0.2801400700350175</v>
       </c>
       <c r="E230">
-        <v>0.001620745542949757</v>
+        <v>0.001387925052047189</v>
       </c>
       <c r="F230">
         <v>1</v>
@@ -6053,16 +6053,16 @@
         <v>235</v>
       </c>
       <c r="B231">
-        <v>0.7369869869869869</v>
+        <v>0.6118618618618619</v>
       </c>
       <c r="C231">
-        <v>0.001523229246001523</v>
+        <v>0.001260239445494644</v>
       </c>
       <c r="D231">
-        <v>0.3441720860430215</v>
+        <v>0.2071035517758879</v>
       </c>
       <c r="E231">
-        <v>0.0007621951219512195</v>
+        <v>0.0006305170239596469</v>
       </c>
       <c r="F231">
         <v>1</v>
@@ -6073,16 +6073,16 @@
         <v>236</v>
       </c>
       <c r="B232">
-        <v>0.9234962406015037</v>
+        <v>0.8803258145363408</v>
       </c>
       <c r="C232">
-        <v>0.005629838142153413</v>
+        <v>0.005722460658082976</v>
       </c>
       <c r="D232">
-        <v>0.2931465732866433</v>
+        <v>0.3046523261630815</v>
       </c>
       <c r="E232">
-        <v>0.002822865208186309</v>
+        <v>0.002869440459110474</v>
       </c>
       <c r="F232">
         <v>1</v>
@@ -6093,16 +6093,16 @@
         <v>237</v>
       </c>
       <c r="B233">
-        <v>0.6846846846846847</v>
+        <v>0.8498498498498499</v>
       </c>
       <c r="C233">
-        <v>0.001430615164520744</v>
+        <v>0.001371742112482853</v>
       </c>
       <c r="D233">
-        <v>0.3016508254127064</v>
+        <v>0.2716358179089545</v>
       </c>
       <c r="E233">
-        <v>0.0007158196134574087</v>
+        <v>0.0006863417982155113</v>
       </c>
       <c r="F233">
         <v>1</v>
@@ -6113,19 +6113,19 @@
         <v>238</v>
       </c>
       <c r="B234">
-        <v>0.7157155566853075</v>
+        <v>0.7696921072699542</v>
       </c>
       <c r="C234">
-        <v>0.03862660944206009</v>
+        <v>0.04386566141192598</v>
       </c>
       <c r="D234">
-        <v>0.327663831915958</v>
+        <v>0.3021510755377689</v>
       </c>
       <c r="E234">
-        <v>0.01976573938506589</v>
+        <v>0.02242466713384723</v>
       </c>
       <c r="F234">
-        <v>0.84375</v>
+        <v>1</v>
       </c>
     </row>
     <row r="235" spans="1:6">
@@ -6133,19 +6133,19 @@
         <v>239</v>
       </c>
       <c r="B235">
-        <v>0.7758098903282924</v>
+        <v>0.7705250510416103</v>
       </c>
       <c r="C235">
-        <v>0.07654836464857341</v>
+        <v>0.07186440677966102</v>
       </c>
       <c r="D235">
-        <v>0.336168084042021</v>
+        <v>0.3151575787893947</v>
       </c>
       <c r="E235">
-        <v>0.03985507246376811</v>
+        <v>0.03737658674188998</v>
       </c>
       <c r="F235">
-        <v>0.9649122807017544</v>
+        <v>0.9298245614035088</v>
       </c>
     </row>
     <row r="236" spans="1:6">
@@ -6153,19 +6153,19 @@
         <v>240</v>
       </c>
       <c r="B236">
-        <v>0.7909227683049147</v>
+        <v>0.7352056168505516</v>
       </c>
       <c r="C236">
-        <v>0.007097232079488999</v>
+        <v>0.005865102639296188</v>
       </c>
       <c r="D236">
-        <v>0.3001500750375188</v>
+        <v>0.3216608304152076</v>
       </c>
       <c r="E236">
-        <v>0.003561253561253561</v>
+        <v>0.002943340691685063</v>
       </c>
       <c r="F236">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="237" spans="1:6">
@@ -6173,16 +6173,16 @@
         <v>241</v>
       </c>
       <c r="B237">
-        <v>0.9416916916916918</v>
+        <v>0.9156656656656657</v>
       </c>
       <c r="C237">
-        <v>0.001437814521926672</v>
+        <v>0.001256281407035176</v>
       </c>
       <c r="D237">
-        <v>0.3051525762881441</v>
+        <v>0.2046023011505753</v>
       </c>
       <c r="E237">
-        <v>0.0007194244604316547</v>
+        <v>0.0006285355122564425</v>
       </c>
       <c r="F237">
         <v>1</v>
@@ -6193,16 +6193,16 @@
         <v>242</v>
       </c>
       <c r="B238">
-        <v>0.9444444444444444</v>
+        <v>0.9101601601601602</v>
       </c>
       <c r="C238">
-        <v>0.001552795031055901</v>
+        <v>0.001301236174365647</v>
       </c>
       <c r="D238">
-        <v>0.3566783391695848</v>
+        <v>0.2321160580290145</v>
       </c>
       <c r="E238">
-        <v>0.000777000777000777</v>
+        <v>0.0006510416666666666</v>
       </c>
       <c r="F238">
         <v>1</v>
@@ -6213,19 +6213,19 @@
         <v>243</v>
       </c>
       <c r="B239">
-        <v>0.8012431928322814</v>
+        <v>0.7763793361866538</v>
       </c>
       <c r="C239">
-        <v>0.08113879003558719</v>
+        <v>0.08241353936718175</v>
       </c>
       <c r="D239">
-        <v>0.3541770885442722</v>
+        <v>0.3761880940470235</v>
       </c>
       <c r="E239">
-        <v>0.04244229337304542</v>
+        <v>0.04317656129529684</v>
       </c>
       <c r="F239">
-        <v>0.9193548387096774</v>
+        <v>0.9032258064516129</v>
       </c>
     </row>
     <row r="240" spans="1:6">
@@ -6233,16 +6233,16 @@
         <v>244</v>
       </c>
       <c r="B240">
-        <v>0.7748618784530387</v>
+        <v>0.7307257659467604</v>
       </c>
       <c r="C240">
-        <v>0.0113314447592068</v>
+        <v>0.0113960113960114</v>
       </c>
       <c r="D240">
-        <v>0.3016508254127064</v>
+        <v>0.3056528264132066</v>
       </c>
       <c r="E240">
-        <v>0.005698005698005698</v>
+        <v>0.005730659025787965</v>
       </c>
       <c r="F240">
         <v>1</v>
@@ -6253,19 +6253,19 @@
         <v>245</v>
       </c>
       <c r="B241">
-        <v>0.7645618974065124</v>
+        <v>0.793723062358305</v>
       </c>
       <c r="C241">
-        <v>0.04884488448844884</v>
+        <v>0.049273531269741</v>
       </c>
       <c r="D241">
-        <v>0.2791395697848925</v>
+        <v>0.2471235617808905</v>
       </c>
       <c r="E241">
-        <v>0.02510176390773406</v>
+        <v>0.02529182879377432</v>
       </c>
       <c r="F241">
-        <v>0.9024390243902439</v>
+        <v>0.9512195121951219</v>
       </c>
     </row>
     <row r="242" spans="1:6">
@@ -6273,16 +6273,16 @@
         <v>246</v>
       </c>
       <c r="B242">
-        <v>0.9144144144144144</v>
+        <v>0.6413913913913913</v>
       </c>
       <c r="C242">
-        <v>0.001374570446735395</v>
+        <v>0.001291155584247902</v>
       </c>
       <c r="D242">
-        <v>0.2731365682841421</v>
+        <v>0.2261130565282641</v>
       </c>
       <c r="E242">
-        <v>0.000687757909215956</v>
+        <v>0.0006459948320413437</v>
       </c>
       <c r="F242">
         <v>1</v>
@@ -6293,16 +6293,16 @@
         <v>247</v>
       </c>
       <c r="B243">
-        <v>0.7207207207207207</v>
+        <v>0.9211711711711712</v>
       </c>
       <c r="C243">
-        <v>0.001428571428571429</v>
+        <v>0.001344086021505376</v>
       </c>
       <c r="D243">
-        <v>0.3006503251625813</v>
+        <v>0.2566283141570785</v>
       </c>
       <c r="E243">
-        <v>0.0007147962830593281</v>
+        <v>0.0006724949562878278</v>
       </c>
       <c r="F243">
         <v>1</v>
@@ -6313,16 +6313,16 @@
         <v>248</v>
       </c>
       <c r="B244">
-        <v>0.6333833833833833</v>
+        <v>0.3941441441441441</v>
       </c>
       <c r="C244">
-        <v>0.001420454545454545</v>
+        <v>0.001407459535538353</v>
       </c>
       <c r="D244">
-        <v>0.296648324162081</v>
+        <v>0.2901450725362681</v>
       </c>
       <c r="E244">
-        <v>0.0007107320540156361</v>
+        <v>0.0007042253521126761</v>
       </c>
       <c r="F244">
         <v>1</v>
@@ -6333,16 +6333,16 @@
         <v>249</v>
       </c>
       <c r="B245">
-        <v>0.7939006836991723</v>
+        <v>0.7542101475350846</v>
       </c>
       <c r="C245">
-        <v>0.01846590909090909</v>
+        <v>0.01782042494859493</v>
       </c>
       <c r="D245">
-        <v>0.3086543271635818</v>
+        <v>0.2831415707853927</v>
       </c>
       <c r="E245">
-        <v>0.009325681492109038</v>
+        <v>0.008996539792387544</v>
       </c>
       <c r="F245">
         <v>0.9285714285714286</v>
@@ -6353,19 +6353,19 @@
         <v>250</v>
       </c>
       <c r="B246">
-        <v>0.77300979407333</v>
+        <v>0.7564038171772979</v>
       </c>
       <c r="C246">
-        <v>0.009810791871058164</v>
+        <v>0.009975062344139651</v>
       </c>
       <c r="D246">
-        <v>0.2931465732866433</v>
+        <v>0.2056028014007004</v>
       </c>
       <c r="E246">
-        <v>0.004933051444679351</v>
+        <v>0.005012531328320802</v>
       </c>
       <c r="F246">
-        <v>0.875</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247" spans="1:6">
@@ -6373,16 +6373,16 @@
         <v>251</v>
       </c>
       <c r="B247">
-        <v>0.9271771771771772</v>
+        <v>0.7082082082082082</v>
       </c>
       <c r="C247">
-        <v>0.001439884809215263</v>
+        <v>0.00136332651670075</v>
       </c>
       <c r="D247">
-        <v>0.3061530765382691</v>
+        <v>0.2671335667833917</v>
       </c>
       <c r="E247">
-        <v>0.0007204610951008645</v>
+        <v>0.0006821282401091405</v>
       </c>
       <c r="F247">
         <v>1</v>
@@ -6393,19 +6393,19 @@
         <v>252</v>
       </c>
       <c r="B248">
-        <v>0.5014753892516323</v>
+        <v>0.5281265695630336</v>
       </c>
       <c r="C248">
-        <v>0.007704160246533128</v>
+        <v>0.01049475262368816</v>
       </c>
       <c r="D248">
-        <v>0.3556778389194598</v>
+        <v>0.3396698349174587</v>
       </c>
       <c r="E248">
-        <v>0.003875968992248062</v>
+        <v>0.005279034690799397</v>
       </c>
       <c r="F248">
-        <v>0.625</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="249" spans="1:6">
@@ -6413,19 +6413,19 @@
         <v>253</v>
       </c>
       <c r="B249">
-        <v>0.3829032954160115</v>
+        <v>0.484131754986282</v>
       </c>
       <c r="C249">
-        <v>0.02565930149679259</v>
+        <v>0.02992518703241895</v>
       </c>
       <c r="D249">
-        <v>0.3161580790395198</v>
+        <v>0.2216108054027013</v>
       </c>
       <c r="E249">
-        <v>0.01313868613138686</v>
+        <v>0.01527689369828135</v>
       </c>
       <c r="F249">
-        <v>0.5454545454545454</v>
+        <v>0.7272727272727273</v>
       </c>
     </row>
     <row r="250" spans="1:6">
@@ -6433,19 +6433,19 @@
         <v>254</v>
       </c>
       <c r="B250">
-        <v>0.4437906604448381</v>
+        <v>0.4805979427092203</v>
       </c>
       <c r="C250">
-        <v>0.1939024390243902</v>
+        <v>0.2320499479708637</v>
       </c>
       <c r="D250">
-        <v>0.3386693346673337</v>
+        <v>0.2616308154077038</v>
       </c>
       <c r="E250">
-        <v>0.1162280701754386</v>
+        <v>0.1351515151515152</v>
       </c>
       <c r="F250">
-        <v>0.5845588235294118</v>
+        <v>0.8198529411764706</v>
       </c>
     </row>
     <row r="251" spans="1:6">
@@ -6453,19 +6453,19 @@
         <v>255</v>
       </c>
       <c r="B251">
-        <v>0.1026539809714572</v>
+        <v>0.3507761642463695</v>
       </c>
       <c r="C251">
-        <v>0</v>
+        <v>0.001232285890326556</v>
       </c>
       <c r="D251">
-        <v>0.3181590795397699</v>
+        <v>0.1890945472736368</v>
       </c>
       <c r="E251">
-        <v>0</v>
+        <v>0.0006169031462060457</v>
       </c>
       <c r="F251">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="252" spans="1:6">
@@ -6473,19 +6473,19 @@
         <v>256</v>
       </c>
       <c r="B252">
-        <v>0.4564046484298492</v>
+        <v>0.4965136776131096</v>
       </c>
       <c r="C252">
-        <v>0.2021893110109466</v>
+        <v>0.2287323943661972</v>
       </c>
       <c r="D252">
-        <v>0.3801900950475238</v>
+        <v>0.3151575787893947</v>
       </c>
       <c r="E252">
-        <v>0.1218944099378882</v>
+        <v>0.1344370860927152</v>
       </c>
       <c r="F252">
-        <v>0.5924528301886792</v>
+        <v>0.7660377358490567</v>
       </c>
     </row>
     <row r="253" spans="1:6">
@@ -6493,19 +6493,19 @@
         <v>257</v>
       </c>
       <c r="B253">
-        <v>0.4170774238549175</v>
+        <v>0.4659090909090909</v>
       </c>
       <c r="C253">
-        <v>0.03269367448471926</v>
+        <v>0.03877005347593583</v>
       </c>
       <c r="D253">
-        <v>0.319159579789895</v>
+        <v>0.2806403201600801</v>
       </c>
       <c r="E253">
-        <v>0.01687454145267792</v>
+        <v>0.01997245179063361</v>
       </c>
       <c r="F253">
-        <v>0.5227272727272727</v>
+        <v>0.6590909090909091</v>
       </c>
     </row>
     <row r="254" spans="1:6">
@@ -6513,16 +6513,16 @@
         <v>258</v>
       </c>
       <c r="B254">
-        <v>0.7712410102023751</v>
+        <v>0.7430590399732397</v>
       </c>
       <c r="C254">
-        <v>0.008778346744696415</v>
+        <v>0.007425742574257425</v>
       </c>
       <c r="D254">
-        <v>0.3221610805402702</v>
+        <v>0.1975987993996998</v>
       </c>
       <c r="E254">
-        <v>0.00440852314474651</v>
+        <v>0.003726708074534161</v>
       </c>
       <c r="F254">
         <v>1</v>
@@ -6533,16 +6533,16 @@
         <v>259</v>
       </c>
       <c r="B255">
-        <v>0.8240647682858737</v>
+        <v>0.8568118369625907</v>
       </c>
       <c r="C255">
-        <v>0.0124052377670572</v>
+        <v>0.01095556908094948</v>
       </c>
       <c r="D255">
-        <v>0.2831415707853927</v>
+        <v>0.1870935467733867</v>
       </c>
       <c r="E255">
-        <v>0.00624133148404993</v>
+        <v>0.00550795593635251</v>
       </c>
       <c r="F255">
         <v>1</v>
@@ -6553,16 +6553,16 @@
         <v>260</v>
       </c>
       <c r="B256">
-        <v>0.8054858672018732</v>
+        <v>0.8177788927914367</v>
       </c>
       <c r="C256">
-        <v>0.008771929824561403</v>
+        <v>0.007722007722007722</v>
       </c>
       <c r="D256">
-        <v>0.3216608304152076</v>
+        <v>0.2286143071535768</v>
       </c>
       <c r="E256">
-        <v>0.004405286343612335</v>
+        <v>0.003875968992248062</v>
       </c>
       <c r="F256">
         <v>1</v>
@@ -6573,16 +6573,16 @@
         <v>261</v>
       </c>
       <c r="B257">
-        <v>0.8617243686235158</v>
+        <v>0.9013212911858171</v>
       </c>
       <c r="C257">
-        <v>0.008403361344537815</v>
+        <v>0.007357449417535254</v>
       </c>
       <c r="D257">
-        <v>0.2916458229114557</v>
+        <v>0.1900950475237619</v>
       </c>
       <c r="E257">
-        <v>0.004219409282700422</v>
+        <v>0.003692307692307692</v>
       </c>
       <c r="F257">
         <v>1</v>
@@ -6593,19 +6593,19 @@
         <v>262</v>
       </c>
       <c r="B258">
-        <v>0.7237434199354729</v>
+        <v>0.7719406237618157</v>
       </c>
       <c r="C258">
-        <v>0.04375804375804376</v>
+        <v>0.04281345565749235</v>
       </c>
       <c r="D258">
-        <v>0.2566283141570785</v>
+        <v>0.2171085542771386</v>
       </c>
       <c r="E258">
-        <v>0.02239789196310936</v>
+        <v>0.02188868042526579</v>
       </c>
       <c r="F258">
-        <v>0.9444444444444444</v>
+        <v>0.9722222222222222</v>
       </c>
     </row>
     <row r="259" spans="1:6">
@@ -6613,16 +6613,16 @@
         <v>263</v>
       </c>
       <c r="B259">
-        <v>0.8221719457013575</v>
+        <v>0.8886877828054298</v>
       </c>
       <c r="C259">
-        <v>0.01374570446735395</v>
+        <v>0.0130039011703511</v>
       </c>
       <c r="D259">
-        <v>0.2821410705352677</v>
+        <v>0.2406203101550775</v>
       </c>
       <c r="E259">
-        <v>0.006920415224913495</v>
+        <v>0.006544502617801047</v>
       </c>
       <c r="F259">
         <v>1</v>
@@ -6633,19 +6633,19 @@
         <v>264</v>
       </c>
       <c r="B260">
-        <v>0.7469286801478583</v>
+        <v>0.7877165325795463</v>
       </c>
       <c r="C260">
-        <v>0.04020100502512563</v>
+        <v>0.03927272727272727</v>
       </c>
       <c r="D260">
-        <v>0.3311655827913957</v>
+        <v>0.3391695847923962</v>
       </c>
       <c r="E260">
-        <v>0.02051282051282051</v>
+        <v>0.0200445434298441</v>
       </c>
       <c r="F260">
-        <v>1</v>
+        <v>0.9642857142857143</v>
       </c>
     </row>
     <row r="261" spans="1:6">
@@ -6653,16 +6653,16 @@
         <v>265</v>
       </c>
       <c r="B261">
-        <v>0.8930005017561465</v>
+        <v>0.7640909851145676</v>
       </c>
       <c r="C261">
-        <v>0.008895478131949592</v>
+        <v>0.007551919446192574</v>
       </c>
       <c r="D261">
-        <v>0.3311655827913957</v>
+        <v>0.2111055527763882</v>
       </c>
       <c r="E261">
-        <v>0.004467609828741623</v>
+        <v>0.003790271636133923</v>
       </c>
       <c r="F261">
         <v>1</v>
@@ -6673,19 +6673,19 @@
         <v>266</v>
       </c>
       <c r="B262">
-        <v>0.7776659959758552</v>
+        <v>0.5998948234863728</v>
       </c>
       <c r="C262">
-        <v>0.01453104359313078</v>
+        <v>0.0136986301369863</v>
       </c>
       <c r="D262">
-        <v>0.2536268134067033</v>
+        <v>0.3516758379189595</v>
       </c>
       <c r="E262">
-        <v>0.007318695941450432</v>
+        <v>0.006907137375287797</v>
       </c>
       <c r="F262">
-        <v>1</v>
+        <v>0.8181818181818182</v>
       </c>
     </row>
     <row r="263" spans="1:6">
@@ -6693,19 +6693,19 @@
         <v>267</v>
       </c>
       <c r="B263">
-        <v>0.8215219961264684</v>
+        <v>0.8095272530623538</v>
       </c>
       <c r="C263">
-        <v>0.1138790035587189</v>
+        <v>0.1009055627425614</v>
       </c>
       <c r="D263">
-        <v>0.3771885942971486</v>
+        <v>0.3046523261630815</v>
       </c>
       <c r="E263">
-        <v>0.06051437216338881</v>
+        <v>0.05331510594668489</v>
       </c>
       <c r="F263">
-        <v>0.963855421686747</v>
+        <v>0.9397590361445783</v>
       </c>
     </row>
     <row r="264" spans="1:6">
@@ -6713,16 +6713,16 @@
         <v>268</v>
       </c>
       <c r="B264">
-        <v>0.8955410821643286</v>
+        <v>0.6452905811623246</v>
       </c>
       <c r="C264">
-        <v>0.004395604395604396</v>
+        <v>0.00364741641337386</v>
       </c>
       <c r="D264">
-        <v>0.32016008004002</v>
+        <v>0.1800900450225112</v>
       </c>
       <c r="E264">
-        <v>0.002202643171806168</v>
+        <v>0.001827040194884287</v>
       </c>
       <c r="F264">
         <v>1</v>
@@ -6733,19 +6733,19 @@
         <v>269</v>
       </c>
       <c r="B265">
-        <v>0.4997414995431155</v>
+        <v>0.5282426778242677</v>
       </c>
       <c r="C265">
-        <v>0.08146067415730338</v>
+        <v>0.08109965635738832</v>
       </c>
       <c r="D265">
-        <v>0.3456728364182091</v>
+        <v>0.3311655827913957</v>
       </c>
       <c r="E265">
-        <v>0.04338070306656694</v>
+        <v>0.04312865497076023</v>
       </c>
       <c r="F265">
-        <v>0.6666666666666666</v>
+        <v>0.6781609195402298</v>
       </c>
     </row>
     <row r="266" spans="1:6">
@@ -6753,16 +6753,16 @@
         <v>270</v>
       </c>
       <c r="B266">
-        <v>0.724937343358396</v>
+        <v>0.7302631578947369</v>
       </c>
       <c r="C266">
-        <v>0.006130268199233717</v>
+        <v>0.0053475935828877</v>
       </c>
       <c r="D266">
-        <v>0.351175587793897</v>
+        <v>0.2556278139069535</v>
       </c>
       <c r="E266">
-        <v>0.003074558032282859</v>
+        <v>0.002680965147453083</v>
       </c>
       <c r="F266">
         <v>1</v>
@@ -6773,16 +6773,16 @@
         <v>271</v>
       </c>
       <c r="B267">
-        <v>0.9018871075484303</v>
+        <v>0.8249832999331997</v>
       </c>
       <c r="C267">
-        <v>0.004758128469468675</v>
+        <v>0.004344677769732078</v>
       </c>
       <c r="D267">
-        <v>0.3721860930465233</v>
+        <v>0.3121560780390195</v>
       </c>
       <c r="E267">
-        <v>0.002384737678855326</v>
+        <v>0.002177068214804064</v>
       </c>
       <c r="F267">
         <v>1</v>
@@ -6793,16 +6793,16 @@
         <v>272</v>
       </c>
       <c r="B268">
-        <v>0.8081997327989311</v>
+        <v>0.8547094188376754</v>
       </c>
       <c r="C268">
-        <v>0.004590665646518746</v>
+        <v>0.00395778364116095</v>
       </c>
       <c r="D268">
-        <v>0.3491745872936468</v>
+        <v>0.2446223111555778</v>
       </c>
       <c r="E268">
-        <v>0.002300613496932515</v>
+        <v>0.001982815598149372</v>
       </c>
       <c r="F268">
         <v>1</v>
@@ -6813,19 +6813,19 @@
         <v>273</v>
       </c>
       <c r="B269">
-        <v>0.7800125313283208</v>
+        <v>0.5868421052631578</v>
       </c>
       <c r="C269">
-        <v>0.005912786400591279</v>
+        <v>0.003976143141153081</v>
       </c>
       <c r="D269">
-        <v>0.3271635817908954</v>
+        <v>0.2481240620310155</v>
       </c>
       <c r="E269">
-        <v>0.002965159377316531</v>
+        <v>0.001993355481727575</v>
       </c>
       <c r="F269">
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="270" spans="1:6">
@@ -6833,16 +6833,16 @@
         <v>274</v>
       </c>
       <c r="B270">
-        <v>0.7520875083500332</v>
+        <v>0.6534736138944556</v>
       </c>
       <c r="C270">
-        <v>0.004418262150220913</v>
+        <v>0.004169562195969423</v>
       </c>
       <c r="D270">
-        <v>0.3236618309154577</v>
+        <v>0.2831415707853927</v>
       </c>
       <c r="E270">
-        <v>0.002214022140221402</v>
+        <v>0.002089136490250696</v>
       </c>
       <c r="F270">
         <v>1</v>
@@ -6853,16 +6853,16 @@
         <v>275</v>
       </c>
       <c r="B271">
-        <v>0.6969924812030075</v>
+        <v>0.6459899749373433</v>
       </c>
       <c r="C271">
-        <v>0.006134969325153374</v>
+        <v>0.006254886630179828</v>
       </c>
       <c r="D271">
-        <v>0.3516758379189595</v>
+        <v>0.3641820910455227</v>
       </c>
       <c r="E271">
-        <v>0.003076923076923077</v>
+        <v>0.003137254901960784</v>
       </c>
       <c r="F271">
         <v>1</v>
@@ -6873,16 +6873,16 @@
         <v>276</v>
       </c>
       <c r="B272">
-        <v>0.8890280561122245</v>
+        <v>0.7687040748162992</v>
       </c>
       <c r="C272">
-        <v>0.004431314623338257</v>
+        <v>0.004739336492890996</v>
       </c>
       <c r="D272">
-        <v>0.3256628314157078</v>
+        <v>0.3696848424212106</v>
       </c>
       <c r="E272">
-        <v>0.002220577350111029</v>
+        <v>0.002375296912114014</v>
       </c>
       <c r="F272">
         <v>1</v>
@@ -6893,19 +6893,19 @@
         <v>277</v>
       </c>
       <c r="B273">
-        <v>0.8071169941235828</v>
+        <v>0.5409420074790764</v>
       </c>
       <c r="C273">
-        <v>0.0228494623655914</v>
+        <v>0.01870407481629927</v>
       </c>
       <c r="D273">
-        <v>0.2726363181590795</v>
+        <v>0.2651325662831416</v>
       </c>
       <c r="E273">
-        <v>0.01155676410605031</v>
+        <v>0.00945945945945946</v>
       </c>
       <c r="F273">
-        <v>1</v>
+        <v>0.8235294117647058</v>
       </c>
     </row>
     <row r="274" spans="1:6">
@@ -6913,16 +6913,16 @@
         <v>278</v>
       </c>
       <c r="B274">
-        <v>0.8927855711422846</v>
+        <v>0.7377254509018036</v>
       </c>
       <c r="C274">
-        <v>0.004319654427645789</v>
+        <v>0.004045853000674309</v>
       </c>
       <c r="D274">
-        <v>0.3081540770385193</v>
+        <v>0.2611305652826413</v>
       </c>
       <c r="E274">
-        <v>0.002164502164502165</v>
+        <v>0.002027027027027027</v>
       </c>
       <c r="F274">
         <v>1</v>
@@ -6933,16 +6933,16 @@
         <v>279</v>
       </c>
       <c r="B275">
-        <v>0.8120407481629927</v>
+        <v>0.8137107548430194</v>
       </c>
       <c r="C275">
-        <v>0.004552352048558422</v>
+        <v>0.004135079255685734</v>
       </c>
       <c r="D275">
-        <v>0.343671835917959</v>
+        <v>0.2771385692846423</v>
       </c>
       <c r="E275">
-        <v>0.002281368821292776</v>
+        <v>0.002071823204419889</v>
       </c>
       <c r="F275">
         <v>1</v>
@@ -6953,16 +6953,16 @@
         <v>280</v>
       </c>
       <c r="B276">
-        <v>0.8507014028056111</v>
+        <v>0.7038243152972612</v>
       </c>
       <c r="C276">
-        <v>0.004118050789293068</v>
+        <v>0.00424929178470255</v>
       </c>
       <c r="D276">
-        <v>0.2741370685342671</v>
+        <v>0.296648324162081</v>
       </c>
       <c r="E276">
-        <v>0.002063273727647868</v>
+        <v>0.0021291696238467</v>
       </c>
       <c r="F276">
         <v>1</v>
@@ -6973,19 +6973,19 @@
         <v>281</v>
       </c>
       <c r="B277">
-        <v>0.8269809428284854</v>
+        <v>0.5841524573721163</v>
       </c>
       <c r="C277">
-        <v>0.007304601899196494</v>
+        <v>0.0056777856635912</v>
       </c>
       <c r="D277">
-        <v>0.32016008004002</v>
+        <v>0.2991495747873937</v>
       </c>
       <c r="E277">
-        <v>0.003665689149560118</v>
+        <v>0.002849002849002849</v>
       </c>
       <c r="F277">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="278" spans="1:6">
@@ -6993,16 +6993,16 @@
         <v>282</v>
       </c>
       <c r="B278">
-        <v>0.6480942828485456</v>
+        <v>0.5696088264794383</v>
       </c>
       <c r="C278">
-        <v>0.005835156819839533</v>
+        <v>0.005141388174807198</v>
       </c>
       <c r="D278">
-        <v>0.3181590795397699</v>
+        <v>0.2256128064032016</v>
       </c>
       <c r="E278">
-        <v>0.002928257686676428</v>
+        <v>0.002578981302385558</v>
       </c>
       <c r="F278">
         <v>0.8</v>
@@ -7013,16 +7013,16 @@
         <v>283</v>
       </c>
       <c r="B279">
-        <v>0.751002004008016</v>
+        <v>0.6497160988643954</v>
       </c>
       <c r="C279">
-        <v>0.00453514739229025</v>
+        <v>0.004178272980501393</v>
       </c>
       <c r="D279">
-        <v>0.3411705852926463</v>
+        <v>0.2846423211605803</v>
       </c>
       <c r="E279">
-        <v>0.002272727272727273</v>
+        <v>0.00209351011863224</v>
       </c>
       <c r="F279">
         <v>1</v>
@@ -7033,16 +7033,16 @@
         <v>284</v>
       </c>
       <c r="B280">
-        <v>0.8116232464929859</v>
+        <v>0.7327154308617234</v>
       </c>
       <c r="C280">
-        <v>0.004713275726630008</v>
+        <v>0.004467609828741623</v>
       </c>
       <c r="D280">
-        <v>0.3661830915457729</v>
+        <v>0.3311655827913957</v>
       </c>
       <c r="E280">
-        <v>0.002362204724409449</v>
+        <v>0.002238805970149254</v>
       </c>
       <c r="F280">
         <v>1</v>
@@ -7053,16 +7053,16 @@
         <v>285</v>
       </c>
       <c r="B281">
-        <v>0.8371743486973948</v>
+        <v>0.7742985971943888</v>
       </c>
       <c r="C281">
-        <v>0.004724409448818898</v>
+        <v>0.004807692307692308</v>
       </c>
       <c r="D281">
-        <v>0.3676838419209605</v>
+        <v>0.3786893446723362</v>
       </c>
       <c r="E281">
-        <v>0.002367797947908445</v>
+        <v>0.002409638554216868</v>
       </c>
       <c r="F281">
         <v>1</v>
@@ -7073,16 +7073,16 @@
         <v>286</v>
       </c>
       <c r="B282">
-        <v>0.8016867067468268</v>
+        <v>0.7372244488977955</v>
       </c>
       <c r="C282">
-        <v>0.004618937644341801</v>
+        <v>0.004454342984409799</v>
       </c>
       <c r="D282">
-        <v>0.3531765882941471</v>
+        <v>0.3291645822911456</v>
       </c>
       <c r="E282">
-        <v>0.002314814814814815</v>
+        <v>0.002232142857142857</v>
       </c>
       <c r="F282">
         <v>1</v>
@@ -7093,16 +7093,16 @@
         <v>287</v>
       </c>
       <c r="B283">
-        <v>0.7996826987307949</v>
+        <v>0.7565130260521042</v>
       </c>
       <c r="C283">
-        <v>0.004474272930648769</v>
+        <v>0.004511278195488722</v>
       </c>
       <c r="D283">
-        <v>0.3321660830415208</v>
+        <v>0.3376688344172086</v>
       </c>
       <c r="E283">
-        <v>0.002242152466367713</v>
+        <v>0.002260738507912585</v>
       </c>
       <c r="F283">
         <v>1</v>
@@ -7113,19 +7113,19 @@
         <v>288</v>
       </c>
       <c r="B284">
-        <v>0.6548245614035088</v>
+        <v>0.5781328320802005</v>
       </c>
       <c r="C284">
-        <v>0.006116207951070336</v>
+        <v>0.004428044280442804</v>
       </c>
       <c r="D284">
-        <v>0.3496748374187094</v>
+        <v>0.3251625812906453</v>
       </c>
       <c r="E284">
-        <v>0.003067484662576687</v>
+        <v>0.002220577350111029</v>
       </c>
       <c r="F284">
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="285" spans="1:6">
@@ -7133,16 +7133,16 @@
         <v>289</v>
       </c>
       <c r="B285">
-        <v>0.7823934837092731</v>
+        <v>0.756203007518797</v>
       </c>
       <c r="C285">
-        <v>0.00625</v>
+        <v>0.006509357200976403</v>
       </c>
       <c r="D285">
-        <v>0.3636818409204602</v>
+        <v>0.3891945972986493</v>
       </c>
       <c r="E285">
-        <v>0.003134796238244514</v>
+        <v>0.00326530612244898</v>
       </c>
       <c r="F285">
         <v>1</v>
@@ -7153,16 +7153,16 @@
         <v>290</v>
       </c>
       <c r="B286">
-        <v>0.9061456245824983</v>
+        <v>0.7772211088844355</v>
       </c>
       <c r="C286">
-        <v>0.004514672686230248</v>
+        <v>0.004942339373970346</v>
       </c>
       <c r="D286">
-        <v>0.3381690845422711</v>
+        <v>0.3956978489244622</v>
       </c>
       <c r="E286">
-        <v>0.002262443438914027</v>
+        <v>0.002477291494632535</v>
       </c>
       <c r="F286">
         <v>1</v>
@@ -7173,19 +7173,19 @@
         <v>291</v>
       </c>
       <c r="B287">
-        <v>0.7171583459404942</v>
+        <v>0.5522881996974282</v>
       </c>
       <c r="C287">
-        <v>0.01998572448251249</v>
+        <v>0.0170940170940171</v>
       </c>
       <c r="D287">
-        <v>0.3131565782891446</v>
+        <v>0.3671835917958979</v>
       </c>
       <c r="E287">
-        <v>0.01010830324909747</v>
+        <v>0.00865460267505901</v>
       </c>
       <c r="F287">
-        <v>0.875</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="288" spans="1:6">
@@ -7193,16 +7193,16 @@
         <v>292</v>
       </c>
       <c r="B288">
-        <v>0.9005511022044088</v>
+        <v>0.7547595190380761</v>
       </c>
       <c r="C288">
-        <v>0.004491017964071856</v>
+        <v>0.004273504273504274</v>
       </c>
       <c r="D288">
-        <v>0.3346673336668334</v>
+        <v>0.3006503251625813</v>
       </c>
       <c r="E288">
-        <v>0.002250562640660165</v>
+        <v>0.002141327623126338</v>
       </c>
       <c r="F288">
         <v>1</v>
@@ -7213,16 +7213,16 @@
         <v>293</v>
       </c>
       <c r="B289">
-        <v>0.823062792251169</v>
+        <v>0.8368403473613895</v>
       </c>
       <c r="C289">
-        <v>0.004761904761904762</v>
+        <v>0.004739336492890996</v>
       </c>
       <c r="D289">
-        <v>0.3726863431715858</v>
+        <v>0.3696848424212106</v>
       </c>
       <c r="E289">
-        <v>0.002386634844868735</v>
+        <v>0.002375296912114014</v>
       </c>
       <c r="F289">
         <v>1</v>
@@ -7233,19 +7233,19 @@
         <v>294</v>
       </c>
       <c r="B290">
-        <v>0.8163990633885265</v>
+        <v>0.6329653788258907</v>
       </c>
       <c r="C290">
-        <v>0.008374040474528961</v>
+        <v>0.007880220646178092</v>
       </c>
       <c r="D290">
-        <v>0.2891445722861431</v>
+        <v>0.3701850925462731</v>
       </c>
       <c r="E290">
-        <v>0.004204625087596356</v>
+        <v>0.00395882818685669</v>
       </c>
       <c r="F290">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="291" spans="1:6">
@@ -7253,16 +7253,16 @@
         <v>295</v>
       </c>
       <c r="B291">
-        <v>0.8084502338009352</v>
+        <v>0.6852037408149632</v>
       </c>
       <c r="C291">
-        <v>0.004580152671755725</v>
+        <v>0.00474308300395257</v>
       </c>
       <c r="D291">
-        <v>0.3476738369184592</v>
+        <v>0.3701850925462731</v>
       </c>
       <c r="E291">
-        <v>0.002295332823259373</v>
+        <v>0.002377179080824089</v>
       </c>
       <c r="F291">
         <v>1</v>
@@ -7273,16 +7273,16 @@
         <v>296</v>
       </c>
       <c r="B292">
-        <v>0.6388051367950865</v>
+        <v>0.6538525963149078</v>
       </c>
       <c r="C292">
-        <v>0.01257861635220126</v>
+        <v>0.01108801108801109</v>
       </c>
       <c r="D292">
-        <v>0.3716858429214607</v>
+        <v>0.2861430715357679</v>
       </c>
       <c r="E292">
-        <v>0.006334125098970704</v>
+        <v>0.005578800557880056</v>
       </c>
       <c r="F292">
         <v>0.8888888888888888</v>
@@ -7293,16 +7293,16 @@
         <v>297</v>
       </c>
       <c r="B293">
-        <v>0.825317301269205</v>
+        <v>0.6942217768871075</v>
       </c>
       <c r="C293">
-        <v>0.00477326968973747</v>
+        <v>0.004735595895816891</v>
       </c>
       <c r="D293">
-        <v>0.3741870935467734</v>
+        <v>0.3691845922961481</v>
       </c>
       <c r="E293">
-        <v>0.002392344497607655</v>
+        <v>0.002373417721518987</v>
       </c>
       <c r="F293">
         <v>1</v>
@@ -7313,16 +7313,16 @@
         <v>298</v>
       </c>
       <c r="B294">
-        <v>0.8776276276276277</v>
+        <v>0.8903903903903904</v>
       </c>
       <c r="C294">
-        <v>0.001375515818431912</v>
+        <v>0.001400560224089636</v>
       </c>
       <c r="D294">
-        <v>0.2736368184092046</v>
+        <v>0.2866433216608304</v>
       </c>
       <c r="E294">
-        <v>0.0006882312456985547</v>
+        <v>0.000700770847932726</v>
       </c>
       <c r="F294">
         <v>1</v>
@@ -7333,19 +7333,19 @@
         <v>299</v>
       </c>
       <c r="B295">
-        <v>0.5761523046092184</v>
+        <v>0.58500334001336</v>
       </c>
       <c r="C295">
-        <v>0.002628120893561104</v>
+        <v>0.003799873337555415</v>
       </c>
       <c r="D295">
-        <v>0.2406203101550775</v>
+        <v>0.2131065532766383</v>
       </c>
       <c r="E295">
-        <v>0.001316655694535879</v>
+        <v>0.001903553299492386</v>
       </c>
       <c r="F295">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="296" spans="1:6">
@@ -7353,16 +7353,16 @@
         <v>300</v>
       </c>
       <c r="B296">
-        <v>0.6862086258776329</v>
+        <v>0.7749247743229689</v>
       </c>
       <c r="C296">
-        <v>0.007022471910112359</v>
+        <v>0.006626905235255135</v>
       </c>
       <c r="D296">
-        <v>0.2926463231615808</v>
+        <v>0.2501250625312657</v>
       </c>
       <c r="E296">
-        <v>0.003523608174770966</v>
+        <v>0.003324468085106383</v>
       </c>
       <c r="F296">
         <v>1</v>
@@ -7373,19 +7373,19 @@
         <v>301</v>
       </c>
       <c r="B297">
-        <v>0.7416499665998664</v>
+        <v>0.5596192384769539</v>
       </c>
       <c r="C297">
-        <v>0.004373177842565598</v>
+        <v>0.003316749585406302</v>
       </c>
       <c r="D297">
-        <v>0.3166583291645823</v>
+        <v>0.3986993496748374</v>
       </c>
       <c r="E297">
-        <v>0.002191380569758948</v>
+        <v>0.001662510390689942</v>
       </c>
       <c r="F297">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="298" spans="1:6">
@@ -7393,19 +7393,19 @@
         <v>302</v>
       </c>
       <c r="B298">
-        <v>0.7192395149065185</v>
+        <v>0.6153991915108641</v>
       </c>
       <c r="C298">
-        <v>0.02505219206680585</v>
+        <v>0.02043795620437956</v>
       </c>
       <c r="D298">
-        <v>0.2991495747873937</v>
+        <v>0.328664332166083</v>
       </c>
       <c r="E298">
-        <v>0.01270289343683839</v>
+        <v>0.01037037037037037</v>
       </c>
       <c r="F298">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="299" spans="1:6">
@@ -7413,19 +7413,19 @@
         <v>303</v>
       </c>
       <c r="B299">
-        <v>0.8421843687374749</v>
+        <v>0.6054609218436874</v>
       </c>
       <c r="C299">
-        <v>0.004175365344467641</v>
+        <v>0.002772002772002772</v>
       </c>
       <c r="D299">
-        <v>0.2841420710355178</v>
+        <v>0.2801400700350175</v>
       </c>
       <c r="E299">
-        <v>0.002092050209205021</v>
+        <v>0.001388888888888889</v>
       </c>
       <c r="F299">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="300" spans="1:6">
@@ -7433,19 +7433,19 @@
         <v>304</v>
       </c>
       <c r="B300">
-        <v>0.7251169004676019</v>
+        <v>0.6527221108884436</v>
       </c>
       <c r="C300">
-        <v>0.003014318010550113</v>
+        <v>0.004728132387706856</v>
       </c>
       <c r="D300">
-        <v>0.3381690845422711</v>
+        <v>0.368184092046023</v>
       </c>
       <c r="E300">
-        <v>0.001510574018126888</v>
+        <v>0.002369668246445498</v>
       </c>
       <c r="F300">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="301" spans="1:6">
@@ -7453,19 +7453,19 @@
         <v>305</v>
       </c>
       <c r="B301">
-        <v>0.7757106872975891</v>
+        <v>0.5341129902842749</v>
       </c>
       <c r="C301">
-        <v>0.0177717019822283</v>
+        <v>0.01356443104747551</v>
       </c>
       <c r="D301">
-        <v>0.2811405702851426</v>
+        <v>0.3451725862931466</v>
       </c>
       <c r="E301">
-        <v>0.008971704623878536</v>
+        <v>0.006854531607006854</v>
       </c>
       <c r="F301">
-        <v>0.9285714285714286</v>
+        <v>0.6428571428571429</v>
       </c>
     </row>
     <row r="302" spans="1:6">
@@ -7473,16 +7473,16 @@
         <v>306</v>
       </c>
       <c r="B302">
-        <v>0.7920260782347041</v>
+        <v>0.6211133400200601</v>
       </c>
       <c r="C302">
-        <v>0.00574300071787509</v>
+        <v>0.006024096385542169</v>
       </c>
       <c r="D302">
-        <v>0.3071535767883942</v>
+        <v>0.3396698349174587</v>
       </c>
       <c r="E302">
-        <v>0.002881844380403458</v>
+        <v>0.003023431594860166</v>
       </c>
       <c r="F302">
         <v>0.8</v>
@@ -7493,16 +7493,16 @@
         <v>307</v>
       </c>
       <c r="B303">
-        <v>0.6514629948364888</v>
+        <v>0.6393789443488238</v>
       </c>
       <c r="C303">
-        <v>0.008583690987124463</v>
+        <v>0.008016032064128256</v>
       </c>
       <c r="D303">
-        <v>0.3066533266633317</v>
+        <v>0.2571285642821411</v>
       </c>
       <c r="E303">
-        <v>0.004313443565780014</v>
+        <v>0.004026845637583893</v>
       </c>
       <c r="F303">
         <v>0.8571428571428571</v>
@@ -7513,19 +7513,19 @@
         <v>308</v>
       </c>
       <c r="B304">
-        <v>0.7784736138944555</v>
+        <v>0.5475951903807615</v>
       </c>
       <c r="C304">
-        <v>0.00437636761487965</v>
+        <v>0.002892263195950831</v>
       </c>
       <c r="D304">
-        <v>0.3171585792896448</v>
+        <v>0.3101550775387694</v>
       </c>
       <c r="E304">
-        <v>0.002192982456140351</v>
+        <v>0.001449275362318841</v>
       </c>
       <c r="F304">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="305" spans="1:6">
@@ -7533,19 +7533,19 @@
         <v>309</v>
       </c>
       <c r="B305">
-        <v>0.6823100150981379</v>
+        <v>0.6820793491024996</v>
       </c>
       <c r="C305">
-        <v>0.01568068424803992</v>
+        <v>0.01243008079552517</v>
       </c>
       <c r="D305">
-        <v>0.3091545772886443</v>
+        <v>0.2051025512756378</v>
       </c>
       <c r="E305">
-        <v>0.007907979870596693</v>
+        <v>0.006261740763932373</v>
       </c>
       <c r="F305">
-        <v>0.9166666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="306" spans="1:6">
@@ -7553,16 +7553,16 @@
         <v>310</v>
       </c>
       <c r="B306">
-        <v>0.5892230576441103</v>
+        <v>0.5234335839598997</v>
       </c>
       <c r="C306">
-        <v>0.004447739065974796</v>
+        <v>0.004051316677920324</v>
       </c>
       <c r="D306">
-        <v>0.3281640820410205</v>
+        <v>0.2621310655327664</v>
       </c>
       <c r="E306">
-        <v>0.002230483271375465</v>
+        <v>0.002031144211238998</v>
       </c>
       <c r="F306">
         <v>0.75</v>
@@ -7573,16 +7573,16 @@
         <v>311</v>
       </c>
       <c r="B307">
-        <v>0.5025689223057644</v>
+        <v>0.5759398496240602</v>
       </c>
       <c r="C307">
-        <v>0.004246284501061571</v>
+        <v>0.003807106598984772</v>
       </c>
       <c r="D307">
-        <v>0.2961480740370185</v>
+        <v>0.2146073036518259</v>
       </c>
       <c r="E307">
-        <v>0.0021291696238467</v>
+        <v>0.001908396946564885</v>
       </c>
       <c r="F307">
         <v>0.75</v>
@@ -7593,19 +7593,19 @@
         <v>312</v>
       </c>
       <c r="B308">
-        <v>0.6820567375886526</v>
+        <v>0.6752786220871327</v>
       </c>
       <c r="C308">
-        <v>0.03070481507327285</v>
+        <v>0.02889447236180905</v>
       </c>
       <c r="D308">
-        <v>0.3051525762881441</v>
+        <v>0.2266133066533267</v>
       </c>
       <c r="E308">
-        <v>0.015625</v>
+        <v>0.01467772814294831</v>
       </c>
       <c r="F308">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="309" spans="1:6">
@@ -7613,16 +7613,16 @@
         <v>313</v>
       </c>
       <c r="B309">
-        <v>0.6161779545319641</v>
+        <v>0.6479937080785897</v>
       </c>
       <c r="C309">
-        <v>0.01962158374211633</v>
+        <v>0.01819363222871995</v>
       </c>
       <c r="D309">
-        <v>0.3001500750375188</v>
+        <v>0.2441220610305153</v>
       </c>
       <c r="E309">
-        <v>0.009929078014184398</v>
+        <v>0.009198423127463863</v>
       </c>
       <c r="F309">
         <v>0.8235294117647058</v>
@@ -7633,19 +7633,19 @@
         <v>314</v>
       </c>
       <c r="B310">
-        <v>0.6345934139784947</v>
+        <v>0.5771505376344086</v>
       </c>
       <c r="C310">
-        <v>0.01931649331352155</v>
+        <v>0.01627218934911243</v>
       </c>
       <c r="D310">
-        <v>0.3396698349174587</v>
+        <v>0.3346673336668334</v>
       </c>
       <c r="E310">
-        <v>0.009767092411720512</v>
+        <v>0.008227374719521317</v>
       </c>
       <c r="F310">
-        <v>0.8666666666666667</v>
+        <v>0.7333333333333333</v>
       </c>
     </row>
     <row r="311" spans="1:6">
@@ -7653,16 +7653,16 @@
         <v>315</v>
       </c>
       <c r="B311">
-        <v>0.9041541541541541</v>
+        <v>0.3968968968968969</v>
       </c>
       <c r="C311">
-        <v>0.001469507714915503</v>
+        <v>0.001372683596431023</v>
       </c>
       <c r="D311">
-        <v>0.32016008004002</v>
+        <v>0.272136068034017</v>
       </c>
       <c r="E311">
-        <v>0.0007352941176470588</v>
+        <v>0.0006868131868131869</v>
       </c>
       <c r="F311">
         <v>1</v>
@@ -7673,16 +7673,16 @@
         <v>316</v>
       </c>
       <c r="B312">
-        <v>0.5909090909090909</v>
+        <v>0.6032144650929181</v>
       </c>
       <c r="C312">
-        <v>0.008895478131949592</v>
+        <v>0.008275862068965517</v>
       </c>
       <c r="D312">
-        <v>0.3311655827913957</v>
+        <v>0.2806403201600801</v>
       </c>
       <c r="E312">
-        <v>0.004474272930648769</v>
+        <v>0.004160887656033287</v>
       </c>
       <c r="F312">
         <v>0.75</v>
@@ -7693,19 +7693,19 @@
         <v>317</v>
       </c>
       <c r="B313">
-        <v>0.7371683759449179</v>
+        <v>0.6880085704655978</v>
       </c>
       <c r="C313">
-        <v>0.02351313969571231</v>
+        <v>0.02328589909443726</v>
       </c>
       <c r="D313">
-        <v>0.2936468234117058</v>
+        <v>0.2446223111555778</v>
       </c>
       <c r="E313">
-        <v>0.01192982456140351</v>
+        <v>0.01180327868852459</v>
       </c>
       <c r="F313">
-        <v>0.8095238095238095</v>
+        <v>0.8571428571428571</v>
       </c>
     </row>
     <row r="314" spans="1:6">
@@ -7713,16 +7713,16 @@
         <v>318</v>
       </c>
       <c r="B314">
-        <v>0.8731353987378084</v>
+        <v>0.7415017211703958</v>
       </c>
       <c r="C314">
-        <v>0.009621993127147767</v>
+        <v>0.008991650610147719</v>
       </c>
       <c r="D314">
-        <v>0.2791395697848925</v>
+        <v>0.2281140570285143</v>
       </c>
       <c r="E314">
-        <v>0.004834254143646409</v>
+        <v>0.004516129032258065</v>
       </c>
       <c r="F314">
         <v>1</v>
@@ -7733,19 +7733,19 @@
         <v>319</v>
       </c>
       <c r="B315">
-        <v>0.6864024084295032</v>
+        <v>0.6004348553269777</v>
       </c>
       <c r="C315">
-        <v>0.007407407407407408</v>
+        <v>0.007537688442211055</v>
       </c>
       <c r="D315">
-        <v>0.3296648324162081</v>
+        <v>0.2096048024012006</v>
       </c>
       <c r="E315">
-        <v>0.003720238095238095</v>
+        <v>0.003783102143757881</v>
       </c>
       <c r="F315">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
     </row>
     <row r="316" spans="1:6">
@@ -7753,19 +7753,19 @@
         <v>320</v>
       </c>
       <c r="B316">
-        <v>0.4954545454545454</v>
+        <v>0.380130249867092</v>
       </c>
       <c r="C316">
-        <v>0.01854974704890388</v>
+        <v>0.01344086021505376</v>
       </c>
       <c r="D316">
-        <v>0.4177088544272136</v>
+        <v>0.2656328164082041</v>
       </c>
       <c r="E316">
-        <v>0.009425878320479864</v>
+        <v>0.006807351940095302</v>
       </c>
       <c r="F316">
-        <v>0.5789473684210527</v>
+        <v>0.5263157894736842</v>
       </c>
     </row>
     <row r="317" spans="1:6">
@@ -7773,19 +7773,19 @@
         <v>321</v>
       </c>
       <c r="B317">
-        <v>0.441640024678894</v>
+        <v>0.5305821975433282</v>
       </c>
       <c r="C317">
-        <v>0.01538461538461539</v>
+        <v>0.01745454545454546</v>
       </c>
       <c r="D317">
-        <v>0.295647823911956</v>
+        <v>0.3241620810405202</v>
       </c>
       <c r="E317">
-        <v>0.007790368271954674</v>
+        <v>0.008843036109064112</v>
       </c>
       <c r="F317">
-        <v>0.6111111111111112</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="318" spans="1:6">
@@ -7793,19 +7793,19 @@
         <v>322</v>
       </c>
       <c r="B318">
-        <v>0.8110832497492477</v>
+        <v>0.4942828485456369</v>
       </c>
       <c r="C318">
-        <v>0.006802721088435374</v>
+        <v>0.004261363636363636</v>
       </c>
       <c r="D318">
-        <v>0.2696348174087044</v>
+        <v>0.2986493246623312</v>
       </c>
       <c r="E318">
-        <v>0.003412969283276451</v>
+        <v>0.002138275124732716</v>
       </c>
       <c r="F318">
-        <v>1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="319" spans="1:6">
@@ -7813,16 +7813,16 @@
         <v>323</v>
       </c>
       <c r="B319">
-        <v>0.8897795591182366</v>
+        <v>0.904809619238477</v>
       </c>
       <c r="C319">
-        <v>0.004559270516717325</v>
+        <v>0.004276550249465431</v>
       </c>
       <c r="D319">
-        <v>0.344672336168084</v>
+        <v>0.3011505752876438</v>
       </c>
       <c r="E319">
-        <v>0.002284843869002285</v>
+        <v>0.002142857142857143</v>
       </c>
       <c r="F319">
         <v>1</v>
@@ -7833,16 +7833,16 @@
         <v>324</v>
       </c>
       <c r="B320">
-        <v>0.8460863020572003</v>
+        <v>0.8535290182304733</v>
       </c>
       <c r="C320">
-        <v>0.008391608391608392</v>
+        <v>0.007523510971786834</v>
       </c>
       <c r="D320">
-        <v>0.2906453226613306</v>
+        <v>0.208104052026013</v>
       </c>
       <c r="E320">
-        <v>0.004213483146067416</v>
+        <v>0.003775959723096287</v>
       </c>
       <c r="F320">
         <v>1</v>
@@ -7853,19 +7853,19 @@
         <v>325</v>
       </c>
       <c r="B321">
-        <v>0.7630623433583961</v>
+        <v>0.7679824561403509</v>
       </c>
       <c r="C321">
-        <v>0.2055384615384615</v>
+        <v>0.1915966386554622</v>
       </c>
       <c r="D321">
-        <v>0.3541770885442722</v>
+        <v>0.2781390695347674</v>
       </c>
       <c r="E321">
-        <v>0.1151724137931034</v>
+        <v>0.1062111801242236</v>
       </c>
       <c r="F321">
-        <v>0.9542857142857143</v>
+        <v>0.9771428571428571</v>
       </c>
     </row>
     <row r="322" spans="1:6">
@@ -7873,19 +7873,19 @@
         <v>326</v>
       </c>
       <c r="B322">
-        <v>0.1714214214214214</v>
+        <v>0.5778278278278278</v>
       </c>
       <c r="C322">
-        <v>0</v>
+        <v>0.001289490651192779</v>
       </c>
       <c r="D322">
-        <v>0.3601800900450225</v>
+        <v>0.2251125562781391</v>
       </c>
       <c r="E322">
-        <v>0</v>
+        <v>0.0006451612903225806</v>
       </c>
       <c r="F322">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="323" spans="1:6">
@@ -7893,16 +7893,16 @@
         <v>327</v>
       </c>
       <c r="B323">
-        <v>0.6909409409409409</v>
+        <v>0.963963963963964</v>
       </c>
       <c r="C323">
-        <v>0.001547987616099071</v>
+        <v>0.001358695652173913</v>
       </c>
       <c r="D323">
-        <v>0.3546773386693347</v>
+        <v>0.264632316158079</v>
       </c>
       <c r="E323">
-        <v>0.000774593338497289</v>
+        <v>0.0006798096532970768</v>
       </c>
       <c r="F323">
         <v>1</v>
@@ -7913,16 +7913,16 @@
         <v>328</v>
       </c>
       <c r="B324">
-        <v>0.6468968968968969</v>
+        <v>0.831081081081081</v>
       </c>
       <c r="C324">
-        <v>0.001362397820163488</v>
+        <v>0.001262626262626263</v>
       </c>
       <c r="D324">
-        <v>0.2666333166583292</v>
+        <v>0.2086043021510755</v>
       </c>
       <c r="E324">
-        <v>0.0006816632583503749</v>
+        <v>0.0006317119393556538</v>
       </c>
       <c r="F324">
         <v>1</v>
@@ -7933,16 +7933,16 @@
         <v>329</v>
       </c>
       <c r="B325">
-        <v>0.798407917383821</v>
+        <v>0.7123493975903614</v>
       </c>
       <c r="C325">
-        <v>0.01068702290076336</v>
+        <v>0.009695290858725761</v>
       </c>
       <c r="D325">
-        <v>0.3516758379189595</v>
+        <v>0.2846423211605803</v>
       </c>
       <c r="E325">
-        <v>0.005372217958557176</v>
+        <v>0.004871259568545581</v>
       </c>
       <c r="F325">
         <v>1</v>
@@ -7953,19 +7953,19 @@
         <v>330</v>
       </c>
       <c r="B326">
-        <v>0.7099270256668344</v>
+        <v>0.7427235363194096</v>
       </c>
       <c r="C326">
-        <v>0.01650412603150788</v>
+        <v>0.01696113074204947</v>
       </c>
       <c r="D326">
-        <v>0.3441720860430215</v>
+        <v>0.304152076038019</v>
       </c>
       <c r="E326">
-        <v>0.008327024981074944</v>
+        <v>0.008553100498930863</v>
       </c>
       <c r="F326">
-        <v>0.9166666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="327" spans="1:6">
@@ -7973,19 +7973,19 @@
         <v>331</v>
       </c>
       <c r="B327">
-        <v>0.6428460763808196</v>
+        <v>0.638236888992176</v>
       </c>
       <c r="C327">
-        <v>0.01741884402216944</v>
+        <v>0.01577287066246057</v>
       </c>
       <c r="D327">
-        <v>0.3791895947973987</v>
+        <v>0.375687843921961</v>
       </c>
       <c r="E327">
-        <v>0.008800000000000001</v>
+        <v>0.00796812749003984</v>
       </c>
       <c r="F327">
-        <v>0.8461538461538461</v>
+        <v>0.7692307692307693</v>
       </c>
     </row>
     <row r="328" spans="1:6">
@@ -7993,19 +7993,19 @@
         <v>332</v>
       </c>
       <c r="B328">
-        <v>0.6137254901960785</v>
+        <v>0.7247863247863248</v>
       </c>
       <c r="C328">
-        <v>0.01118099231306778</v>
+        <v>0.0115681233933162</v>
       </c>
       <c r="D328">
-        <v>0.2921460730365182</v>
+        <v>0.2306153076538269</v>
       </c>
       <c r="E328">
-        <v>0.005629838142153413</v>
+        <v>0.005821474773609315</v>
       </c>
       <c r="F328">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="329" spans="1:6">
@@ -8013,16 +8013,16 @@
         <v>333</v>
       </c>
       <c r="B329">
-        <v>0.4076576576576577</v>
+        <v>0.8408408408408409</v>
       </c>
       <c r="C329">
-        <v>0.001411432604093155</v>
+        <v>0.001261034047919294</v>
       </c>
       <c r="D329">
-        <v>0.2921460730365182</v>
+        <v>0.2076038019009505</v>
       </c>
       <c r="E329">
-        <v>0.0007062146892655367</v>
+        <v>0.0006309148264984228</v>
       </c>
       <c r="F329">
         <v>1</v>
@@ -8033,16 +8033,16 @@
         <v>334</v>
       </c>
       <c r="B330">
-        <v>0.7275045994313429</v>
+        <v>0.6271533701287841</v>
       </c>
       <c r="C330">
-        <v>0.009654062751407884</v>
+        <v>0.007827788649706457</v>
       </c>
       <c r="D330">
-        <v>0.384192096048024</v>
+        <v>0.2391195597798899</v>
       </c>
       <c r="E330">
-        <v>0.004850444624090542</v>
+        <v>0.003929273084479371</v>
       </c>
       <c r="F330">
         <v>1</v>
@@ -8053,16 +8053,16 @@
         <v>335</v>
       </c>
       <c r="B331">
-        <v>0.834626940410616</v>
+        <v>0.914121181772659</v>
       </c>
       <c r="C331">
-        <v>0.003210272873194221</v>
+        <v>0.002752924982794219</v>
       </c>
       <c r="D331">
-        <v>0.3786893446723362</v>
+        <v>0.2751375687843922</v>
       </c>
       <c r="E331">
-        <v>0.001607717041800643</v>
+        <v>0.001378359751895245</v>
       </c>
       <c r="F331">
         <v>1</v>
@@ -8073,16 +8073,16 @@
         <v>336</v>
       </c>
       <c r="B332">
-        <v>0.6256892230576442</v>
+        <v>0.6063283208020049</v>
       </c>
       <c r="C332">
-        <v>0.005856515373352855</v>
+        <v>0.005431093007467753</v>
       </c>
       <c r="D332">
-        <v>0.3206603301650826</v>
+        <v>0.2671335667833917</v>
       </c>
       <c r="E332">
-        <v>0.002936857562408223</v>
+        <v>0.002722940776038121</v>
       </c>
       <c r="F332">
         <v>1</v>
@@ -8093,19 +8093,19 @@
         <v>337</v>
       </c>
       <c r="B333">
-        <v>0.7164719823937702</v>
+        <v>0.6363974944980532</v>
       </c>
       <c r="C333">
-        <v>0.03581267217630854</v>
+        <v>0.03536585365853658</v>
       </c>
       <c r="D333">
-        <v>0.2996498249124562</v>
+        <v>0.2086043021510755</v>
       </c>
       <c r="E333">
-        <v>0.01828410689170183</v>
+        <v>0.01801242236024845</v>
       </c>
       <c r="F333">
-        <v>0.8666666666666667</v>
+        <v>0.9666666666666667</v>
       </c>
     </row>
     <row r="334" spans="1:6">
@@ -8113,19 +8113,19 @@
         <v>338</v>
       </c>
       <c r="B334">
-        <v>0.3535929432013769</v>
+        <v>0.5434954102122777</v>
       </c>
       <c r="C334">
-        <v>0.003284072249589491</v>
+        <v>0.007102272727272727</v>
       </c>
       <c r="D334">
-        <v>0.3926963481740871</v>
+        <v>0.3006503251625813</v>
       </c>
       <c r="E334">
-        <v>0.001651527663088357</v>
+        <v>0.00356887937187723</v>
       </c>
       <c r="F334">
-        <v>0.2857142857142857</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="335" spans="1:6">
@@ -8133,19 +8133,19 @@
         <v>339</v>
       </c>
       <c r="B335">
-        <v>0.4419700018291567</v>
+        <v>0.5446542893725992</v>
       </c>
       <c r="C335">
-        <v>0.01087695445275323</v>
+        <v>0.0115979381443299</v>
       </c>
       <c r="D335">
-        <v>0.272136068034017</v>
+        <v>0.2326163081540771</v>
       </c>
       <c r="E335">
-        <v>0.005479452054794521</v>
+        <v>0.005840363400389357</v>
       </c>
       <c r="F335">
-        <v>0.7272727272727273</v>
+        <v>0.8181818181818182</v>
       </c>
     </row>
     <row r="336" spans="1:6">
@@ -8153,16 +8153,16 @@
         <v>340</v>
       </c>
       <c r="B336">
-        <v>0.6290726817042608</v>
+        <v>0.6164786967418547</v>
       </c>
       <c r="C336">
-        <v>0.005710206995003569</v>
+        <v>0.004944375772558714</v>
       </c>
       <c r="D336">
-        <v>0.3031515757878939</v>
+        <v>0.1945972986493247</v>
       </c>
       <c r="E336">
-        <v>0.002863278453829635</v>
+        <v>0.002478314745972739</v>
       </c>
       <c r="F336">
         <v>1</v>
@@ -8173,19 +8173,19 @@
         <v>341</v>
       </c>
       <c r="B337">
-        <v>0.5112781954887219</v>
+        <v>0.5793233082706767</v>
       </c>
       <c r="C337">
-        <v>0.00293470286133529</v>
+        <v>0.005280528052805281</v>
       </c>
       <c r="D337">
-        <v>0.32016008004002</v>
+        <v>0.2461230615307654</v>
       </c>
       <c r="E337">
-        <v>0.001471670345842531</v>
+        <v>0.002647253474520185</v>
       </c>
       <c r="F337">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="338" spans="1:6">
@@ -8193,19 +8193,19 @@
         <v>342</v>
       </c>
       <c r="B338">
-        <v>0.2965178096757043</v>
+        <v>0.4237107921318447</v>
       </c>
       <c r="C338">
-        <v>0.01110340041637752</v>
+        <v>0.01923076923076923</v>
       </c>
       <c r="D338">
-        <v>0.2871435717858929</v>
+        <v>0.183591795897949</v>
       </c>
       <c r="E338">
-        <v>0.005625879043600563</v>
+        <v>0.009726443768996961</v>
       </c>
       <c r="F338">
-        <v>0.4210526315789473</v>
+        <v>0.8421052631578947</v>
       </c>
     </row>
     <row r="339" spans="1:6">
@@ -8213,13 +8213,13 @@
         <v>343</v>
       </c>
       <c r="B339">
-        <v>0.2132132132132132</v>
+        <v>0.07807807807807809</v>
       </c>
       <c r="C339">
         <v>0</v>
       </c>
       <c r="D339">
-        <v>0.2781390695347674</v>
+        <v>0.2086043021510755</v>
       </c>
       <c r="E339">
         <v>0</v>
@@ -8233,19 +8233,19 @@
         <v>344</v>
       </c>
       <c r="B340">
-        <v>0.471206810215323</v>
+        <v>0.3681772658988482</v>
       </c>
       <c r="C340">
-        <v>0.002991772625280479</v>
+        <v>0.001225490196078431</v>
       </c>
       <c r="D340">
-        <v>0.3331665832916458</v>
+        <v>0.184592296148074</v>
       </c>
       <c r="E340">
-        <v>0.00149812734082397</v>
+        <v>0.0006134969325153375</v>
       </c>
       <c r="F340">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="341" spans="1:6">
@@ -8253,16 +8253,16 @@
         <v>345</v>
       </c>
       <c r="B341">
-        <v>0.9484226339509264</v>
+        <v>0.8337506259389084</v>
       </c>
       <c r="C341">
-        <v>0.00301659125188537</v>
+        <v>0.003225806451612903</v>
       </c>
       <c r="D341">
-        <v>0.3386693346673337</v>
+        <v>0.3816908454227114</v>
       </c>
       <c r="E341">
-        <v>0.001510574018126888</v>
+        <v>0.001615508885298869</v>
       </c>
       <c r="F341">
         <v>1</v>
@@ -8273,16 +8273,16 @@
         <v>346</v>
       </c>
       <c r="B342">
-        <v>0.5748248248248249</v>
+        <v>0.7555055055055054</v>
       </c>
       <c r="C342">
-        <v>0.001771479185119575</v>
+        <v>0.001480384900074019</v>
       </c>
       <c r="D342">
-        <v>0.4362181090545272</v>
+        <v>0.3251625812906453</v>
       </c>
       <c r="E342">
-        <v>0.0008865248226950354</v>
+        <v>0.0007407407407407407</v>
       </c>
       <c r="F342">
         <v>1</v>
@@ -8293,19 +8293,19 @@
         <v>347</v>
       </c>
       <c r="B343">
-        <v>0.5590772316950853</v>
+        <v>0.7237211634904714</v>
       </c>
       <c r="C343">
-        <v>0.00645682001614205</v>
+        <v>0.006480881399870382</v>
       </c>
       <c r="D343">
-        <v>0.384192096048024</v>
+        <v>0.2331165582791396</v>
       </c>
       <c r="E343">
-        <v>0.003241491085899514</v>
+        <v>0.003250975292587776</v>
       </c>
       <c r="F343">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="344" spans="1:6">
@@ -8313,19 +8313,19 @@
         <v>348</v>
       </c>
       <c r="B344">
-        <v>0.6675652346182147</v>
+        <v>0.6569380766400634</v>
       </c>
       <c r="C344">
-        <v>0.04688644688644689</v>
+        <v>0.04276729559748427</v>
       </c>
       <c r="D344">
-        <v>0.3491745872936468</v>
+        <v>0.2386193096548274</v>
       </c>
       <c r="E344">
-        <v>0.02407825432656132</v>
+        <v>0.02187902187902188</v>
       </c>
       <c r="F344">
-        <v>0.8888888888888888</v>
+        <v>0.9444444444444444</v>
       </c>
     </row>
     <row r="345" spans="1:6">
@@ -8333,19 +8333,19 @@
         <v>349</v>
       </c>
       <c r="B345">
-        <v>0.6097970139238382</v>
+        <v>0.5118478443214225</v>
       </c>
       <c r="C345">
-        <v>0.01516300227445034</v>
+        <v>0.01198402130492676</v>
       </c>
       <c r="D345">
-        <v>0.3501750875437719</v>
+        <v>0.2576288144072036</v>
       </c>
       <c r="E345">
-        <v>0.007651109410864576</v>
+        <v>0.006040268456375839</v>
       </c>
       <c r="F345">
-        <v>0.8333333333333334</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="346" spans="1:6">
@@ -8353,19 +8353,19 @@
         <v>350</v>
       </c>
       <c r="B346">
-        <v>0.4922866775168566</v>
+        <v>0.5314403627063474</v>
       </c>
       <c r="C346">
-        <v>0.04407294832826748</v>
+        <v>0.04909747292418772</v>
       </c>
       <c r="D346">
-        <v>0.3706853426713357</v>
+        <v>0.3411705852926463</v>
       </c>
       <c r="E346">
-        <v>0.02279874213836478</v>
+        <v>0.02535421327367636</v>
       </c>
       <c r="F346">
-        <v>0.6590909090909091</v>
+        <v>0.7727272727272727</v>
       </c>
     </row>
     <row r="347" spans="1:6">
@@ -8373,13 +8373,13 @@
         <v>351</v>
       </c>
       <c r="B347">
-        <v>0.1043543543543543</v>
+        <v>0.1856856856856857</v>
       </c>
       <c r="C347">
         <v>0</v>
       </c>
       <c r="D347">
-        <v>0.2666333166583292</v>
+        <v>0.2371185592796398</v>
       </c>
       <c r="E347">
         <v>0</v>
@@ -8393,19 +8393,19 @@
         <v>352</v>
       </c>
       <c r="B348">
-        <v>0.7195806962025316</v>
+        <v>0.8380109440928269</v>
       </c>
       <c r="C348">
-        <v>0.09825033647375504</v>
+        <v>0.09375</v>
       </c>
       <c r="D348">
-        <v>0.3296648324162081</v>
+        <v>0.2456228114057029</v>
       </c>
       <c r="E348">
-        <v>0.05188343994314144</v>
+        <v>0.04921135646687697</v>
       </c>
       <c r="F348">
-        <v>0.9240506329113924</v>
+        <v>0.9873417721518988</v>
       </c>
     </row>
     <row r="349" spans="1:6">
@@ -8413,16 +8413,16 @@
         <v>353</v>
       </c>
       <c r="B349">
-        <v>0.6055137844611529</v>
+        <v>0.7132832080200501</v>
       </c>
       <c r="C349">
-        <v>0.004231311706629055</v>
+        <v>0.004514672686230248</v>
       </c>
       <c r="D349">
-        <v>0.2936468234117058</v>
+        <v>0.3381690845422711</v>
       </c>
       <c r="E349">
-        <v>0.002121640735502122</v>
+        <v>0.002264150943396227</v>
       </c>
       <c r="F349">
         <v>0.75</v>
@@ -8433,16 +8433,16 @@
         <v>354</v>
       </c>
       <c r="B350">
-        <v>0.7101701115785624</v>
+        <v>0.7468904335101517</v>
       </c>
       <c r="C350">
-        <v>0.01417434443656981</v>
+        <v>0.01186239620403321</v>
       </c>
       <c r="D350">
-        <v>0.304152076038019</v>
+        <v>0.1665832916458229</v>
       </c>
       <c r="E350">
-        <v>0.007142857142857143</v>
+        <v>0.005970149253731343</v>
       </c>
       <c r="F350">
         <v>0.9090909090909091</v>
@@ -8453,19 +8453,19 @@
         <v>355</v>
       </c>
       <c r="B351">
-        <v>0.7495319569400384</v>
+        <v>0.7372176573578102</v>
       </c>
       <c r="C351">
-        <v>0.1502890173410405</v>
+        <v>0.1361556064073227</v>
       </c>
       <c r="D351">
-        <v>0.3381690845422711</v>
+        <v>0.2446223111555778</v>
       </c>
       <c r="E351">
-        <v>0.08158995815899582</v>
+        <v>0.07323076923076922</v>
       </c>
       <c r="F351">
-        <v>0.9512195121951219</v>
+        <v>0.967479674796748</v>
       </c>
     </row>
     <row r="352" spans="1:6">
@@ -8473,19 +8473,19 @@
         <v>356</v>
       </c>
       <c r="B352">
-        <v>0.7527895466748094</v>
+        <v>0.741014288077153</v>
       </c>
       <c r="C352">
-        <v>0.1032095657646318</v>
+        <v>0.1016311166875784</v>
       </c>
       <c r="D352">
-        <v>0.2871435717858929</v>
+        <v>0.2836418209104552</v>
       </c>
       <c r="E352">
-        <v>0.0544127405441274</v>
+        <v>0.05357142857142857</v>
       </c>
       <c r="F352">
-        <v>1</v>
+        <v>0.9878048780487805</v>
       </c>
     </row>
     <row r="353" spans="1:6">
@@ -8493,19 +8493,19 @@
         <v>357</v>
       </c>
       <c r="B353">
-        <v>0.5907352315110196</v>
+        <v>0.6032282086238564</v>
       </c>
       <c r="C353">
-        <v>0.02285575939531382</v>
+        <v>0.02320723764640767</v>
       </c>
       <c r="D353">
-        <v>0.3295793195743171</v>
+        <v>0.2712039780574048</v>
       </c>
       <c r="E353">
-        <v>0.01230987302251114</v>
+        <v>0.01240595437535159</v>
       </c>
       <c r="F353">
-        <v>0.755052294103011</v>
+        <v>0.7969352671618057</v>
       </c>
     </row>
   </sheetData>
